--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE3B59A-7F73-4690-A960-80E69BCDC5FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F452AEEC-58A2-431E-B60E-91644BE5E09F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1122,9 +1122,6 @@
     <t>САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у</t>
   </si>
   <si>
-    <t xml:space="preserve">СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11 </t>
-  </si>
-  <si>
     <t>Ротация кода 6459</t>
   </si>
   <si>
@@ -1152,10 +1149,13 @@
     <t>БРАУНШВЕЙГСКАЯ с/к с/н мгс 1/100_Л10</t>
   </si>
   <si>
-    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10 (7613)</t>
+    <t>ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
   </si>
   <si>
-    <t>ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
+    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
   </si>
 </sst>
 </file>
@@ -2083,15 +2083,15 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5655,17 +5655,17 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="146">
+      <c r="D1" s="142">
         <v>130438122</v>
       </c>
-      <c r="E1" s="142" t="s">
+      <c r="E1" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="145"/>
       <c r="K1" s="130">
         <v>130438122</v>
       </c>
@@ -5696,13 +5696,13 @@
         <f>D3+3</f>
         <v>46219</v>
       </c>
-      <c r="G3" s="145" t="str">
+      <c r="G3" s="146" t="str">
         <f>VLOOKUP(D1,K:L,2,0)</f>
         <v>130438122 ООО "НОВОЕ ВРЕМЯ"  272151 Бердянский р-н 90  Трояны</v>
       </c>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="145"/>
       <c r="K3" s="130">
         <v>130438120</v>
       </c>
@@ -10665,7 +10665,7 @@
         <v>7608</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>21</v>
@@ -10688,7 +10688,7 @@
         <v>45</v>
       </c>
       <c r="J101" s="52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L101" s="129"/>
     </row>
@@ -10697,7 +10697,7 @@
         <v>7610</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>21</v>
@@ -10720,7 +10720,7 @@
         <v>45</v>
       </c>
       <c r="J102" s="52" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L102" s="129"/>
     </row>
@@ -11597,7 +11597,7 @@
         <v>60</v>
       </c>
       <c r="J126" s="52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L126" s="129"/>
     </row>
@@ -11629,7 +11629,7 @@
         <v>60</v>
       </c>
       <c r="J127" s="141" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L127" s="129"/>
     </row>
@@ -11668,7 +11668,7 @@
         <v>7616</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>21</v>
@@ -11691,7 +11691,7 @@
         <v>60</v>
       </c>
       <c r="J129" s="52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L129" s="129"/>
     </row>
@@ -11850,7 +11850,7 @@
         <v>7626</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>21</v>
@@ -11873,7 +11873,7 @@
         <v>60</v>
       </c>
       <c r="J135" s="52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L135" s="129"/>
     </row>
@@ -13251,7 +13251,7 @@
         <v>60</v>
       </c>
       <c r="J161" s="52" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L161" s="129"/>
     </row>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F452AEEC-58A2-431E-B60E-91644BE5E09F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C61D7A-3F27-4E40-B973-4ECCC7535AB7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$162</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$598</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$598</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$164</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$600</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$600</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="225">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1152,10 +1152,19 @@
     <t>ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
   </si>
   <si>
-    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
+    <t>СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
   </si>
   <si>
-    <t>СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
+    <t>СЫРРРВЕЛАТ Папа может в/к в/у 0.28кг 8шт</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у 0.84кг</t>
+  </si>
+  <si>
+    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10 (7613)</t>
+  </si>
+  <si>
+    <t>ДЛЯ ДЕТЕЙ Папа может сос п/о мгс 0.33кг</t>
   </si>
 </sst>
 </file>
@@ -5633,7 +5642,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1686"/>
+  <dimension ref="A1:BO1688"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -7679,7 +7688,7 @@
         <v>7461</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="C40" s="55" t="s">
         <v>21</v>
@@ -10076,7 +10085,7 @@
         <v>0.33</v>
       </c>
       <c r="G81" s="23">
-        <f t="shared" ref="G81:G91" si="14">E81*F81</f>
+        <f t="shared" ref="G81:G93" si="14">E81*F81</f>
         <v>0</v>
       </c>
       <c r="H81" s="14">
@@ -10242,87 +10251,81 @@
     </row>
     <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="56">
-        <v>6807</v>
+        <v>7133</v>
       </c>
       <c r="B87" s="54" t="s">
-        <v>76</v>
+        <v>222</v>
       </c>
       <c r="C87" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D87" s="57">
-        <v>1001300366807</v>
+        <v>1001300456946</v>
       </c>
       <c r="E87" s="24"/>
-      <c r="F87" s="58">
-        <v>0.33</v>
-      </c>
+      <c r="F87" s="58"/>
       <c r="G87" s="23">
-        <f t="shared" si="14"/>
+        <f>E87</f>
         <v>0</v>
       </c>
-      <c r="H87" s="59">
-        <v>2.64</v>
-      </c>
-      <c r="I87" s="59">
-        <v>45</v>
-      </c>
+      <c r="H87" s="59"/>
+      <c r="I87" s="59"/>
       <c r="J87" s="59"/>
       <c r="L87" s="129"/>
     </row>
     <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="56">
-        <v>7154</v>
+        <v>6807</v>
       </c>
       <c r="B88" s="54" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C88" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D88" s="57">
-        <v>1001300387154</v>
+        <v>1001300366807</v>
       </c>
       <c r="E88" s="24"/>
-      <c r="F88" s="23">
-        <v>0.35</v>
+      <c r="F88" s="58">
+        <v>0.33</v>
       </c>
       <c r="G88" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H88" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I88" s="14">
-        <v>50</v>
-      </c>
-      <c r="J88" s="29"/>
+      <c r="H88" s="59">
+        <v>2.64</v>
+      </c>
+      <c r="I88" s="59">
+        <v>45</v>
+      </c>
+      <c r="J88" s="59"/>
       <c r="L88" s="129"/>
     </row>
     <row r="89" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="56">
-        <v>7157</v>
+        <v>7154</v>
       </c>
       <c r="B89" s="54" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C89" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D89" s="57">
-        <v>1001300387157</v>
+        <v>1001300387154</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="23">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="G89" s="23">
-        <f>E89</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H89" s="14">
-        <v>5.04</v>
+        <v>2.8</v>
       </c>
       <c r="I89" s="14">
         <v>50</v>
@@ -10332,57 +10335,57 @@
     </row>
     <row r="90" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="56">
-        <v>7236</v>
+        <v>7157</v>
       </c>
       <c r="B90" s="54" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C90" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D90" s="57">
-        <v>1001304507236</v>
+        <v>1001300387157</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.63</v>
       </c>
       <c r="G90" s="23">
-        <f t="shared" si="14"/>
+        <f>E90</f>
         <v>0</v>
       </c>
       <c r="H90" s="14">
-        <v>2.2400000000000002</v>
+        <v>5.04</v>
       </c>
       <c r="I90" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J90" s="29"/>
       <c r="L90" s="129"/>
     </row>
     <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="56">
-        <v>6787</v>
-      </c>
-      <c r="B91" s="123" t="s">
-        <v>66</v>
+        <v>7236</v>
+      </c>
+      <c r="B91" s="54" t="s">
+        <v>69</v>
       </c>
       <c r="C91" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D91" s="57">
-        <v>1001300456787</v>
+        <v>1001304507236</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G91" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H91" s="14">
-        <v>2.64</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I91" s="14">
         <v>45</v>
@@ -10392,147 +10395,143 @@
     </row>
     <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="56">
-        <v>7166</v>
-      </c>
-      <c r="B92" s="123" t="s">
-        <v>72</v>
+        <v>7236</v>
+      </c>
+      <c r="B92" s="54" t="s">
+        <v>221</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D92" s="57">
-        <v>1001303987166</v>
+        <v>1001307357489</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.7</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G92" s="23">
-        <f>E92</f>
+        <f t="shared" ref="G92" si="15">E92*F92</f>
         <v>0</v>
       </c>
-      <c r="H92" s="14">
-        <v>5.6</v>
-      </c>
-      <c r="I92" s="14">
-        <v>50</v>
-      </c>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
       <c r="J92" s="29"/>
       <c r="L92" s="129"/>
     </row>
-    <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="56">
-        <v>7169</v>
-      </c>
-      <c r="B93" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C93" s="50" t="s">
+        <v>6787</v>
+      </c>
+      <c r="B93" s="123" t="s">
+        <v>66</v>
+      </c>
+      <c r="C93" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D93" s="51">
-        <v>1001303987169</v>
+      <c r="D93" s="57">
+        <v>1001300456787</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="G93" s="23">
-        <f>E93*F93</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H93" s="14">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="I93" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J93" s="29"/>
       <c r="L93" s="129"/>
     </row>
-    <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="56">
-        <v>5544</v>
-      </c>
-      <c r="B94" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="C94" s="50" t="s">
+        <v>7166</v>
+      </c>
+      <c r="B94" s="123" t="s">
+        <v>72</v>
+      </c>
+      <c r="C94" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="D94" s="51">
-        <v>1001051875544</v>
+      <c r="D94" s="57">
+        <v>1001303987166</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.81</v>
+        <v>0.7</v>
       </c>
       <c r="G94" s="23">
         <f>E94</f>
         <v>0</v>
       </c>
       <c r="H94" s="14">
-        <v>4.8600000000000003</v>
+        <v>5.6</v>
       </c>
       <c r="I94" s="14">
-        <v>45</v>
-      </c>
-      <c r="J94" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J94" s="29"/>
       <c r="L94" s="129"/>
     </row>
     <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="56">
-        <v>6697</v>
+        <v>7169</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C95" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D95" s="51">
-        <v>1001301876697</v>
+        <v>1001303987169</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
         <v>0.35</v>
       </c>
       <c r="G95" s="23">
-        <f t="shared" ref="G95:G102" si="15">E95*F95</f>
+        <f>E95*F95</f>
         <v>0</v>
       </c>
       <c r="H95" s="14">
         <v>2.8</v>
       </c>
       <c r="I95" s="14">
-        <v>45</v>
-      </c>
-      <c r="J95" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J95" s="29"/>
       <c r="L95" s="129"/>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="56">
-        <v>7237</v>
+        <v>5544</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D96" s="51">
-        <v>1001304497237</v>
+        <v>1001051875544</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.81</v>
       </c>
       <c r="G96" s="23">
-        <f t="shared" si="15"/>
+        <f>E96</f>
         <v>0</v>
       </c>
       <c r="H96" s="14">
-        <v>2.2400000000000002</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I96" s="14">
         <v>45</v>
@@ -10542,27 +10541,27 @@
     </row>
     <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="56">
-        <v>7238</v>
+        <v>6697</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D97" s="51">
-        <v>1001305197238</v>
+        <v>1001301876697</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G97" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="G97:G104" si="16">E97*F97</f>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I97" s="14">
         <v>45</v>
@@ -10572,87 +10571,87 @@
     </row>
     <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="56">
-        <v>7177</v>
+        <v>7237</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="51">
-        <v>1001302347177</v>
+        <v>1001304497237</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G98" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.8</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I98" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J98" s="49"/>
       <c r="L98" s="129"/>
     </row>
     <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="56">
-        <v>7332</v>
+        <v>7238</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="51">
-        <v>1001301777332</v>
+        <v>1001305197238</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G99" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I99" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J99" s="49"/>
       <c r="L99" s="129"/>
     </row>
     <row r="100" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="56">
-        <v>7333</v>
+        <v>7177</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="51">
-        <v>1001303987333</v>
+        <v>1001302347177</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G100" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I100" s="14">
         <v>50</v>
@@ -10661,256 +10660,144 @@
       <c r="L100" s="129"/>
     </row>
     <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="133">
-        <v>7608</v>
+      <c r="A101" s="56">
+        <v>7332</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>221</v>
+        <v>63</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D101" s="51">
-        <v>1001304197608</v>
+        <v>1001301777332</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G101" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I101" s="14">
-        <v>45</v>
-      </c>
-      <c r="J101" s="52" t="s">
-        <v>210</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J101" s="49"/>
       <c r="L101" s="129"/>
     </row>
-    <row r="102" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="133">
-        <v>7610</v>
+    <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="56">
+        <v>7333</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>211</v>
+        <v>70</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="51">
-        <v>1001306717610</v>
+        <v>1001303987333</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G102" s="23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H102" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I102" s="14">
+        <v>50</v>
+      </c>
+      <c r="J102" s="49"/>
+      <c r="L102" s="129"/>
+    </row>
+    <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="133">
+        <v>7608</v>
+      </c>
+      <c r="B103" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="C103" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" s="51">
+        <v>1001304197608</v>
+      </c>
+      <c r="E103" s="24"/>
+      <c r="F103" s="23">
         <v>0.1</v>
       </c>
-      <c r="G102" s="23">
-        <f t="shared" si="15"/>
+      <c r="G103" s="23">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H102" s="14">
+      <c r="H103" s="14">
         <v>1</v>
       </c>
-      <c r="I102" s="14">
+      <c r="I103" s="14">
         <v>45</v>
       </c>
-      <c r="J102" s="52" t="s">
+      <c r="J103" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="L103" s="129"/>
+    </row>
+    <row r="104" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="133">
+        <v>7610</v>
+      </c>
+      <c r="B104" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="C104" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E104" s="24"/>
+      <c r="F104" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G104" s="23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H104" s="14">
+        <v>1</v>
+      </c>
+      <c r="I104" s="14">
+        <v>45</v>
+      </c>
+      <c r="J104" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="L102" s="129"/>
-    </row>
-    <row r="103" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="47" t="s">
+      <c r="L104" s="129"/>
+    </row>
+    <row r="105" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B103" s="42" t="s">
+      <c r="B105" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C103" s="42"/>
-      <c r="D103" s="42"/>
-      <c r="E103" s="42"/>
-      <c r="F103" s="41"/>
-      <c r="G103" s="42"/>
-      <c r="H103" s="42"/>
-      <c r="I103" s="42"/>
-      <c r="J103" s="43"/>
-      <c r="K103" s="60"/>
-      <c r="L103" s="129"/>
-      <c r="M103" s="129"/>
-      <c r="N103" s="129"/>
-      <c r="O103" s="129"/>
-      <c r="P103" s="129"/>
-      <c r="Q103" s="129"/>
-      <c r="R103" s="129"/>
-      <c r="S103" s="129"/>
-      <c r="T103" s="129"/>
-      <c r="U103" s="129"/>
-      <c r="V103" s="129"/>
-      <c r="W103" s="129"/>
-      <c r="X103" s="129"/>
-      <c r="Y103" s="129"/>
-      <c r="Z103" s="129"/>
-      <c r="AA103" s="129"/>
-      <c r="AB103" s="129"/>
-      <c r="AC103" s="129"/>
-      <c r="AD103" s="129"/>
-      <c r="AE103" s="129"/>
-      <c r="AF103" s="129"/>
-      <c r="AG103" s="129"/>
-      <c r="AH103" s="129"/>
-      <c r="AI103" s="129"/>
-      <c r="AJ103" s="129"/>
-      <c r="AK103" s="129"/>
-      <c r="AL103" s="129"/>
-      <c r="AM103" s="129"/>
-      <c r="AN103" s="129"/>
-      <c r="AO103" s="129"/>
-      <c r="AP103" s="129"/>
-      <c r="AQ103" s="129"/>
-      <c r="AR103" s="129"/>
-      <c r="AS103" s="129"/>
-      <c r="AT103" s="129"/>
-      <c r="AU103" s="129"/>
-      <c r="AV103" s="129"/>
-      <c r="AW103" s="129"/>
-      <c r="AX103" s="129"/>
-      <c r="AY103" s="129"/>
-      <c r="AZ103" s="129"/>
-      <c r="BA103" s="129"/>
-      <c r="BB103" s="129"/>
-      <c r="BC103" s="129"/>
-      <c r="BD103" s="129"/>
-      <c r="BE103" s="129"/>
-      <c r="BF103" s="129"/>
-      <c r="BG103" s="129"/>
-      <c r="BH103" s="129"/>
-      <c r="BI103" s="129"/>
-      <c r="BJ103" s="129"/>
-      <c r="BK103" s="129"/>
-      <c r="BL103" s="129"/>
-      <c r="BM103" s="129"/>
-      <c r="BN103" s="129"/>
-      <c r="BO103" s="129"/>
-    </row>
-    <row r="104" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="56">
-        <v>3582</v>
-      </c>
-      <c r="B104" s="54" t="s">
-        <v>161</v>
-      </c>
-      <c r="C104" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D104" s="57">
-        <v>1001061973582</v>
-      </c>
-      <c r="E104" s="24"/>
-      <c r="F104" s="58">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G104" s="23">
-        <f>E104</f>
-        <v>0</v>
-      </c>
-      <c r="H104" s="117">
-        <v>3.9</v>
-      </c>
-      <c r="I104" s="116">
-        <v>120</v>
-      </c>
-      <c r="J104" s="59"/>
-      <c r="K104" s="60"/>
-      <c r="L104" s="129"/>
-      <c r="M104" s="129"/>
-      <c r="N104" s="129"/>
-      <c r="O104" s="129"/>
-      <c r="P104" s="129"/>
-      <c r="Q104" s="129"/>
-      <c r="R104" s="129"/>
-      <c r="S104" s="129"/>
-      <c r="T104" s="129"/>
-      <c r="U104" s="129"/>
-      <c r="V104" s="129"/>
-      <c r="W104" s="129"/>
-      <c r="X104" s="129"/>
-      <c r="Y104" s="129"/>
-      <c r="Z104" s="129"/>
-      <c r="AA104" s="129"/>
-      <c r="AB104" s="129"/>
-      <c r="AC104" s="129"/>
-      <c r="AD104" s="129"/>
-      <c r="AE104" s="129"/>
-      <c r="AF104" s="129"/>
-      <c r="AG104" s="129"/>
-      <c r="AH104" s="129"/>
-      <c r="AI104" s="129"/>
-      <c r="AJ104" s="129"/>
-      <c r="AK104" s="129"/>
-      <c r="AL104" s="129"/>
-      <c r="AM104" s="129"/>
-      <c r="AN104" s="129"/>
-      <c r="AO104" s="129"/>
-      <c r="AP104" s="129"/>
-      <c r="AQ104" s="129"/>
-      <c r="AR104" s="129"/>
-      <c r="AS104" s="129"/>
-      <c r="AT104" s="129"/>
-      <c r="AU104" s="129"/>
-      <c r="AV104" s="129"/>
-      <c r="AW104" s="129"/>
-      <c r="AX104" s="129"/>
-      <c r="AY104" s="129"/>
-      <c r="AZ104" s="129"/>
-      <c r="BA104" s="129"/>
-      <c r="BB104" s="129"/>
-      <c r="BC104" s="129"/>
-      <c r="BD104" s="129"/>
-      <c r="BE104" s="129"/>
-      <c r="BF104" s="129"/>
-      <c r="BG104" s="129"/>
-      <c r="BH104" s="129"/>
-      <c r="BI104" s="129"/>
-      <c r="BJ104" s="129"/>
-      <c r="BK104" s="129"/>
-      <c r="BL104" s="129"/>
-      <c r="BM104" s="129"/>
-      <c r="BN104" s="129"/>
-      <c r="BO104" s="129"/>
-    </row>
-    <row r="105" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="56">
-        <v>3986</v>
-      </c>
-      <c r="B105" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="C105" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D105" s="57">
-        <v>1001061973986</v>
-      </c>
-      <c r="E105" s="24"/>
-      <c r="F105" s="58">
-        <v>0.25</v>
-      </c>
-      <c r="G105" s="23">
-        <f t="shared" ref="G105:G110" si="16">E105*F105</f>
-        <v>0</v>
-      </c>
-      <c r="H105" s="117">
-        <v>2</v>
-      </c>
-      <c r="I105" s="116">
-        <v>120</v>
-      </c>
-      <c r="J105" s="59"/>
+      <c r="C105" s="42"/>
+      <c r="D105" s="42"/>
+      <c r="E105" s="42"/>
+      <c r="F105" s="41"/>
+      <c r="G105" s="42"/>
+      <c r="H105" s="42"/>
+      <c r="I105" s="42"/>
+      <c r="J105" s="43"/>
       <c r="K105" s="60"/>
       <c r="L105" s="129"/>
       <c r="M105" s="129"/>
@@ -10969,89 +10856,201 @@
       <c r="BN105" s="129"/>
       <c r="BO105" s="129"/>
     </row>
-    <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A106" s="56">
-        <v>5931</v>
-      </c>
-      <c r="B106" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="C106" s="50" t="s">
+        <v>3582</v>
+      </c>
+      <c r="B106" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="C106" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D106" s="57">
+        <v>1001061973582</v>
+      </c>
+      <c r="E106" s="24"/>
+      <c r="F106" s="58">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="G106" s="23">
+        <f>E106</f>
+        <v>0</v>
+      </c>
+      <c r="H106" s="117">
+        <v>3.9</v>
+      </c>
+      <c r="I106" s="116">
+        <v>120</v>
+      </c>
+      <c r="J106" s="59"/>
+      <c r="K106" s="60"/>
+      <c r="L106" s="129"/>
+      <c r="M106" s="129"/>
+      <c r="N106" s="129"/>
+      <c r="O106" s="129"/>
+      <c r="P106" s="129"/>
+      <c r="Q106" s="129"/>
+      <c r="R106" s="129"/>
+      <c r="S106" s="129"/>
+      <c r="T106" s="129"/>
+      <c r="U106" s="129"/>
+      <c r="V106" s="129"/>
+      <c r="W106" s="129"/>
+      <c r="X106" s="129"/>
+      <c r="Y106" s="129"/>
+      <c r="Z106" s="129"/>
+      <c r="AA106" s="129"/>
+      <c r="AB106" s="129"/>
+      <c r="AC106" s="129"/>
+      <c r="AD106" s="129"/>
+      <c r="AE106" s="129"/>
+      <c r="AF106" s="129"/>
+      <c r="AG106" s="129"/>
+      <c r="AH106" s="129"/>
+      <c r="AI106" s="129"/>
+      <c r="AJ106" s="129"/>
+      <c r="AK106" s="129"/>
+      <c r="AL106" s="129"/>
+      <c r="AM106" s="129"/>
+      <c r="AN106" s="129"/>
+      <c r="AO106" s="129"/>
+      <c r="AP106" s="129"/>
+      <c r="AQ106" s="129"/>
+      <c r="AR106" s="129"/>
+      <c r="AS106" s="129"/>
+      <c r="AT106" s="129"/>
+      <c r="AU106" s="129"/>
+      <c r="AV106" s="129"/>
+      <c r="AW106" s="129"/>
+      <c r="AX106" s="129"/>
+      <c r="AY106" s="129"/>
+      <c r="AZ106" s="129"/>
+      <c r="BA106" s="129"/>
+      <c r="BB106" s="129"/>
+      <c r="BC106" s="129"/>
+      <c r="BD106" s="129"/>
+      <c r="BE106" s="129"/>
+      <c r="BF106" s="129"/>
+      <c r="BG106" s="129"/>
+      <c r="BH106" s="129"/>
+      <c r="BI106" s="129"/>
+      <c r="BJ106" s="129"/>
+      <c r="BK106" s="129"/>
+      <c r="BL106" s="129"/>
+      <c r="BM106" s="129"/>
+      <c r="BN106" s="129"/>
+      <c r="BO106" s="129"/>
+    </row>
+    <row r="107" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="56">
+        <v>3986</v>
+      </c>
+      <c r="B107" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="C107" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D106" s="51">
-        <v>1001060755931</v>
-      </c>
-      <c r="E106" s="24"/>
-      <c r="F106" s="23">
-        <v>0.22</v>
-      </c>
-      <c r="G106" s="23">
-        <f t="shared" si="16"/>
+      <c r="D107" s="57">
+        <v>1001061973986</v>
+      </c>
+      <c r="E107" s="24"/>
+      <c r="F107" s="58">
+        <v>0.25</v>
+      </c>
+      <c r="G107" s="23">
+        <f t="shared" ref="G107:G112" si="17">E107*F107</f>
         <v>0</v>
       </c>
-      <c r="H106" s="115">
-        <v>1.76</v>
-      </c>
-      <c r="I106" s="14">
+      <c r="H107" s="117">
+        <v>2</v>
+      </c>
+      <c r="I107" s="116">
         <v>120</v>
       </c>
-      <c r="J106" s="29"/>
-      <c r="L106" s="129"/>
-    </row>
-    <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="56">
-        <v>5708</v>
-      </c>
-      <c r="B107" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C107" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D107" s="51">
-        <v>1001063145708</v>
-      </c>
-      <c r="E107" s="24"/>
-      <c r="F107" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G107" s="23">
-        <f t="shared" ref="G107:G108" si="17">E107</f>
-        <v>0</v>
-      </c>
-      <c r="H107" s="14">
-        <v>4</v>
-      </c>
-      <c r="I107" s="14">
-        <v>120</v>
-      </c>
-      <c r="J107" s="29"/>
+      <c r="J107" s="59"/>
+      <c r="K107" s="60"/>
       <c r="L107" s="129"/>
+      <c r="M107" s="129"/>
+      <c r="N107" s="129"/>
+      <c r="O107" s="129"/>
+      <c r="P107" s="129"/>
+      <c r="Q107" s="129"/>
+      <c r="R107" s="129"/>
+      <c r="S107" s="129"/>
+      <c r="T107" s="129"/>
+      <c r="U107" s="129"/>
+      <c r="V107" s="129"/>
+      <c r="W107" s="129"/>
+      <c r="X107" s="129"/>
+      <c r="Y107" s="129"/>
+      <c r="Z107" s="129"/>
+      <c r="AA107" s="129"/>
+      <c r="AB107" s="129"/>
+      <c r="AC107" s="129"/>
+      <c r="AD107" s="129"/>
+      <c r="AE107" s="129"/>
+      <c r="AF107" s="129"/>
+      <c r="AG107" s="129"/>
+      <c r="AH107" s="129"/>
+      <c r="AI107" s="129"/>
+      <c r="AJ107" s="129"/>
+      <c r="AK107" s="129"/>
+      <c r="AL107" s="129"/>
+      <c r="AM107" s="129"/>
+      <c r="AN107" s="129"/>
+      <c r="AO107" s="129"/>
+      <c r="AP107" s="129"/>
+      <c r="AQ107" s="129"/>
+      <c r="AR107" s="129"/>
+      <c r="AS107" s="129"/>
+      <c r="AT107" s="129"/>
+      <c r="AU107" s="129"/>
+      <c r="AV107" s="129"/>
+      <c r="AW107" s="129"/>
+      <c r="AX107" s="129"/>
+      <c r="AY107" s="129"/>
+      <c r="AZ107" s="129"/>
+      <c r="BA107" s="129"/>
+      <c r="BB107" s="129"/>
+      <c r="BC107" s="129"/>
+      <c r="BD107" s="129"/>
+      <c r="BE107" s="129"/>
+      <c r="BF107" s="129"/>
+      <c r="BG107" s="129"/>
+      <c r="BH107" s="129"/>
+      <c r="BI107" s="129"/>
+      <c r="BJ107" s="129"/>
+      <c r="BK107" s="129"/>
+      <c r="BL107" s="129"/>
+      <c r="BM107" s="129"/>
+      <c r="BN107" s="129"/>
+      <c r="BO107" s="129"/>
     </row>
     <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="56">
-        <v>3287</v>
+        <v>5931</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D108" s="51">
-        <v>1001060763287</v>
+        <v>1001060755931</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="G108" s="23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H108" s="14">
-        <v>3.9</v>
+      <c r="H108" s="115">
+        <v>1.76</v>
       </c>
       <c r="I108" s="14">
         <v>120</v>
@@ -11061,27 +11060,27 @@
     </row>
     <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="56">
-        <v>4993</v>
+        <v>5708</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="C109" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D109" s="51">
-        <v>1001060764993</v>
+        <v>1001063145708</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G109:G110" si="18">E109</f>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -11091,27 +11090,27 @@
     </row>
     <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="56">
-        <v>5483</v>
+        <v>3287</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C110" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D110" s="51">
-        <v>1001062505483</v>
+        <v>1001060763287</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -11121,27 +11120,27 @@
     </row>
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="56">
-        <v>4117</v>
+        <v>4993</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="C111" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D111" s="51">
-        <v>1001062504117</v>
+        <v>1001060764993</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" ref="G111:G112" si="18">E111</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I111" s="14">
         <v>120</v>
@@ -11151,27 +11150,27 @@
     </row>
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="56">
-        <v>614</v>
+        <v>5483</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="C112" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D112" s="51">
-        <v>1001060720614</v>
+        <v>1001062505483</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H112" s="14">
-        <v>3.64</v>
+        <v>2</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -11181,27 +11180,27 @@
     </row>
     <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="56">
-        <v>6967</v>
+        <v>4117</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C113" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D113" s="51">
-        <v>1001063656967</v>
+        <v>1001062504117</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.25</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" ref="G113:G122" si="19">E113*F113</f>
+        <f t="shared" ref="G113:G114" si="19">E113</f>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -11211,27 +11210,27 @@
     </row>
     <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="56">
-        <v>6937</v>
+        <v>614</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C114" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D114" s="51">
-        <v>1001063106937</v>
+        <v>1001060720614</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G114" s="23">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -11241,27 +11240,27 @@
     </row>
     <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="56">
-        <v>7143</v>
+        <v>6967</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D115" s="51">
-        <v>1001060717143</v>
+        <v>1001063656967</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G115:G124" si="20">E115*F115</f>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I115" s="14">
         <v>120</v>
@@ -11271,27 +11270,27 @@
     </row>
     <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="56">
-        <v>7147</v>
+        <v>6937</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D116" s="51">
-        <v>1001063237147</v>
+        <v>1001063106937</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I116" s="14">
         <v>120</v>
@@ -11301,87 +11300,87 @@
     </row>
     <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="56">
-        <v>7456</v>
+        <v>7143</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D117" s="51">
-        <v>1001063097456</v>
+        <v>1001060717143</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I117" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J117" s="29"/>
       <c r="L117" s="129"/>
     </row>
     <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="56">
-        <v>7364</v>
+        <v>7147</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D118" s="51">
-        <v>1001063217364</v>
+        <v>1001063237147</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
         <v>0.22</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
         <v>1.76</v>
       </c>
       <c r="I118" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J118" s="29"/>
       <c r="L118" s="129"/>
     </row>
     <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="56">
-        <v>7383</v>
+        <v>7456</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="51">
-        <v>1001065467383</v>
+        <v>1001063097456</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I119" s="14">
         <v>90</v>
@@ -11391,83 +11390,83 @@
     </row>
     <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="56">
-        <v>7317</v>
+        <v>7364</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="51">
-        <v>1001066567317</v>
+        <v>1001063217364</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I120" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J120" s="29"/>
       <c r="L120" s="129"/>
     </row>
     <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="56">
-        <v>7318</v>
+        <v>7383</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D121" s="51">
-        <v>1001060727318</v>
+        <v>1001065467383</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="I121" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J121" s="29"/>
       <c r="L121" s="129"/>
     </row>
     <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="56">
-        <v>7316</v>
+        <v>7317</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D122" s="51">
-        <v>1001060727316</v>
+        <v>1001066567317</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
         <v>0.54</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
@@ -11481,243 +11480,241 @@
     </row>
     <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="56">
-        <v>6832</v>
+        <v>7318</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D123" s="51">
-        <v>1001065616832</v>
+        <v>1001060727318</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.215</v>
+        <v>0.27</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" ref="G123:G124" si="20">E123</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="I123" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J123" s="29"/>
       <c r="L123" s="129"/>
     </row>
     <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="56">
-        <v>7299</v>
+        <v>7316</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D124" s="51">
-        <v>1001060677299</v>
+        <v>1001060727316</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G124" s="23">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I124" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J124" s="29"/>
       <c r="L124" s="129"/>
     </row>
     <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="56">
-        <v>7386</v>
+        <v>6832</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D125" s="51">
-        <v>1001067017386</v>
+        <v>1001065616832</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G125" s="23">
-        <f t="shared" ref="G125:G135" si="21">E125*F125</f>
+        <f t="shared" ref="G125:G126" si="21">E125</f>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I125" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J125" s="29"/>
       <c r="L125" s="129"/>
     </row>
     <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="133">
-        <v>7613</v>
+      <c r="A126" s="56">
+        <v>7299</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D126" s="51">
-        <v>1001061977613</v>
+        <v>1001060677299</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.1</v>
+        <v>0.215</v>
       </c>
       <c r="G126" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>1</v>
+        <v>2.15</v>
       </c>
       <c r="I126" s="14">
-        <v>60</v>
-      </c>
-      <c r="J126" s="52" t="s">
-        <v>215</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J126" s="29"/>
       <c r="L126" s="129"/>
     </row>
     <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="135">
-        <v>6834</v>
-      </c>
-      <c r="B127" s="136" t="s">
-        <v>149</v>
-      </c>
-      <c r="C127" s="137" t="s">
+      <c r="A127" s="56">
+        <v>7386</v>
+      </c>
+      <c r="B127" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C127" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D127" s="138">
-        <v>1001203146834</v>
-      </c>
-      <c r="E127" s="139"/>
-      <c r="F127" s="140">
-        <v>0.1</v>
-      </c>
-      <c r="G127" s="140">
-        <f t="shared" si="21"/>
+      <c r="D127" s="51">
+        <v>1001067017386</v>
+      </c>
+      <c r="E127" s="24"/>
+      <c r="F127" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G127" s="23">
+        <f t="shared" ref="G127:G137" si="22">E127*F127</f>
         <v>0</v>
       </c>
-      <c r="H127" s="141">
-        <v>1</v>
-      </c>
-      <c r="I127" s="141">
-        <v>60</v>
-      </c>
-      <c r="J127" s="141" t="s">
-        <v>214</v>
-      </c>
+      <c r="H127" s="14">
+        <v>1.35</v>
+      </c>
+      <c r="I127" s="14">
+        <v>90</v>
+      </c>
+      <c r="J127" s="29"/>
       <c r="L127" s="129"/>
     </row>
     <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="56">
-        <v>7382</v>
+      <c r="A128" s="133">
+        <v>7613</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>85</v>
+        <v>223</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D128" s="51">
-        <v>1001203117382</v>
+        <v>1001061977613</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G128" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I128" s="14">
         <v>60</v>
       </c>
-      <c r="J128" s="29"/>
+      <c r="J128" s="52" t="s">
+        <v>215</v>
+      </c>
       <c r="L128" s="129"/>
     </row>
     <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="133">
-        <v>7616</v>
-      </c>
-      <c r="B129" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="C129" s="50" t="s">
+      <c r="A129" s="135">
+        <v>6834</v>
+      </c>
+      <c r="B129" s="136" t="s">
+        <v>149</v>
+      </c>
+      <c r="C129" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="D129" s="51">
-        <v>1001062507616</v>
-      </c>
-      <c r="E129" s="24"/>
-      <c r="F129" s="23">
+      <c r="D129" s="138">
+        <v>1001203146834</v>
+      </c>
+      <c r="E129" s="139"/>
+      <c r="F129" s="140">
         <v>0.1</v>
       </c>
-      <c r="G129" s="23">
-        <f t="shared" si="21"/>
+      <c r="G129" s="140">
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H129" s="14">
-        <v>1.4</v>
-      </c>
-      <c r="I129" s="14">
+      <c r="H129" s="141">
+        <v>1</v>
+      </c>
+      <c r="I129" s="141">
         <v>60</v>
       </c>
-      <c r="J129" s="52" t="s">
-        <v>216</v>
+      <c r="J129" s="141" t="s">
+        <v>214</v>
       </c>
       <c r="L129" s="129"/>
     </row>
     <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="56">
-        <v>6221</v>
+        <v>7382</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D130" s="51">
-        <v>1001205376221</v>
+        <v>1001203117382</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G130" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="I130" s="14">
         <v>60</v>
@@ -11726,58 +11723,60 @@
       <c r="L130" s="129"/>
     </row>
     <row r="131" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="56">
-        <v>6222</v>
+      <c r="A131" s="133">
+        <v>7616</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>153</v>
+        <v>219</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="51">
-        <v>1001205386222</v>
+        <v>1001062507616</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G131" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H131" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I131" s="14">
         <v>60</v>
       </c>
-      <c r="J131" s="29"/>
+      <c r="J131" s="52" t="s">
+        <v>216</v>
+      </c>
       <c r="L131" s="129"/>
     </row>
     <row r="132" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="56">
-        <v>6965</v>
+        <v>6221</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D132" s="51">
-        <v>1001206356965</v>
+        <v>1001205376221</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
@@ -11787,27 +11786,27 @@
     </row>
     <row r="133" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="56">
-        <v>6557</v>
+        <v>6222</v>
       </c>
       <c r="B133" s="53" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C133" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D133" s="51">
-        <v>1001200756557</v>
+        <v>1001205386222</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H133" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I133" s="14">
         <v>60</v>
@@ -11817,27 +11816,27 @@
     </row>
     <row r="134" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="56">
-        <v>5679</v>
+        <v>6965</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D134" s="51">
-        <v>1001190765679</v>
+        <v>1001206356965</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
-        <v>0.15</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H134" s="14">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="I134" s="14">
         <v>60</v>
@@ -11845,25 +11844,25 @@
       <c r="J134" s="29"/>
       <c r="L134" s="129"/>
     </row>
-    <row r="135" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="133">
-        <v>7626</v>
+    <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="56">
+        <v>6557</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>218</v>
+        <v>155</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D135" s="51">
-        <v>1001066607626</v>
+        <v>1001200756557</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="23">
         <v>0.1</v>
       </c>
       <c r="G135" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H135" s="14">
@@ -11872,256 +11871,144 @@
       <c r="I135" s="14">
         <v>60</v>
       </c>
-      <c r="J135" s="52" t="s">
-        <v>217</v>
-      </c>
+      <c r="J135" s="29"/>
       <c r="L135" s="129"/>
     </row>
-    <row r="136" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="B136" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C136" s="42"/>
-      <c r="D136" s="42"/>
-      <c r="E136" s="42"/>
-      <c r="F136" s="41"/>
-      <c r="G136" s="42"/>
-      <c r="H136" s="42"/>
-      <c r="I136" s="42"/>
-      <c r="J136" s="43"/>
+    <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="56">
+        <v>5679</v>
+      </c>
+      <c r="B136" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="C136" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D136" s="51">
+        <v>1001190765679</v>
+      </c>
+      <c r="E136" s="24"/>
+      <c r="F136" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G136" s="23">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="H136" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I136" s="14">
+        <v>60</v>
+      </c>
+      <c r="J136" s="29"/>
       <c r="L136" s="129"/>
     </row>
-    <row r="137" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="56">
-        <v>4584</v>
-      </c>
-      <c r="B137" s="121" t="s">
-        <v>125</v>
+    <row r="137" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="133">
+        <v>7626</v>
+      </c>
+      <c r="B137" s="53" t="s">
+        <v>218</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D137" s="120">
-        <v>1001092674584</v>
+        <v>21</v>
+      </c>
+      <c r="D137" s="51">
+        <v>1001066607626</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="G137" s="23">
-        <f>E137</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
       </c>
-      <c r="J137" s="29"/>
+      <c r="J137" s="52" t="s">
+        <v>217</v>
+      </c>
       <c r="L137" s="129"/>
     </row>
-    <row r="138" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="56">
-        <v>6495</v>
-      </c>
-      <c r="B138" s="122" t="s">
-        <v>97</v>
-      </c>
-      <c r="C138" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D138" s="70">
-        <v>1001092436495</v>
-      </c>
-      <c r="E138" s="24"/>
-      <c r="F138" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="G138" s="23">
-        <f>E138*F138</f>
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B138" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C138" s="42"/>
+      <c r="D138" s="42"/>
+      <c r="E138" s="42"/>
+      <c r="F138" s="41"/>
+      <c r="G138" s="42"/>
+      <c r="H138" s="42"/>
+      <c r="I138" s="42"/>
+      <c r="J138" s="43"/>
+      <c r="L138" s="129"/>
+    </row>
+    <row r="139" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="56">
+        <v>4584</v>
+      </c>
+      <c r="B139" s="121" t="s">
+        <v>125</v>
+      </c>
+      <c r="C139" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D139" s="120">
+        <v>1001092674584</v>
+      </c>
+      <c r="E139" s="24"/>
+      <c r="F139" s="23">
+        <v>2.5</v>
+      </c>
+      <c r="G139" s="23">
+        <f>E139</f>
         <v>0</v>
       </c>
-      <c r="H138" s="59">
-        <v>1.8</v>
-      </c>
-      <c r="I138" s="59">
-        <v>45</v>
-      </c>
-      <c r="J138" s="59"/>
-      <c r="K138" s="60"/>
-      <c r="L138" s="129"/>
-      <c r="M138" s="129"/>
-      <c r="N138" s="129"/>
-      <c r="O138" s="129"/>
-      <c r="P138" s="129"/>
-      <c r="Q138" s="129"/>
-      <c r="R138" s="129"/>
-      <c r="S138" s="129"/>
-      <c r="T138" s="129"/>
-      <c r="U138" s="129"/>
-      <c r="V138" s="129"/>
-      <c r="W138" s="129"/>
-      <c r="X138" s="129"/>
-      <c r="Y138" s="129"/>
-      <c r="Z138" s="129"/>
-      <c r="AA138" s="129"/>
-      <c r="AB138" s="129"/>
-      <c r="AC138" s="129"/>
-      <c r="AD138" s="129"/>
-      <c r="AE138" s="129"/>
-      <c r="AF138" s="129"/>
-      <c r="AG138" s="129"/>
-      <c r="AH138" s="129"/>
-      <c r="AI138" s="129"/>
-      <c r="AJ138" s="129"/>
-      <c r="AK138" s="129"/>
-      <c r="AL138" s="129"/>
-      <c r="AM138" s="129"/>
-      <c r="AN138" s="129"/>
-      <c r="AO138" s="129"/>
-      <c r="AP138" s="129"/>
-      <c r="AQ138" s="129"/>
-      <c r="AR138" s="129"/>
-      <c r="AS138" s="129"/>
-      <c r="AT138" s="129"/>
-      <c r="AU138" s="129"/>
-      <c r="AV138" s="129"/>
-      <c r="AW138" s="129"/>
-      <c r="AX138" s="129"/>
-      <c r="AY138" s="129"/>
-      <c r="AZ138" s="129"/>
-      <c r="BA138" s="129"/>
-      <c r="BB138" s="129"/>
-      <c r="BC138" s="129"/>
-      <c r="BD138" s="129"/>
-      <c r="BE138" s="129"/>
-      <c r="BF138" s="129"/>
-      <c r="BG138" s="129"/>
-      <c r="BH138" s="129"/>
-      <c r="BI138" s="129"/>
-      <c r="BJ138" s="129"/>
-      <c r="BK138" s="129"/>
-      <c r="BL138" s="129"/>
-      <c r="BM138" s="129"/>
-      <c r="BN138" s="129"/>
-      <c r="BO138" s="129"/>
-    </row>
-    <row r="139" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="56">
-        <v>6470</v>
-      </c>
-      <c r="B139" s="118" t="s">
-        <v>126</v>
-      </c>
-      <c r="C139" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D139" s="70">
-        <v>1001092436470</v>
-      </c>
-      <c r="E139" s="24"/>
-      <c r="F139" s="58">
-        <v>1.2</v>
-      </c>
-      <c r="G139" s="23">
-        <f t="shared" ref="G139:G140" si="22">E139</f>
-        <v>0</v>
-      </c>
-      <c r="H139" s="59">
-        <v>4.8</v>
-      </c>
-      <c r="I139" s="59">
-        <v>45</v>
-      </c>
-      <c r="J139" s="59"/>
-      <c r="K139" s="60"/>
+      <c r="H139" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I139" s="14">
+        <v>60</v>
+      </c>
+      <c r="J139" s="29"/>
       <c r="L139" s="129"/>
-      <c r="M139" s="129"/>
-      <c r="N139" s="129"/>
-      <c r="O139" s="129"/>
-      <c r="P139" s="129"/>
-      <c r="Q139" s="129"/>
-      <c r="R139" s="129"/>
-      <c r="S139" s="129"/>
-      <c r="T139" s="129"/>
-      <c r="U139" s="129"/>
-      <c r="V139" s="129"/>
-      <c r="W139" s="129"/>
-      <c r="X139" s="129"/>
-      <c r="Y139" s="129"/>
-      <c r="Z139" s="129"/>
-      <c r="AA139" s="129"/>
-      <c r="AB139" s="129"/>
-      <c r="AC139" s="129"/>
-      <c r="AD139" s="129"/>
-      <c r="AE139" s="129"/>
-      <c r="AF139" s="129"/>
-      <c r="AG139" s="129"/>
-      <c r="AH139" s="129"/>
-      <c r="AI139" s="129"/>
-      <c r="AJ139" s="129"/>
-      <c r="AK139" s="129"/>
-      <c r="AL139" s="129"/>
-      <c r="AM139" s="129"/>
-      <c r="AN139" s="129"/>
-      <c r="AO139" s="129"/>
-      <c r="AP139" s="129"/>
-      <c r="AQ139" s="129"/>
-      <c r="AR139" s="129"/>
-      <c r="AS139" s="129"/>
-      <c r="AT139" s="129"/>
-      <c r="AU139" s="129"/>
-      <c r="AV139" s="129"/>
-      <c r="AW139" s="129"/>
-      <c r="AX139" s="129"/>
-      <c r="AY139" s="129"/>
-      <c r="AZ139" s="129"/>
-      <c r="BA139" s="129"/>
-      <c r="BB139" s="129"/>
-      <c r="BC139" s="129"/>
-      <c r="BD139" s="129"/>
-      <c r="BE139" s="129"/>
-      <c r="BF139" s="129"/>
-      <c r="BG139" s="129"/>
-      <c r="BH139" s="129"/>
-      <c r="BI139" s="129"/>
-      <c r="BJ139" s="129"/>
-      <c r="BK139" s="129"/>
-      <c r="BL139" s="129"/>
-      <c r="BM139" s="129"/>
-      <c r="BN139" s="129"/>
-      <c r="BO139" s="129"/>
     </row>
     <row r="140" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="56">
-        <v>5452</v>
-      </c>
-      <c r="B140" s="118" t="s">
-        <v>95</v>
+        <v>6495</v>
+      </c>
+      <c r="B140" s="122" t="s">
+        <v>97</v>
       </c>
       <c r="C140" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D140" s="70">
-        <v>1001092485452</v>
+        <v>1001092436495</v>
       </c>
       <c r="E140" s="24"/>
       <c r="F140" s="58">
-        <v>1.35</v>
+        <v>0.3</v>
       </c>
       <c r="G140" s="23">
-        <f t="shared" si="22"/>
+        <f>E140*F140</f>
         <v>0</v>
       </c>
       <c r="H140" s="59">
-        <v>4.05</v>
+        <v>1.8</v>
       </c>
       <c r="I140" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J140" s="59"/>
       <c r="K140" s="60"/>
@@ -12184,30 +12071,30 @@
     </row>
     <row r="141" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="56">
-        <v>3215</v>
+        <v>6470</v>
       </c>
       <c r="B141" s="118" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="C141" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D141" s="70">
-        <v>1001094053215</v>
+        <v>1001092436470</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="58">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G141" s="23">
-        <f>E141*F141</f>
+        <f t="shared" ref="G141:G142" si="23">E141</f>
         <v>0</v>
       </c>
       <c r="H141" s="59">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="I141" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J141" s="59"/>
       <c r="K141" s="60"/>
@@ -12270,27 +12157,27 @@
     </row>
     <row r="142" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="56">
-        <v>6866</v>
+        <v>5452</v>
       </c>
       <c r="B142" s="118" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C142" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D142" s="70">
-        <v>1001095716866</v>
+        <v>1001092485452</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="58">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="G142" s="23">
-        <f>E142</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H142" s="59">
-        <v>6</v>
+        <v>4.05</v>
       </c>
       <c r="I142" s="59">
         <v>60</v>
@@ -12354,29 +12241,29 @@
       <c r="BN142" s="129"/>
       <c r="BO142" s="129"/>
     </row>
-    <row r="143" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="56">
-        <v>5495</v>
-      </c>
-      <c r="B143" s="54" t="s">
-        <v>96</v>
+        <v>3215</v>
+      </c>
+      <c r="B143" s="118" t="s">
+        <v>94</v>
       </c>
       <c r="C143" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D143" s="119">
-        <v>1001093345495</v>
+      <c r="D143" s="70">
+        <v>1001094053215</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="58">
         <v>0.4</v>
       </c>
       <c r="G143" s="23">
-        <f t="shared" ref="G143:G145" si="23">E143*F143</f>
+        <f>E143*F143</f>
         <v>0</v>
       </c>
       <c r="H143" s="59">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="I143" s="59">
         <v>60</v>
@@ -12440,32 +12327,32 @@
       <c r="BN143" s="129"/>
       <c r="BO143" s="129"/>
     </row>
-    <row r="144" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="56">
-        <v>7377</v>
-      </c>
-      <c r="B144" s="54" t="s">
-        <v>127</v>
+        <v>6866</v>
+      </c>
+      <c r="B144" s="118" t="s">
+        <v>93</v>
       </c>
       <c r="C144" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D144" s="119">
-        <v>1001095027377</v>
+        <v>23</v>
+      </c>
+      <c r="D144" s="70">
+        <v>1001095716866</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="58">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" si="23"/>
+        <f>E144</f>
         <v>0</v>
       </c>
       <c r="H144" s="59">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="I144" s="59">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J144" s="59"/>
       <c r="K144" s="60"/>
@@ -12528,30 +12415,30 @@
     </row>
     <row r="145" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="56">
-        <v>6925</v>
+        <v>5495</v>
       </c>
       <c r="B145" s="54" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C145" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D145" s="119">
-        <v>1001095226925</v>
+        <v>1001093345495</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="58">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G145:G147" si="24">E145*F145</f>
         <v>0</v>
       </c>
       <c r="H145" s="59">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I145" s="59">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J145" s="59"/>
       <c r="K145" s="60"/>
@@ -12612,32 +12499,32 @@
       <c r="BN145" s="129"/>
       <c r="BO145" s="129"/>
     </row>
-    <row r="146" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="56">
-        <v>6025</v>
+        <v>7377</v>
       </c>
       <c r="B146" s="54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C146" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D146" s="119">
-        <v>1001094966025</v>
+        <v>1001095027377</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="58">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="G146" s="23">
-        <f>E146</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H146" s="59">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="I146" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J146" s="59"/>
       <c r="K146" s="60"/>
@@ -12698,36 +12585,34 @@
       <c r="BN146" s="129"/>
       <c r="BO146" s="129"/>
     </row>
-    <row r="147" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="133">
-        <v>7647</v>
+    <row r="147" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="56">
+        <v>6925</v>
       </c>
       <c r="B147" s="54" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="C147" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D147" s="119">
-        <v>1001097747647</v>
+        <v>1001095226925</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="58">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G147" s="23">
-        <f>E147*F147</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H147" s="59">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="I147" s="59">
-        <v>30</v>
-      </c>
-      <c r="J147" s="132" t="s">
-        <v>208</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J147" s="59"/>
       <c r="K147" s="60"/>
       <c r="L147" s="129"/>
       <c r="M147" s="129"/>
@@ -12786,36 +12671,34 @@
       <c r="BN147" s="129"/>
       <c r="BO147" s="129"/>
     </row>
-    <row r="148" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="133">
-        <v>7651</v>
+    <row r="148" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="56">
+        <v>6025</v>
       </c>
       <c r="B148" s="54" t="s">
-        <v>207</v>
+        <v>128</v>
       </c>
       <c r="C148" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D148" s="119">
-        <v>1001097767651</v>
+        <v>1001094966025</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="58">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="G148" s="23">
-        <f>E148*F148</f>
+        <f>E148</f>
         <v>0</v>
       </c>
       <c r="H148" s="59">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I148" s="59">
-        <v>30</v>
-      </c>
-      <c r="J148" s="132" t="s">
-        <v>208</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J148" s="59"/>
       <c r="K148" s="60"/>
       <c r="L148" s="129"/>
       <c r="M148" s="129"/>
@@ -12874,288 +12757,404 @@
       <c r="BN148" s="129"/>
       <c r="BO148" s="129"/>
     </row>
-    <row r="149" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="47" t="s">
+    <row r="149" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="133">
+        <v>7647</v>
+      </c>
+      <c r="B149" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C149" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149" s="119">
+        <v>1001097747647</v>
+      </c>
+      <c r="E149" s="24"/>
+      <c r="F149" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G149" s="23">
+        <f>E149*F149</f>
+        <v>0</v>
+      </c>
+      <c r="H149" s="59">
+        <v>1</v>
+      </c>
+      <c r="I149" s="59">
+        <v>30</v>
+      </c>
+      <c r="J149" s="132" t="s">
+        <v>208</v>
+      </c>
+      <c r="K149" s="60"/>
+      <c r="L149" s="129"/>
+      <c r="M149" s="129"/>
+      <c r="N149" s="129"/>
+      <c r="O149" s="129"/>
+      <c r="P149" s="129"/>
+      <c r="Q149" s="129"/>
+      <c r="R149" s="129"/>
+      <c r="S149" s="129"/>
+      <c r="T149" s="129"/>
+      <c r="U149" s="129"/>
+      <c r="V149" s="129"/>
+      <c r="W149" s="129"/>
+      <c r="X149" s="129"/>
+      <c r="Y149" s="129"/>
+      <c r="Z149" s="129"/>
+      <c r="AA149" s="129"/>
+      <c r="AB149" s="129"/>
+      <c r="AC149" s="129"/>
+      <c r="AD149" s="129"/>
+      <c r="AE149" s="129"/>
+      <c r="AF149" s="129"/>
+      <c r="AG149" s="129"/>
+      <c r="AH149" s="129"/>
+      <c r="AI149" s="129"/>
+      <c r="AJ149" s="129"/>
+      <c r="AK149" s="129"/>
+      <c r="AL149" s="129"/>
+      <c r="AM149" s="129"/>
+      <c r="AN149" s="129"/>
+      <c r="AO149" s="129"/>
+      <c r="AP149" s="129"/>
+      <c r="AQ149" s="129"/>
+      <c r="AR149" s="129"/>
+      <c r="AS149" s="129"/>
+      <c r="AT149" s="129"/>
+      <c r="AU149" s="129"/>
+      <c r="AV149" s="129"/>
+      <c r="AW149" s="129"/>
+      <c r="AX149" s="129"/>
+      <c r="AY149" s="129"/>
+      <c r="AZ149" s="129"/>
+      <c r="BA149" s="129"/>
+      <c r="BB149" s="129"/>
+      <c r="BC149" s="129"/>
+      <c r="BD149" s="129"/>
+      <c r="BE149" s="129"/>
+      <c r="BF149" s="129"/>
+      <c r="BG149" s="129"/>
+      <c r="BH149" s="129"/>
+      <c r="BI149" s="129"/>
+      <c r="BJ149" s="129"/>
+      <c r="BK149" s="129"/>
+      <c r="BL149" s="129"/>
+      <c r="BM149" s="129"/>
+      <c r="BN149" s="129"/>
+      <c r="BO149" s="129"/>
+    </row>
+    <row r="150" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="133">
+        <v>7651</v>
+      </c>
+      <c r="B150" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="C150" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="119">
+        <v>1001097767651</v>
+      </c>
+      <c r="E150" s="24"/>
+      <c r="F150" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G150" s="23">
+        <f>E150*F150</f>
+        <v>0</v>
+      </c>
+      <c r="H150" s="59">
+        <v>1</v>
+      </c>
+      <c r="I150" s="59">
+        <v>30</v>
+      </c>
+      <c r="J150" s="132" t="s">
+        <v>208</v>
+      </c>
+      <c r="K150" s="60"/>
+      <c r="L150" s="129"/>
+      <c r="M150" s="129"/>
+      <c r="N150" s="129"/>
+      <c r="O150" s="129"/>
+      <c r="P150" s="129"/>
+      <c r="Q150" s="129"/>
+      <c r="R150" s="129"/>
+      <c r="S150" s="129"/>
+      <c r="T150" s="129"/>
+      <c r="U150" s="129"/>
+      <c r="V150" s="129"/>
+      <c r="W150" s="129"/>
+      <c r="X150" s="129"/>
+      <c r="Y150" s="129"/>
+      <c r="Z150" s="129"/>
+      <c r="AA150" s="129"/>
+      <c r="AB150" s="129"/>
+      <c r="AC150" s="129"/>
+      <c r="AD150" s="129"/>
+      <c r="AE150" s="129"/>
+      <c r="AF150" s="129"/>
+      <c r="AG150" s="129"/>
+      <c r="AH150" s="129"/>
+      <c r="AI150" s="129"/>
+      <c r="AJ150" s="129"/>
+      <c r="AK150" s="129"/>
+      <c r="AL150" s="129"/>
+      <c r="AM150" s="129"/>
+      <c r="AN150" s="129"/>
+      <c r="AO150" s="129"/>
+      <c r="AP150" s="129"/>
+      <c r="AQ150" s="129"/>
+      <c r="AR150" s="129"/>
+      <c r="AS150" s="129"/>
+      <c r="AT150" s="129"/>
+      <c r="AU150" s="129"/>
+      <c r="AV150" s="129"/>
+      <c r="AW150" s="129"/>
+      <c r="AX150" s="129"/>
+      <c r="AY150" s="129"/>
+      <c r="AZ150" s="129"/>
+      <c r="BA150" s="129"/>
+      <c r="BB150" s="129"/>
+      <c r="BC150" s="129"/>
+      <c r="BD150" s="129"/>
+      <c r="BE150" s="129"/>
+      <c r="BF150" s="129"/>
+      <c r="BG150" s="129"/>
+      <c r="BH150" s="129"/>
+      <c r="BI150" s="129"/>
+      <c r="BJ150" s="129"/>
+      <c r="BK150" s="129"/>
+      <c r="BL150" s="129"/>
+      <c r="BM150" s="129"/>
+      <c r="BN150" s="129"/>
+      <c r="BO150" s="129"/>
+    </row>
+    <row r="151" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B149" s="42" t="s">
+      <c r="B151" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C149" s="42"/>
-      <c r="D149" s="42"/>
-      <c r="E149" s="42"/>
-      <c r="F149" s="41"/>
-      <c r="G149" s="42"/>
-      <c r="H149" s="42"/>
-      <c r="I149" s="42"/>
-      <c r="J149" s="43"/>
-      <c r="L149" s="129"/>
-    </row>
-    <row r="150" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="56">
+      <c r="C151" s="42"/>
+      <c r="D151" s="42"/>
+      <c r="E151" s="42"/>
+      <c r="F151" s="41"/>
+      <c r="G151" s="42"/>
+      <c r="H151" s="42"/>
+      <c r="I151" s="42"/>
+      <c r="J151" s="43"/>
+      <c r="L151" s="129"/>
+    </row>
+    <row r="152" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="56">
         <v>7090</v>
       </c>
-      <c r="B150" s="35" t="s">
+      <c r="B152" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C150" s="50" t="s">
+      <c r="C152" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D150" s="51">
+      <c r="D152" s="51">
         <v>1001084217090</v>
-      </c>
-      <c r="E150" s="24"/>
-      <c r="F150" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G150" s="23">
-        <f t="shared" ref="G150:G152" si="24">E150*F150</f>
-        <v>0</v>
-      </c>
-      <c r="H150" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I150" s="14">
-        <v>50</v>
-      </c>
-      <c r="J150" s="29"/>
-      <c r="L150" s="129"/>
-    </row>
-    <row r="151" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="56">
-        <v>7187</v>
-      </c>
-      <c r="B151" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C151" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D151" s="51">
-        <v>1001085637187</v>
-      </c>
-      <c r="E151" s="24"/>
-      <c r="F151" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G151" s="23">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="H151" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I151" s="14">
-        <v>50</v>
-      </c>
-      <c r="J151" s="29"/>
-      <c r="L151" s="129"/>
-    </row>
-    <row r="152" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="133">
-        <v>6008</v>
-      </c>
-      <c r="B152" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="C152" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D152" s="51">
-        <v>1001084856008</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
         <v>0.3</v>
       </c>
       <c r="G152" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G152:G153" si="25">E152*F152</f>
         <v>0</v>
       </c>
       <c r="H152" s="14">
         <v>1.8</v>
       </c>
       <c r="I152" s="14">
-        <v>40</v>
-      </c>
-      <c r="J152" s="132" t="s">
-        <v>208</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J152" s="29"/>
       <c r="L152" s="129"/>
     </row>
     <row r="153" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="56">
-        <v>6620</v>
+        <v>7187</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D153" s="51">
-        <v>1001081596620</v>
+        <v>1001085637187</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G153" s="23">
-        <f>E153</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H153" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I153" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J153" s="29"/>
       <c r="L153" s="129"/>
     </row>
     <row r="154" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="56">
-        <v>7103</v>
+      <c r="A154" s="133">
+        <v>6008</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D154" s="51">
-        <v>1001223297103</v>
+        <v>1001084856008</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" ref="G154:G161" si="25">E154*F154</f>
+        <f>E154</f>
         <v>0</v>
       </c>
       <c r="H154" s="14">
         <v>1.8</v>
       </c>
       <c r="I154" s="14">
-        <v>50</v>
-      </c>
-      <c r="J154" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J154" s="132" t="s">
+        <v>208</v>
+      </c>
       <c r="L154" s="129"/>
     </row>
     <row r="155" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="56">
-        <v>7092</v>
+        <v>6620</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D155" s="51">
-        <v>1001223297092</v>
+        <v>1001081596620</v>
       </c>
       <c r="E155" s="24"/>
       <c r="F155" s="23">
-        <v>0.14000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="G155" s="23">
-        <f t="shared" si="25"/>
+        <f>E155</f>
         <v>0</v>
       </c>
       <c r="H155" s="14">
-        <v>1.4</v>
+        <v>3.15</v>
       </c>
       <c r="I155" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J155" s="29"/>
       <c r="L155" s="129"/>
     </row>
     <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="56">
-        <v>6228</v>
+        <v>7103</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D156" s="51">
-        <v>1001225416228</v>
+        <v>1001223297103</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="G156" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G156:G163" si="26">E156*F156</f>
         <v>0</v>
       </c>
       <c r="H156" s="14">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="I156" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J156" s="29"/>
       <c r="L156" s="129"/>
     </row>
     <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="56">
-        <v>6448</v>
+        <v>7092</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D157" s="51">
-        <v>1001234146448</v>
+        <v>1001223297092</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I157" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J157" s="29"/>
       <c r="L157" s="129"/>
     </row>
     <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="56">
-        <v>6208</v>
+        <v>6228</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001220226208</v>
+        <v>1001225416228</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G158" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I158" s="14">
         <v>45</v>
@@ -13165,57 +13164,57 @@
     </row>
     <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="56">
-        <v>6754</v>
+        <v>6448</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D159" s="51">
-        <v>1001225406754</v>
+        <v>1001234146448</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G159" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I159" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J159" s="29"/>
       <c r="L159" s="129"/>
     </row>
     <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="56">
-        <v>6279</v>
+        <v>6208</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D160" s="51">
-        <v>1001220286279</v>
+        <v>1001220226208</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
         <v>0.15</v>
       </c>
       <c r="G160" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -13223,79 +13222,119 @@
       <c r="J160" s="29"/>
       <c r="L160" s="129"/>
     </row>
-    <row r="161" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="133">
-        <v>7612</v>
+    <row r="161" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="56">
+        <v>6754</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D161" s="51">
-        <v>1001453907612</v>
+        <v>1001225406754</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G161" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="I161" s="14">
         <v>60</v>
       </c>
-      <c r="J161" s="52" t="s">
+      <c r="J161" s="29"/>
+      <c r="L161" s="129"/>
+    </row>
+    <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="56">
+        <v>6279</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C162" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162" s="51">
+        <v>1001220286279</v>
+      </c>
+      <c r="E162" s="24"/>
+      <c r="F162" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G162" s="23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H162" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I162" s="14">
+        <v>45</v>
+      </c>
+      <c r="J162" s="29"/>
+      <c r="L162" s="129"/>
+    </row>
+    <row r="163" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="133">
+        <v>7612</v>
+      </c>
+      <c r="B163" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C163" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E163" s="24"/>
+      <c r="F163" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G163" s="23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H163" s="14">
+        <v>1</v>
+      </c>
+      <c r="I163" s="14">
+        <v>60</v>
+      </c>
+      <c r="J163" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="L161" s="129"/>
-    </row>
-    <row r="162" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="48"/>
-      <c r="B162" s="45" t="s">
+      <c r="L163" s="129"/>
+    </row>
+    <row r="164" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="48"/>
+      <c r="B164" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C162" s="16"/>
-      <c r="D162" s="36"/>
-      <c r="E162" s="17">
-        <f>SUM(E10:E161)</f>
+      <c r="C164" s="16"/>
+      <c r="D164" s="36"/>
+      <c r="E164" s="17">
+        <f>SUM(E10:E163)</f>
         <v>0</v>
       </c>
-      <c r="F162" s="17"/>
-      <c r="G162" s="17">
-        <f>SUM(G11:G161)</f>
+      <c r="F164" s="17"/>
+      <c r="G164" s="17">
+        <f>SUM(G11:G163)</f>
         <v>0</v>
       </c>
-      <c r="H162" s="17"/>
-      <c r="I162" s="17"/>
-      <c r="J162" s="17"/>
-    </row>
-    <row r="163" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="37"/>
-      <c r="C163" s="18"/>
-      <c r="D163" s="40"/>
-      <c r="F163" s="19"/>
-      <c r="G163" s="19"/>
-      <c r="H163" s="20"/>
-      <c r="I163" s="20"/>
-      <c r="J163" s="21"/>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B164" s="37"/>
-      <c r="C164" s="18"/>
-      <c r="D164" s="40"/>
-      <c r="F164" s="19"/>
-      <c r="G164" s="19"/>
-      <c r="H164" s="20"/>
-      <c r="I164" s="20"/>
-      <c r="J164" s="21"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H164" s="17"/>
+      <c r="I164" s="17"/>
+      <c r="J164" s="17"/>
+    </row>
+    <row r="165" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B165" s="37"/>
       <c r="C165" s="18"/>
       <c r="D165" s="40"/>
@@ -13337,55 +13376,55 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B169" s="37"/>
-      <c r="C169" s="62"/>
-      <c r="D169" s="63"/>
-      <c r="E169" s="64"/>
-      <c r="F169" s="65"/>
-      <c r="G169" s="65"/>
-      <c r="H169" s="66"/>
-      <c r="I169" s="66"/>
+      <c r="C169" s="18"/>
+      <c r="D169" s="40"/>
+      <c r="F169" s="19"/>
+      <c r="G169" s="19"/>
+      <c r="H169" s="20"/>
+      <c r="I169" s="20"/>
       <c r="J169" s="21"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B170" s="37"/>
-      <c r="C170" s="62"/>
-      <c r="D170" s="63"/>
-      <c r="E170" s="64"/>
-      <c r="F170" s="65"/>
-      <c r="G170" s="65"/>
-      <c r="H170" s="66"/>
-      <c r="I170" s="66"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="40"/>
+      <c r="F170" s="19"/>
+      <c r="G170" s="19"/>
+      <c r="H170" s="20"/>
+      <c r="I170" s="20"/>
       <c r="J170" s="21"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
       <c r="C171" s="62"/>
-      <c r="D171" s="67"/>
-      <c r="E171" s="68"/>
-      <c r="F171" s="67"/>
-      <c r="G171" s="69"/>
-      <c r="H171" s="70"/>
-      <c r="I171" s="71"/>
+      <c r="D171" s="63"/>
+      <c r="E171" s="64"/>
+      <c r="F171" s="65"/>
+      <c r="G171" s="65"/>
+      <c r="H171" s="66"/>
+      <c r="I171" s="66"/>
       <c r="J171" s="21"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B172" s="37"/>
-      <c r="C172" s="18"/>
-      <c r="D172" s="40"/>
-      <c r="F172" s="19"/>
-      <c r="G172" s="19"/>
-      <c r="H172" s="20"/>
-      <c r="I172" s="20"/>
+      <c r="C172" s="62"/>
+      <c r="D172" s="63"/>
+      <c r="E172" s="64"/>
+      <c r="F172" s="65"/>
+      <c r="G172" s="65"/>
+      <c r="H172" s="66"/>
+      <c r="I172" s="66"/>
       <c r="J172" s="21"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
-      <c r="C173" s="18"/>
-      <c r="D173" s="40"/>
-      <c r="F173" s="19"/>
-      <c r="G173" s="19"/>
-      <c r="H173" s="20"/>
-      <c r="I173" s="20"/>
+      <c r="C173" s="62"/>
+      <c r="D173" s="67"/>
+      <c r="E173" s="68"/>
+      <c r="F173" s="67"/>
+      <c r="G173" s="69"/>
+      <c r="H173" s="70"/>
+      <c r="I173" s="71"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -28518,13 +28557,33 @@
       <c r="I1686" s="20"/>
       <c r="J1686" s="21"/>
     </row>
+    <row r="1687" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1687" s="37"/>
+      <c r="C1687" s="18"/>
+      <c r="D1687" s="40"/>
+      <c r="F1687" s="19"/>
+      <c r="G1687" s="19"/>
+      <c r="H1687" s="20"/>
+      <c r="I1687" s="20"/>
+      <c r="J1687" s="21"/>
+    </row>
+    <row r="1688" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1688" s="37"/>
+      <c r="C1688" s="18"/>
+      <c r="D1688" s="40"/>
+      <c r="F1688" s="19"/>
+      <c r="G1688" s="19"/>
+      <c r="H1688" s="20"/>
+      <c r="I1688" s="20"/>
+      <c r="J1688" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J162" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J164" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D171">
+  <conditionalFormatting sqref="D173">
     <cfRule type="duplicateValues" dxfId="312" priority="1"/>
     <cfRule type="duplicateValues" dxfId="311" priority="2"/>
     <cfRule type="duplicateValues" dxfId="310" priority="3"/>
@@ -28536,7 +28595,7 @@
     <cfRule type="duplicateValues" dxfId="304" priority="10"/>
     <cfRule type="duplicateValues" dxfId="303" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D171">
+  <conditionalFormatting sqref="D173">
     <cfRule type="duplicateValues" dxfId="302" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C61D7A-3F27-4E40-B973-4ECCC7535AB7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9F1126-C273-4F8C-9EFA-82DDB1B31AAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$164</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$600</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$600</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$166</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$602</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$602</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="228">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1166,6 +1166,15 @@
   <si>
     <t>ДЛЯ ДЕТЕЙ Папа может сос п/о мгс 0.33кг</t>
   </si>
+  <si>
+    <t>С ИНДЕЙКОЙ ПМ сос ц/о в/у 1/270 8шт.</t>
+  </si>
+  <si>
+    <t>ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.</t>
+  </si>
+  <si>
+    <t>ДЛЯ ДЕТЕЙ сос п/о мгс 0.33кг 8шт.</t>
+  </si>
 </sst>
 </file>
 
@@ -1689,7 +1698,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2065,14 +2074,8 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5642,7 +5645,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1688"/>
+  <dimension ref="A1:BO1690"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -5664,17 +5667,17 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="142">
+      <c r="D1" s="140">
         <v>130438122</v>
       </c>
-      <c r="E1" s="143" t="s">
+      <c r="E1" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="145"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="130">
         <v>130438122</v>
       </c>
@@ -5695,23 +5698,23 @@
       <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="134">
+      <c r="D3" s="133">
         <v>46216</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="134">
+      <c r="F3" s="133">
         <f>D3+3</f>
         <v>46219</v>
       </c>
-      <c r="G3" s="146" t="str">
+      <c r="G3" s="144" t="str">
         <f>VLOOKUP(D1,K:L,2,0)</f>
         <v>130438122 ООО "НОВОЕ ВРЕМЯ"  272151 Бердянский р-н 90  Трояны</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="145"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="143"/>
       <c r="K3" s="130">
         <v>130438120</v>
       </c>
@@ -5881,7 +5884,8 @@
       <c r="J10" s="43"/>
     </row>
     <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="133">
+      <c r="A11" s="56" t="str">
+        <f>RIGHT(D11,4)</f>
         <v>7523</v>
       </c>
       <c r="B11" s="53" t="s">
@@ -5969,7 +5973,8 @@
       <c r="BO11" s="128"/>
     </row>
     <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56">
+      <c r="A12" s="56" t="str">
+        <f>RIGHT(D12,4)</f>
         <v>6220</v>
       </c>
       <c r="B12" s="53" t="s">
@@ -6055,7 +6060,8 @@
       <c r="BO12" s="128"/>
     </row>
     <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="133">
+      <c r="A13" s="56" t="str">
+        <f t="shared" ref="A13:A35" si="1">RIGHT(D13,4)</f>
         <v>7539</v>
       </c>
       <c r="B13" s="53" t="s">
@@ -6143,7 +6149,8 @@
       <c r="BO13" s="128"/>
     </row>
     <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="133">
+      <c r="A14" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>7536</v>
       </c>
       <c r="B14" s="53" t="s">
@@ -6231,7 +6238,8 @@
       <c r="BO14" s="128"/>
     </row>
     <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56">
+      <c r="A15" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6340</v>
       </c>
       <c r="B15" s="53" t="s">
@@ -6317,7 +6325,8 @@
       <c r="BO15" s="128"/>
     </row>
     <row r="16" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="56">
+      <c r="A16" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6861</v>
       </c>
       <c r="B16" s="53" t="s">
@@ -6385,7 +6394,8 @@
       <c r="AX16" s="129"/>
     </row>
     <row r="17" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="56">
+      <c r="A17" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6862</v>
       </c>
       <c r="B17" s="53" t="s">
@@ -6402,7 +6412,7 @@
         <v>1.95</v>
       </c>
       <c r="G17" s="23">
-        <f t="shared" ref="G17" si="1">E17</f>
+        <f t="shared" ref="G17" si="2">E17</f>
         <v>0</v>
       </c>
       <c r="H17" s="14">
@@ -6415,7 +6425,8 @@
       <c r="L17" s="129"/>
     </row>
     <row r="18" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="56">
+      <c r="A18" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6341</v>
       </c>
       <c r="B18" s="53" t="s">
@@ -6445,7 +6456,8 @@
       <c r="L18" s="129"/>
     </row>
     <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="56">
+      <c r="A19" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6498</v>
       </c>
       <c r="B19" s="53" t="s">
@@ -6462,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="23">
-        <f t="shared" ref="G19:G20" si="2">E19</f>
+        <f t="shared" ref="G19:G20" si="3">E19</f>
         <v>0</v>
       </c>
       <c r="H19" s="14">
@@ -6475,7 +6487,8 @@
       <c r="L19" s="129"/>
     </row>
     <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="56">
+      <c r="A20" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>4063</v>
       </c>
       <c r="B20" s="53" t="s">
@@ -6492,7 +6505,7 @@
         <v>1.35</v>
       </c>
       <c r="G20" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H20" s="14">
@@ -6505,7 +6518,8 @@
       <c r="L20" s="129"/>
     </row>
     <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="56">
+      <c r="A21" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6333</v>
       </c>
       <c r="B21" s="53" t="s">
@@ -6535,7 +6549,8 @@
       <c r="L21" s="129"/>
     </row>
     <row r="22" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="56">
+      <c r="A22" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>4574</v>
       </c>
       <c r="B22" s="53" t="s">
@@ -6565,7 +6580,8 @@
       <c r="L22" s="129"/>
     </row>
     <row r="23" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="56">
+      <c r="A23" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>7334</v>
       </c>
       <c r="B23" s="53" t="s">
@@ -6595,7 +6611,8 @@
       <c r="L23" s="129"/>
     </row>
     <row r="24" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="56">
+      <c r="A24" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>4813</v>
       </c>
       <c r="B24" s="54" t="s">
@@ -6681,7 +6698,8 @@
       <c r="BO24" s="129"/>
     </row>
     <row r="25" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="56">
+      <c r="A25" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6392</v>
       </c>
       <c r="B25" s="54" t="s">
@@ -6767,7 +6785,8 @@
       <c r="BO25" s="129"/>
     </row>
     <row r="26" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="56">
+      <c r="A26" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>5851</v>
       </c>
       <c r="B26" s="54" t="s">
@@ -6853,7 +6872,8 @@
       <c r="BO26" s="129"/>
     </row>
     <row r="27" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="133">
+      <c r="A27" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>7632</v>
       </c>
       <c r="B27" s="54" t="s">
@@ -6941,7 +6961,8 @@
       <c r="BO27" s="129"/>
     </row>
     <row r="28" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="56">
+      <c r="A28" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>4561</v>
       </c>
       <c r="B28" s="53" t="s">
@@ -6958,7 +6979,7 @@
         <v>1.35</v>
       </c>
       <c r="G28" s="23">
-        <f t="shared" ref="G28:G29" si="3">E28</f>
+        <f t="shared" ref="G28:G29" si="4">E28</f>
         <v>0</v>
       </c>
       <c r="H28" s="14">
@@ -6971,7 +6992,8 @@
       <c r="L28" s="129"/>
     </row>
     <row r="29" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="133">
+      <c r="A29" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>7555</v>
       </c>
       <c r="B29" s="53" t="s">
@@ -6988,7 +7010,7 @@
         <v>1.5</v>
       </c>
       <c r="G29" s="23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="14">
@@ -7003,7 +7025,8 @@
       <c r="L29" s="129"/>
     </row>
     <row r="30" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="56">
+      <c r="A30" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6325</v>
       </c>
       <c r="B30" s="53" t="s">
@@ -7033,7 +7056,8 @@
       <c r="L30" s="129"/>
     </row>
     <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="133">
+      <c r="A31" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>7556</v>
       </c>
       <c r="B31" s="53" t="s">
@@ -7050,7 +7074,7 @@
         <v>1.5</v>
       </c>
       <c r="G31" s="23">
-        <f t="shared" ref="G31:G32" si="4">E31</f>
+        <f t="shared" ref="G31:G32" si="5">E31</f>
         <v>0</v>
       </c>
       <c r="H31" s="14">
@@ -7065,7 +7089,8 @@
       <c r="L31" s="129"/>
     </row>
     <row r="32" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="56">
+      <c r="A32" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>8014</v>
       </c>
       <c r="B32" s="54" t="s">
@@ -7082,7 +7107,7 @@
         <v>1.35</v>
       </c>
       <c r="G32" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H32" s="59">
@@ -7151,7 +7176,8 @@
       <c r="BO32" s="129"/>
     </row>
     <row r="33" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="56">
+      <c r="A33" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>7343</v>
       </c>
       <c r="B33" s="54" t="s">
@@ -7168,7 +7194,7 @@
         <v>0.4</v>
       </c>
       <c r="G33" s="23">
-        <f t="shared" ref="G33:G35" si="5">E33*F33</f>
+        <f t="shared" ref="G33:G35" si="6">E33*F33</f>
         <v>0</v>
       </c>
       <c r="H33" s="59">
@@ -7237,7 +7263,8 @@
       <c r="BO33" s="129"/>
     </row>
     <row r="34" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="56">
+      <c r="A34" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>6797</v>
       </c>
       <c r="B34" s="54" t="s">
@@ -7254,7 +7281,7 @@
         <v>0.4</v>
       </c>
       <c r="G34" s="23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H34" s="59">
@@ -7323,7 +7350,8 @@
       <c r="BO34" s="129"/>
     </row>
     <row r="35" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="56">
+      <c r="A35" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>7231</v>
       </c>
       <c r="B35" s="54" t="s">
@@ -7340,7 +7368,7 @@
         <v>0.3</v>
       </c>
       <c r="G35" s="23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="59">
@@ -7426,7 +7454,8 @@
       <c r="L36" s="129"/>
     </row>
     <row r="37" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="56">
+      <c r="A37" s="56" t="str">
+        <f t="shared" ref="A37:A71" si="7">RIGHT(D37,4)</f>
         <v>6602</v>
       </c>
       <c r="B37" s="54" t="s">
@@ -7443,7 +7472,7 @@
         <v>0.35</v>
       </c>
       <c r="G37" s="23">
-        <f t="shared" ref="G37:G42" si="6">E37*F37</f>
+        <f t="shared" ref="G37:G43" si="8">E37*F37</f>
         <v>0</v>
       </c>
       <c r="H37" s="59">
@@ -7512,11 +7541,12 @@
       <c r="BO37" s="129"/>
     </row>
     <row r="38" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="56">
+      <c r="A38" s="56" t="str">
+        <f t="shared" si="7"/>
         <v>7284</v>
       </c>
       <c r="B38" s="54" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="C38" s="55" t="s">
         <v>21</v>
@@ -7529,7 +7559,7 @@
         <v>0.33</v>
       </c>
       <c r="G38" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H38" s="59">
@@ -7598,7 +7628,8 @@
       <c r="BO38" s="129"/>
     </row>
     <row r="39" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="56">
+      <c r="A39" s="56" t="str">
+        <f t="shared" si="7"/>
         <v>7601</v>
       </c>
       <c r="B39" s="54" t="s">
@@ -7615,7 +7646,7 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="G39" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H39" s="59">
@@ -7684,7 +7715,8 @@
       <c r="BO39" s="129"/>
     </row>
     <row r="40" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="56">
+      <c r="A40" s="56" t="str">
+        <f t="shared" si="7"/>
         <v>7461</v>
       </c>
       <c r="B40" s="54" t="s">
@@ -7701,7 +7733,7 @@
         <v>0.33</v>
       </c>
       <c r="G40" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H40" s="59">
@@ -7772,7 +7804,8 @@
       <c r="BO40" s="129"/>
     </row>
     <row r="41" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="56">
+      <c r="A41" s="56" t="str">
+        <f t="shared" si="7"/>
         <v>7371</v>
       </c>
       <c r="B41" s="54" t="s">
@@ -7789,7 +7822,7 @@
         <v>0.3</v>
       </c>
       <c r="G41" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H41" s="59">
@@ -7858,32 +7891,29 @@
       <c r="BO41" s="129"/>
     </row>
     <row r="42" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="56">
-        <v>6759</v>
+      <c r="A42" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7040</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>42</v>
+        <v>225</v>
       </c>
       <c r="C42" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="70">
-        <v>1001020836759</v>
+        <v>1001025027040</v>
       </c>
       <c r="E42" s="24"/>
       <c r="F42" s="58">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="G42" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H42" s="59">
-        <v>2.8</v>
-      </c>
-      <c r="I42" s="59">
-        <v>30</v>
-      </c>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
       <c r="J42" s="59"/>
       <c r="K42" s="60"/>
       <c r="L42" s="129"/>
@@ -7944,28 +7974,29 @@
       <c r="BO42" s="129"/>
     </row>
     <row r="43" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="56">
-        <v>6761</v>
+      <c r="A43" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6759</v>
       </c>
       <c r="B43" s="54" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D43" s="70">
-        <v>1001020836761</v>
+        <v>1001020836759</v>
       </c>
       <c r="E43" s="24"/>
       <c r="F43" s="58">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G43" s="23">
-        <f t="shared" ref="G43:G44" si="7">E43</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H43" s="59">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I43" s="59">
         <v>30</v>
@@ -8030,31 +8061,32 @@
       <c r="BO43" s="129"/>
     </row>
     <row r="44" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="56">
-        <v>6829</v>
+      <c r="A44" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6761</v>
       </c>
       <c r="B44" s="54" t="s">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="C44" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="70">
-        <v>1001024976829</v>
+        <v>1001020836761</v>
       </c>
       <c r="E44" s="24"/>
       <c r="F44" s="58">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="G44" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="G44:G45" si="9">E44</f>
         <v>0</v>
       </c>
       <c r="H44" s="59">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="I44" s="59">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J44" s="59"/>
       <c r="K44" s="60"/>
@@ -8116,28 +8148,29 @@
       <c r="BO44" s="129"/>
     </row>
     <row r="45" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="56">
-        <v>6616</v>
+      <c r="A45" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6829</v>
       </c>
       <c r="B45" s="54" t="s">
-        <v>43</v>
+        <v>182</v>
       </c>
       <c r="C45" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D45" s="70">
-        <v>1001024976616</v>
+        <v>1001024976829</v>
       </c>
       <c r="E45" s="24"/>
       <c r="F45" s="58">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="G45" s="23">
-        <f>E45*F45</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H45" s="59">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="I45" s="59">
         <v>45</v>
@@ -8202,31 +8235,32 @@
       <c r="BO45" s="129"/>
     </row>
     <row r="46" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="56">
-        <v>7075</v>
+      <c r="A46" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6616</v>
       </c>
       <c r="B46" s="54" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C46" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D46" s="70">
-        <v>1001022657075</v>
+        <v>1001024976616</v>
       </c>
       <c r="E46" s="24"/>
       <c r="F46" s="58">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="G46" s="23">
-        <f>E46</f>
+        <f>E46*F46</f>
         <v>0</v>
       </c>
       <c r="H46" s="59">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="I46" s="59">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J46" s="59"/>
       <c r="K46" s="60"/>
@@ -8288,28 +8322,29 @@
       <c r="BO46" s="129"/>
     </row>
     <row r="47" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="56">
-        <v>7074</v>
+      <c r="A47" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7075</v>
       </c>
       <c r="B47" s="54" t="s">
-        <v>183</v>
+        <v>50</v>
       </c>
       <c r="C47" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D47" s="70">
-        <v>1001022657074</v>
+        <v>1001022657075</v>
       </c>
       <c r="E47" s="24"/>
       <c r="F47" s="58">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="G47" s="23">
-        <f t="shared" ref="G47:G50" si="8">E47*F47</f>
+        <f>E47</f>
         <v>0</v>
       </c>
       <c r="H47" s="59">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I47" s="59">
         <v>50</v>
@@ -8374,28 +8409,29 @@
       <c r="BO47" s="129"/>
     </row>
     <row r="48" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="56">
-        <v>7073</v>
+      <c r="A48" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7074</v>
       </c>
       <c r="B48" s="54" t="s">
-        <v>51</v>
+        <v>183</v>
       </c>
       <c r="C48" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="70">
-        <v>1001022657073</v>
+        <v>1001022657074</v>
       </c>
       <c r="E48" s="24"/>
       <c r="F48" s="58">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="G48" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="G48:G51" si="10">E48*F48</f>
         <v>0</v>
       </c>
       <c r="H48" s="59">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="I48" s="59">
         <v>50</v>
@@ -8460,31 +8496,32 @@
       <c r="BO48" s="129"/>
     </row>
     <row r="49" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="56">
-        <v>6724</v>
+      <c r="A49" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7073</v>
       </c>
       <c r="B49" s="54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C49" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="70">
-        <v>1001020836724</v>
+        <v>1001022657073</v>
       </c>
       <c r="E49" s="24"/>
       <c r="F49" s="58">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="G49" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H49" s="59">
-        <v>4.0999999999999996</v>
+        <v>2.8</v>
       </c>
       <c r="I49" s="59">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J49" s="59"/>
       <c r="K49" s="60"/>
@@ -8546,28 +8583,29 @@
       <c r="BO49" s="129"/>
     </row>
     <row r="50" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="56">
-        <v>5819</v>
+      <c r="A50" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6724</v>
       </c>
       <c r="B50" s="54" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C50" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="70">
-        <v>1001022725819</v>
+        <v>1001020836724</v>
       </c>
       <c r="E50" s="24"/>
       <c r="F50" s="58">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G50" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H50" s="59">
-        <v>3.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I50" s="59">
         <v>45</v>
@@ -8632,28 +8670,29 @@
       <c r="BO50" s="129"/>
     </row>
     <row r="51" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="56">
-        <v>6303</v>
+      <c r="A51" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>5819</v>
       </c>
       <c r="B51" s="54" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D51" s="70">
-        <v>1001022726303</v>
+        <v>1001022725819</v>
       </c>
       <c r="E51" s="24"/>
       <c r="F51" s="58">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G51" s="23">
-        <f>E51</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H51" s="59">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="I51" s="59">
         <v>45</v>
@@ -8718,31 +8757,32 @@
       <c r="BO51" s="129"/>
     </row>
     <row r="52" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="56">
-        <v>7255</v>
+      <c r="A52" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6303</v>
       </c>
       <c r="B52" s="54" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="C52" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D52" s="70">
-        <v>1001025507255</v>
+        <v>1001022726303</v>
       </c>
       <c r="E52" s="24"/>
       <c r="F52" s="58">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G52" s="23">
-        <f>E52*F52</f>
+        <f>E52</f>
         <v>0</v>
       </c>
       <c r="H52" s="59">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="I52" s="59">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J52" s="59"/>
       <c r="K52" s="60"/>
@@ -8804,28 +8844,29 @@
       <c r="BO52" s="129"/>
     </row>
     <row r="53" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="56">
-        <v>7271</v>
+      <c r="A53" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7255</v>
       </c>
       <c r="B53" s="54" t="s">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="C53" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D53" s="70">
-        <v>1001025507271</v>
+        <v>1001025507255</v>
       </c>
       <c r="E53" s="24"/>
       <c r="F53" s="58">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G53" s="23">
-        <f>E53</f>
+        <f>E53*F53</f>
         <v>0</v>
       </c>
       <c r="H53" s="59">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="I53" s="59">
         <v>50</v>
@@ -8890,31 +8931,32 @@
       <c r="BO53" s="129"/>
     </row>
     <row r="54" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="56">
-        <v>6765</v>
+      <c r="A54" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7271</v>
       </c>
       <c r="B54" s="54" t="s">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="C54" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D54" s="70">
-        <v>1001023696765</v>
+        <v>1001025507271</v>
       </c>
       <c r="E54" s="24"/>
       <c r="F54" s="58">
-        <v>0.36</v>
+        <v>1.5</v>
       </c>
       <c r="G54" s="23">
-        <f>E54*F54</f>
+        <f>E54</f>
         <v>0</v>
       </c>
       <c r="H54" s="59">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="I54" s="59">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J54" s="59"/>
       <c r="K54" s="60"/>
@@ -8976,28 +9018,29 @@
       <c r="BO54" s="129"/>
     </row>
     <row r="55" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="56">
-        <v>6767</v>
+      <c r="A55" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6765</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D55" s="70">
-        <v>1001023696767</v>
+        <v>1001023696765</v>
       </c>
       <c r="E55" s="24"/>
       <c r="F55" s="58">
-        <v>1.04</v>
+        <v>0.36</v>
       </c>
       <c r="G55" s="23">
-        <f>E55</f>
+        <f>E55*F55</f>
         <v>0</v>
       </c>
       <c r="H55" s="59">
-        <v>4.16</v>
+        <v>2.16</v>
       </c>
       <c r="I55" s="59">
         <v>45</v>
@@ -9062,28 +9105,29 @@
       <c r="BO55" s="129"/>
     </row>
     <row r="56" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="56">
-        <v>6475</v>
+      <c r="A56" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6767</v>
       </c>
       <c r="B56" s="54" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C56" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D56" s="70">
-        <v>1001025176475</v>
+        <v>1001023696767</v>
       </c>
       <c r="E56" s="24"/>
       <c r="F56" s="58">
-        <v>0.4</v>
+        <v>1.04</v>
       </c>
       <c r="G56" s="23">
-        <f>E56*F56</f>
+        <f>E56</f>
         <v>0</v>
       </c>
       <c r="H56" s="59">
-        <v>2.4</v>
+        <v>4.16</v>
       </c>
       <c r="I56" s="59">
         <v>45</v>
@@ -9148,31 +9192,32 @@
       <c r="BO56" s="129"/>
     </row>
     <row r="57" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="56">
-        <v>7083</v>
+      <c r="A57" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6475</v>
       </c>
       <c r="B57" s="54" t="s">
-        <v>186</v>
+        <v>46</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D57" s="70">
-        <v>1001022467083</v>
+        <v>1001025176475</v>
       </c>
       <c r="E57" s="24"/>
       <c r="F57" s="58">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G57" s="23">
-        <f>E57</f>
+        <f>E57*F57</f>
         <v>0</v>
       </c>
       <c r="H57" s="59">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="I57" s="59">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J57" s="59"/>
       <c r="K57" s="60"/>
@@ -9234,28 +9279,29 @@
       <c r="BO57" s="129"/>
     </row>
     <row r="58" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="56">
-        <v>7080</v>
+      <c r="A58" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7083</v>
       </c>
       <c r="B58" s="54" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="C58" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D58" s="70">
-        <v>1001022467080</v>
+        <v>1001022467083</v>
       </c>
       <c r="E58" s="24"/>
       <c r="F58" s="58">
-        <v>0.41</v>
+        <v>1.5</v>
       </c>
       <c r="G58" s="23">
-        <f t="shared" ref="G58:G60" si="9">E58*F58</f>
+        <f>E58</f>
         <v>0</v>
       </c>
       <c r="H58" s="59">
-        <v>4.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="I58" s="59">
         <v>50</v>
@@ -9320,28 +9366,29 @@
       <c r="BO58" s="129"/>
     </row>
     <row r="59" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="56">
-        <v>7276</v>
+      <c r="A59" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7080</v>
       </c>
       <c r="B59" s="54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C59" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D59" s="70">
-        <v>1001022467276</v>
+        <v>1001022467080</v>
       </c>
       <c r="E59" s="24"/>
       <c r="F59" s="58">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="G59" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="G59:G61" si="11">E59*F59</f>
         <v>0</v>
       </c>
       <c r="H59" s="59">
-        <v>2.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I59" s="59">
         <v>50</v>
@@ -9406,31 +9453,32 @@
       <c r="BO59" s="129"/>
     </row>
     <row r="60" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="56">
-        <v>6762</v>
+      <c r="A60" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7276</v>
       </c>
       <c r="B60" s="54" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C60" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D60" s="70">
-        <v>1001020846762</v>
+        <v>1001022467276</v>
       </c>
       <c r="E60" s="24"/>
       <c r="F60" s="58">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="G60" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H60" s="59">
-        <v>3.28</v>
+        <v>2.1</v>
       </c>
       <c r="I60" s="59">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J60" s="59"/>
       <c r="K60" s="60"/>
@@ -9491,89 +9539,148 @@
       <c r="BN60" s="129"/>
       <c r="BO60" s="129"/>
     </row>
-    <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="56">
+    <row r="61" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6762</v>
+      </c>
+      <c r="B61" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="70">
+        <v>1001020846762</v>
+      </c>
+      <c r="E61" s="24"/>
+      <c r="F61" s="58">
+        <v>0.41</v>
+      </c>
+      <c r="G61" s="23">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="59">
+        <v>3.28</v>
+      </c>
+      <c r="I61" s="59">
+        <v>45</v>
+      </c>
+      <c r="J61" s="59"/>
+      <c r="K61" s="60"/>
+      <c r="L61" s="129"/>
+      <c r="M61" s="129"/>
+      <c r="N61" s="129"/>
+      <c r="O61" s="129"/>
+      <c r="P61" s="129"/>
+      <c r="Q61" s="129"/>
+      <c r="R61" s="129"/>
+      <c r="S61" s="129"/>
+      <c r="T61" s="129"/>
+      <c r="U61" s="129"/>
+      <c r="V61" s="129"/>
+      <c r="W61" s="129"/>
+      <c r="X61" s="129"/>
+      <c r="Y61" s="129"/>
+      <c r="Z61" s="129"/>
+      <c r="AA61" s="129"/>
+      <c r="AB61" s="129"/>
+      <c r="AC61" s="129"/>
+      <c r="AD61" s="129"/>
+      <c r="AE61" s="129"/>
+      <c r="AF61" s="129"/>
+      <c r="AG61" s="129"/>
+      <c r="AH61" s="129"/>
+      <c r="AI61" s="129"/>
+      <c r="AJ61" s="129"/>
+      <c r="AK61" s="129"/>
+      <c r="AL61" s="129"/>
+      <c r="AM61" s="129"/>
+      <c r="AN61" s="129"/>
+      <c r="AO61" s="129"/>
+      <c r="AP61" s="129"/>
+      <c r="AQ61" s="129"/>
+      <c r="AR61" s="129"/>
+      <c r="AS61" s="129"/>
+      <c r="AT61" s="129"/>
+      <c r="AU61" s="129"/>
+      <c r="AV61" s="129"/>
+      <c r="AW61" s="129"/>
+      <c r="AX61" s="129"/>
+      <c r="AY61" s="129"/>
+      <c r="AZ61" s="129"/>
+      <c r="BA61" s="129"/>
+      <c r="BB61" s="129"/>
+      <c r="BC61" s="129"/>
+      <c r="BD61" s="129"/>
+      <c r="BE61" s="129"/>
+      <c r="BF61" s="129"/>
+      <c r="BG61" s="129"/>
+      <c r="BH61" s="129"/>
+      <c r="BI61" s="129"/>
+      <c r="BJ61" s="129"/>
+      <c r="BK61" s="129"/>
+      <c r="BL61" s="129"/>
+      <c r="BM61" s="129"/>
+      <c r="BN61" s="129"/>
+      <c r="BO61" s="129"/>
+    </row>
+    <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="56" t="str">
+        <f t="shared" si="7"/>
         <v>6764</v>
       </c>
-      <c r="B61" s="54" t="s">
+      <c r="B62" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="C61" s="55" t="s">
+      <c r="C62" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="70">
+      <c r="D62" s="70">
         <v>1001020846764</v>
-      </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="23">
-        <v>1</v>
-      </c>
-      <c r="G61" s="23">
-        <f>E61</f>
-        <v>0</v>
-      </c>
-      <c r="H61" s="14">
-        <v>4</v>
-      </c>
-      <c r="I61" s="14">
-        <v>45</v>
-      </c>
-      <c r="J61" s="29"/>
-      <c r="L61" s="129"/>
-    </row>
-    <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="56">
-        <v>7066</v>
-      </c>
-      <c r="B62" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="C62" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="70">
-        <v>1001022377066</v>
       </c>
       <c r="E62" s="24"/>
       <c r="F62" s="23">
-        <v>0.41</v>
+        <v>1</v>
       </c>
       <c r="G62" s="23">
-        <f>E62*F62</f>
+        <f>E62</f>
         <v>0</v>
       </c>
       <c r="H62" s="14">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="I62" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J62" s="29"/>
       <c r="L62" s="129"/>
     </row>
     <row r="63" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="56">
-        <v>7070</v>
+      <c r="A63" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7066</v>
       </c>
       <c r="B63" s="54" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C63" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D63" s="70">
-        <v>1001022377070</v>
+        <v>1001022377066</v>
       </c>
       <c r="E63" s="24"/>
       <c r="F63" s="23">
-        <v>1.5</v>
+        <v>0.41</v>
       </c>
       <c r="G63" s="23">
-        <f>E63</f>
+        <f>E63*F63</f>
         <v>0</v>
       </c>
       <c r="H63" s="14">
-        <v>6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I63" s="14">
         <v>50</v>
@@ -9582,58 +9689,60 @@
       <c r="L63" s="129"/>
     </row>
     <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="56">
-        <v>6713</v>
+      <c r="A64" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7070</v>
       </c>
       <c r="B64" s="54" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C64" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D64" s="70">
-        <v>1001022246713</v>
+        <v>1001022377070</v>
       </c>
       <c r="E64" s="24"/>
       <c r="F64" s="23">
-        <v>0.41</v>
+        <v>1.5</v>
       </c>
       <c r="G64" s="23">
-        <f>E64*F64</f>
+        <f>E64</f>
         <v>0</v>
       </c>
       <c r="H64" s="14">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="I64" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J64" s="29"/>
       <c r="L64" s="129"/>
     </row>
     <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="56">
-        <v>6661</v>
+      <c r="A65" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6713</v>
       </c>
       <c r="B65" s="54" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="C65" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D65" s="70">
-        <v>1001022246661</v>
+        <v>1001022246713</v>
       </c>
       <c r="E65" s="24"/>
       <c r="F65" s="23">
-        <v>1.5</v>
+        <v>0.41</v>
       </c>
       <c r="G65" s="23">
-        <f t="shared" ref="G65:G66" si="10">E65</f>
+        <f>E65*F65</f>
         <v>0</v>
       </c>
       <c r="H65" s="14">
-        <v>6</v>
+        <v>3.28</v>
       </c>
       <c r="I65" s="14">
         <v>45</v>
@@ -9642,28 +9751,29 @@
       <c r="L65" s="129"/>
     </row>
     <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="56">
-        <v>6254</v>
+      <c r="A66" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6661</v>
       </c>
       <c r="B66" s="54" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C66" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D66" s="70">
-        <v>1001022556254</v>
+        <v>1001022246661</v>
       </c>
       <c r="E66" s="24"/>
       <c r="F66" s="23">
         <v>1.5</v>
       </c>
       <c r="G66" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="G66:G67" si="12">E66</f>
         <v>0</v>
       </c>
       <c r="H66" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I66" s="14">
         <v>45</v>
@@ -9672,28 +9782,29 @@
       <c r="L66" s="129"/>
     </row>
     <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="56">
-        <v>6837</v>
+      <c r="A67" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6254</v>
       </c>
       <c r="B67" s="54" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D67" s="70">
-        <v>1001022556837</v>
+        <v>1001022556254</v>
       </c>
       <c r="E67" s="24"/>
       <c r="F67" s="23">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G67" s="23">
-        <f t="shared" ref="G67:G70" si="11">E67*F67</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H67" s="14">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="I67" s="14">
         <v>45</v>
@@ -9702,28 +9813,29 @@
       <c r="L67" s="129"/>
     </row>
     <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="56">
-        <v>7385</v>
+      <c r="A68" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>6837</v>
       </c>
       <c r="B68" s="54" t="s">
-        <v>189</v>
+        <v>48</v>
       </c>
       <c r="C68" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D68" s="70">
-        <v>1001027067385</v>
+        <v>1001022556837</v>
       </c>
       <c r="E68" s="24"/>
       <c r="F68" s="23">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="G68" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="G68:G71" si="13">E68*F68</f>
         <v>0</v>
       </c>
       <c r="H68" s="14">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="I68" s="14">
         <v>45</v>
@@ -9732,28 +9844,29 @@
       <c r="L68" s="129"/>
     </row>
     <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="56">
-        <v>7044</v>
+      <c r="A69" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7385</v>
       </c>
       <c r="B69" s="54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C69" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D69" s="70">
-        <v>1001025167044</v>
+        <v>1001027067385</v>
       </c>
       <c r="E69" s="24"/>
       <c r="F69" s="23">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="G69" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H69" s="14">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I69" s="14">
         <v>45</v>
@@ -9761,29 +9874,30 @@
       <c r="J69" s="29"/>
       <c r="L69" s="129"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="56">
-        <v>7460</v>
+    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7044</v>
       </c>
       <c r="B70" s="54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C70" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D70" s="70">
-        <v>1001027247460</v>
+        <v>1001025167044</v>
       </c>
       <c r="E70" s="24"/>
       <c r="F70" s="23">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="G70" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H70" s="14">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="I70" s="14">
         <v>45</v>
@@ -9791,102 +9905,105 @@
       <c r="J70" s="29"/>
       <c r="L70" s="129"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="47" t="s">
+    <row r="71" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="56" t="str">
+        <f t="shared" si="7"/>
+        <v>7460</v>
+      </c>
+      <c r="B71" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="C71" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="70">
+        <v>1001027247460</v>
+      </c>
+      <c r="E71" s="24"/>
+      <c r="F71" s="23">
+        <v>0.33</v>
+      </c>
+      <c r="G71" s="23">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>2.64</v>
+      </c>
+      <c r="I71" s="14">
+        <v>45</v>
+      </c>
+      <c r="J71" s="29"/>
+      <c r="L71" s="129"/>
+    </row>
+    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B71" s="42" t="s">
+      <c r="B72" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="C71" s="42"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="42"/>
-      <c r="H71" s="42"/>
-      <c r="I71" s="42"/>
-      <c r="J71" s="43"/>
-      <c r="L71" s="129"/>
-    </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="56">
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="43"/>
+      <c r="L72" s="129"/>
+    </row>
+    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="56" t="str">
+        <f t="shared" ref="A73:A79" si="14">RIGHT(D73,4)</f>
         <v>6550</v>
       </c>
-      <c r="B72" s="124" t="s">
+      <c r="B73" s="124" t="s">
         <v>174</v>
       </c>
-      <c r="C72" s="125" t="s">
+      <c r="C73" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="D72" s="57">
+      <c r="D73" s="57">
         <v>1001032736550</v>
       </c>
-      <c r="E72" s="24"/>
-      <c r="F72" s="58">
+      <c r="E73" s="24"/>
+      <c r="F73" s="58">
         <v>1</v>
       </c>
-      <c r="G72" s="23">
-        <f t="shared" ref="G72:G75" si="12">E72</f>
+      <c r="G73" s="23">
+        <f t="shared" ref="G73:G76" si="15">E73</f>
         <v>0</v>
       </c>
-      <c r="H72" s="59">
+      <c r="H73" s="59">
         <v>3</v>
       </c>
-      <c r="I72" s="59">
+      <c r="I73" s="59">
         <v>45</v>
       </c>
-      <c r="J72" s="59"/>
-      <c r="L72" s="129"/>
-    </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="56">
+      <c r="J73" s="59"/>
+      <c r="L73" s="129"/>
+    </row>
+    <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="56" t="str">
+        <f t="shared" si="14"/>
         <v>6608</v>
       </c>
-      <c r="B73" s="124" t="s">
+      <c r="B74" s="124" t="s">
         <v>59</v>
-      </c>
-      <c r="C73" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D73" s="51">
-        <v>1001033856608</v>
-      </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="23">
-        <v>1</v>
-      </c>
-      <c r="G73" s="23">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="14">
-        <v>3</v>
-      </c>
-      <c r="I73" s="14">
-        <v>45</v>
-      </c>
-      <c r="J73" s="29"/>
-      <c r="L73" s="129"/>
-    </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="56">
-        <v>7001</v>
-      </c>
-      <c r="B74" s="124" t="s">
-        <v>58</v>
       </c>
       <c r="C74" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D74" s="51">
-        <v>1001035937001</v>
+        <v>1001033856608</v>
       </c>
       <c r="E74" s="24"/>
       <c r="F74" s="23">
         <v>1</v>
       </c>
       <c r="G74" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H74" s="14">
@@ -9899,24 +10016,25 @@
       <c r="L74" s="129"/>
     </row>
     <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="56">
-        <v>6527</v>
+      <c r="A75" s="56" t="str">
+        <f t="shared" si="14"/>
+        <v>7001</v>
       </c>
       <c r="B75" s="124" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="C75" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D75" s="51">
-        <v>1001031076527</v>
+        <v>1001035937001</v>
       </c>
       <c r="E75" s="24"/>
       <c r="F75" s="23">
         <v>1</v>
       </c>
       <c r="G75" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H75" s="14">
@@ -9929,28 +10047,29 @@
       <c r="L75" s="129"/>
     </row>
     <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="56">
-        <v>6609</v>
-      </c>
-      <c r="B76" s="114" t="s">
-        <v>176</v>
+      <c r="A76" s="56" t="str">
+        <f t="shared" si="14"/>
+        <v>6527</v>
+      </c>
+      <c r="B76" s="124" t="s">
+        <v>175</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D76" s="51">
-        <v>1001033856609</v>
+        <v>1001031076527</v>
       </c>
       <c r="E76" s="24"/>
       <c r="F76" s="23">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G76" s="23">
-        <f t="shared" ref="G76:G78" si="13">E76*F76</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H76" s="14">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="I76" s="14">
         <v>45</v>
@@ -9959,289 +10078,298 @@
       <c r="L76" s="129"/>
     </row>
     <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="56">
-        <v>7059</v>
+      <c r="A77" s="56" t="str">
+        <f t="shared" si="14"/>
+        <v>6609</v>
       </c>
       <c r="B77" s="114" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C77" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D77" s="51">
-        <v>1001035277059</v>
+        <v>1001033856609</v>
       </c>
       <c r="E77" s="24"/>
       <c r="F77" s="23">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G77" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="G77:G79" si="16">E77*F77</f>
         <v>0</v>
       </c>
       <c r="H77" s="14">
         <v>2.4</v>
       </c>
       <c r="I77" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J77" s="29"/>
       <c r="L77" s="129"/>
     </row>
-    <row r="78" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="56">
-        <v>6528</v>
+    <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="56" t="str">
+        <f t="shared" si="14"/>
+        <v>7059</v>
       </c>
       <c r="B78" s="114" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C78" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D78" s="51">
-        <v>1001031076528</v>
+        <v>1001035277059</v>
       </c>
       <c r="E78" s="24"/>
       <c r="F78" s="23">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G78" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H78" s="14">
         <v>2.4</v>
       </c>
       <c r="I78" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J78" s="29"/>
       <c r="L78" s="129"/>
     </row>
-    <row r="79" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="47" t="s">
+    <row r="79" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="56" t="str">
+        <f t="shared" si="14"/>
+        <v>6528</v>
+      </c>
+      <c r="B79" s="114" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="51">
+        <v>1001031076528</v>
+      </c>
+      <c r="E79" s="24"/>
+      <c r="F79" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="G79" s="23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H79" s="14">
+        <v>2.4</v>
+      </c>
+      <c r="I79" s="14">
+        <v>45</v>
+      </c>
+      <c r="J79" s="29"/>
+      <c r="L79" s="129"/>
+    </row>
+    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B79" s="42" t="s">
+      <c r="B80" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="C79" s="42"/>
-      <c r="D79" s="42"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="42"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-      <c r="J79" s="43"/>
-      <c r="L79" s="129"/>
-    </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="133">
+      <c r="C80" s="42"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="43"/>
+      <c r="L80" s="129"/>
+    </row>
+    <row r="81" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="56" t="str">
+        <f t="shared" ref="A81:A105" si="17">RIGHT(D81,4)</f>
         <v>7564</v>
       </c>
-      <c r="B80" s="53" t="s">
+      <c r="B81" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="C80" s="50" t="s">
+      <c r="C81" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D80" s="51">
+      <c r="D81" s="51">
         <v>1001303637564</v>
-      </c>
-      <c r="E80" s="24"/>
-      <c r="F80" s="23">
-        <v>0.84</v>
-      </c>
-      <c r="G80" s="23">
-        <f>E80</f>
-        <v>0</v>
-      </c>
-      <c r="H80" s="14">
-        <v>5.04</v>
-      </c>
-      <c r="I80" s="14">
-        <v>45</v>
-      </c>
-      <c r="J80" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="L80" s="129"/>
-    </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="133">
-        <v>7603</v>
-      </c>
-      <c r="B81" s="54" t="s">
-        <v>132</v>
-      </c>
-      <c r="C81" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D81" s="57">
-        <v>1001303637603</v>
       </c>
       <c r="E81" s="24"/>
       <c r="F81" s="23">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="G81" s="23">
-        <f t="shared" ref="G81:G93" si="14">E81*F81</f>
+        <f>E81</f>
         <v>0</v>
       </c>
       <c r="H81" s="14">
-        <v>2.64</v>
+        <v>5.04</v>
       </c>
       <c r="I81" s="14">
         <v>45</v>
       </c>
       <c r="J81" s="52" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L81" s="129"/>
     </row>
     <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="56">
-        <v>7149</v>
+      <c r="A82" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7603</v>
       </c>
       <c r="B82" s="54" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="C82" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="57">
-        <v>1001303637149</v>
+        <v>1001303637603</v>
       </c>
       <c r="E82" s="24"/>
       <c r="F82" s="23">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
       <c r="G82" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="G82:G94" si="18">E82*F82</f>
         <v>0</v>
       </c>
       <c r="H82" s="14">
-        <v>5.04</v>
+        <v>2.64</v>
       </c>
       <c r="I82" s="14">
-        <v>50</v>
-      </c>
-      <c r="J82" s="29"/>
+        <v>45</v>
+      </c>
+      <c r="J82" s="52" t="s">
+        <v>199</v>
+      </c>
       <c r="L82" s="129"/>
     </row>
     <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="56">
-        <v>7233</v>
+      <c r="A83" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7149</v>
       </c>
       <c r="B83" s="54" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="C83" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="57">
-        <v>1001303637233</v>
+        <v>1001303637149</v>
       </c>
       <c r="E83" s="24"/>
-      <c r="F83" s="58">
-        <v>0.31</v>
+      <c r="F83" s="23">
+        <v>0.84</v>
       </c>
       <c r="G83" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H83" s="59">
-        <v>2.48</v>
-      </c>
-      <c r="I83" s="59">
-        <v>45</v>
-      </c>
-      <c r="J83" s="59"/>
+      <c r="H83" s="14">
+        <v>5.04</v>
+      </c>
+      <c r="I83" s="14">
+        <v>50</v>
+      </c>
+      <c r="J83" s="29"/>
       <c r="L83" s="129"/>
     </row>
     <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="56">
-        <v>7232</v>
+      <c r="A84" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7233</v>
       </c>
       <c r="B84" s="54" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="C84" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D84" s="57">
-        <v>1001302277232</v>
+        <v>1001303637233</v>
       </c>
       <c r="E84" s="24"/>
       <c r="F84" s="58">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G84" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H84" s="59">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I84" s="59">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J84" s="59"/>
       <c r="L84" s="129"/>
     </row>
     <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="56">
-        <v>7241</v>
+      <c r="A85" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7232</v>
       </c>
       <c r="B85" s="54" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C85" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D85" s="57">
-        <v>1001303107241</v>
+        <v>1001302277232</v>
       </c>
       <c r="E85" s="24"/>
       <c r="F85" s="58">
         <v>0.28000000000000003</v>
       </c>
       <c r="G85" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H85" s="59">
         <v>2.2400000000000002</v>
       </c>
       <c r="I85" s="59">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J85" s="59"/>
       <c r="L85" s="129"/>
     </row>
     <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="56">
-        <v>7133</v>
+      <c r="A86" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7241</v>
       </c>
       <c r="B86" s="54" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C86" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D86" s="57">
-        <v>1001300367133</v>
+        <v>1001303107241</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="58">
-        <v>0.84</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G86" s="23">
-        <f>E86</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H86" s="59">
-        <v>5.04</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I86" s="59">
         <v>45</v>
@@ -10250,112 +10378,116 @@
       <c r="L86" s="129"/>
     </row>
     <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="56">
+      <c r="A87" s="56" t="str">
+        <f t="shared" si="17"/>
         <v>7133</v>
       </c>
       <c r="B87" s="54" t="s">
-        <v>222</v>
+        <v>74</v>
       </c>
       <c r="C87" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D87" s="57">
-        <v>1001300456946</v>
+        <v>1001300367133</v>
       </c>
       <c r="E87" s="24"/>
-      <c r="F87" s="58"/>
+      <c r="F87" s="58">
+        <v>0.84</v>
+      </c>
       <c r="G87" s="23">
         <f>E87</f>
         <v>0</v>
       </c>
-      <c r="H87" s="59"/>
-      <c r="I87" s="59"/>
+      <c r="H87" s="59">
+        <v>5.04</v>
+      </c>
+      <c r="I87" s="59">
+        <v>45</v>
+      </c>
       <c r="J87" s="59"/>
       <c r="L87" s="129"/>
     </row>
     <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="56">
-        <v>6807</v>
+      <c r="A88" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>6946</v>
       </c>
       <c r="B88" s="54" t="s">
-        <v>76</v>
+        <v>222</v>
       </c>
       <c r="C88" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D88" s="57">
-        <v>1001300366807</v>
+        <v>1001300456946</v>
       </c>
       <c r="E88" s="24"/>
-      <c r="F88" s="58">
-        <v>0.33</v>
-      </c>
+      <c r="F88" s="58"/>
       <c r="G88" s="23">
-        <f t="shared" si="14"/>
+        <f>E88</f>
         <v>0</v>
       </c>
-      <c r="H88" s="59">
-        <v>2.64</v>
-      </c>
-      <c r="I88" s="59">
-        <v>45</v>
-      </c>
+      <c r="H88" s="59"/>
+      <c r="I88" s="59"/>
       <c r="J88" s="59"/>
       <c r="L88" s="129"/>
     </row>
     <row r="89" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="56">
-        <v>7154</v>
+      <c r="A89" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>6807</v>
       </c>
       <c r="B89" s="54" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C89" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D89" s="57">
+        <v>1001300366807</v>
+      </c>
+      <c r="E89" s="24"/>
+      <c r="F89" s="58">
+        <v>0.33</v>
+      </c>
+      <c r="G89" s="23">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H89" s="59">
+        <v>2.64</v>
+      </c>
+      <c r="I89" s="59">
+        <v>45</v>
+      </c>
+      <c r="J89" s="59"/>
+      <c r="L89" s="129"/>
+    </row>
+    <row r="90" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7154</v>
+      </c>
+      <c r="B90" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="C90" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="57">
         <v>1001300387154</v>
-      </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="23">
-        <v>0.35</v>
-      </c>
-      <c r="G89" s="23">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H89" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I89" s="14">
-        <v>50</v>
-      </c>
-      <c r="J89" s="29"/>
-      <c r="L89" s="129"/>
-    </row>
-    <row r="90" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="56">
-        <v>7157</v>
-      </c>
-      <c r="B90" s="54" t="s">
-        <v>75</v>
-      </c>
-      <c r="C90" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D90" s="57">
-        <v>1001300387157</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="G90" s="23">
-        <f>E90</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H90" s="14">
-        <v>5.04</v>
+        <v>2.8</v>
       </c>
       <c r="I90" s="14">
         <v>50</v>
@@ -10364,144 +10496,149 @@
       <c r="L90" s="129"/>
     </row>
     <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="56">
-        <v>7236</v>
+      <c r="A91" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7157</v>
       </c>
       <c r="B91" s="54" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D91" s="57">
-        <v>1001304507236</v>
+        <v>1001300387157</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.63</v>
       </c>
       <c r="G91" s="23">
-        <f t="shared" si="14"/>
+        <f>E91</f>
         <v>0</v>
       </c>
       <c r="H91" s="14">
-        <v>2.2400000000000002</v>
+        <v>5.04</v>
       </c>
       <c r="I91" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J91" s="29"/>
       <c r="L91" s="129"/>
     </row>
     <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="56">
+      <c r="A92" s="56" t="str">
+        <f t="shared" si="17"/>
         <v>7236</v>
       </c>
       <c r="B92" s="54" t="s">
-        <v>221</v>
+        <v>69</v>
       </c>
       <c r="C92" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="57">
-        <v>1001307357489</v>
+        <v>1001304507236</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" ref="G92" si="15">E92*F92</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H92" s="14"/>
-      <c r="I92" s="14"/>
+      <c r="H92" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I92" s="14">
+        <v>45</v>
+      </c>
       <c r="J92" s="29"/>
       <c r="L92" s="129"/>
     </row>
     <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="56">
-        <v>6787</v>
-      </c>
-      <c r="B93" s="123" t="s">
-        <v>66</v>
+      <c r="A93" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7489</v>
+      </c>
+      <c r="B93" s="54" t="s">
+        <v>221</v>
       </c>
       <c r="C93" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D93" s="57">
-        <v>1001300456787</v>
+        <v>1001307357489</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G93" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="G93" si="19">E93*F93</f>
         <v>0</v>
       </c>
-      <c r="H93" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I93" s="14">
-        <v>45</v>
-      </c>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
       <c r="J93" s="29"/>
       <c r="L93" s="129"/>
     </row>
     <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="56">
-        <v>7166</v>
+      <c r="A94" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>6787</v>
       </c>
       <c r="B94" s="123" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C94" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D94" s="57">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G94" s="23">
-        <f>E94</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H94" s="14">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I94" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J94" s="29"/>
       <c r="L94" s="129"/>
     </row>
-    <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="56">
-        <v>7169</v>
-      </c>
-      <c r="B95" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C95" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D95" s="51">
-        <v>1001303987169</v>
+    <row r="95" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7166</v>
+      </c>
+      <c r="B95" s="123" t="s">
+        <v>72</v>
+      </c>
+      <c r="C95" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="57">
+        <v>1001303987166</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G95" s="23">
-        <f>E95*F95</f>
+        <f>E95</f>
         <v>0</v>
       </c>
       <c r="H95" s="14">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I95" s="14">
         <v>50</v>
@@ -10510,58 +10647,60 @@
       <c r="L95" s="129"/>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="56">
-        <v>5544</v>
+      <c r="A96" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7169</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D96" s="51">
-        <v>1001051875544</v>
+        <v>1001303987169</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G96" s="23">
-        <f>E96</f>
+        <f>E96*F96</f>
         <v>0</v>
       </c>
       <c r="H96" s="14">
-        <v>4.8600000000000003</v>
+        <v>2.8</v>
       </c>
       <c r="I96" s="14">
-        <v>45</v>
-      </c>
-      <c r="J96" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J96" s="29"/>
       <c r="L96" s="129"/>
     </row>
     <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="56">
-        <v>6697</v>
+      <c r="A97" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>5544</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D97" s="51">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G97" s="23">
-        <f t="shared" ref="G97:G104" si="16">E97*F97</f>
+        <f>E97</f>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I97" s="14">
         <v>45</v>
@@ -10570,28 +10709,29 @@
       <c r="L97" s="129"/>
     </row>
     <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="56">
-        <v>7237</v>
+      <c r="A98" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>6697</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="51">
-        <v>1001304497237</v>
+        <v>1001301876697</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G98" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G98:G105" si="20">E98*F98</f>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I98" s="14">
         <v>45</v>
@@ -10600,28 +10740,29 @@
       <c r="L98" s="129"/>
     </row>
     <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="56">
-        <v>7238</v>
+      <c r="A99" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7237</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="51">
-        <v>1001305197238</v>
+        <v>1001304497237</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G99" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>2.48</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I99" s="14">
         <v>45</v>
@@ -10630,58 +10771,60 @@
       <c r="L99" s="129"/>
     </row>
     <row r="100" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="56">
-        <v>7177</v>
+      <c r="A100" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7238</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="51">
-        <v>1001302347177</v>
+        <v>1001305197238</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G100" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I100" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J100" s="49"/>
       <c r="L100" s="129"/>
     </row>
     <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="56">
-        <v>7332</v>
+      <c r="A101" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7177</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D101" s="51">
-        <v>1001301777332</v>
+        <v>1001302347177</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G101" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I101" s="14">
         <v>50</v>
@@ -10690,24 +10833,25 @@
       <c r="L101" s="129"/>
     </row>
     <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="56">
-        <v>7333</v>
+      <c r="A102" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7332</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G102" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H102" s="14">
@@ -10720,56 +10864,56 @@
       <c r="L102" s="129"/>
     </row>
     <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="133">
-        <v>7608</v>
+      <c r="A103" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7333</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D103" s="51">
-        <v>1001304197608</v>
+        <v>1001303987333</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I103" s="14">
-        <v>45</v>
-      </c>
-      <c r="J103" s="52" t="s">
-        <v>210</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J103" s="49"/>
       <c r="L103" s="129"/>
     </row>
-    <row r="104" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="133">
-        <v>7610</v>
+    <row r="104" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7608</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C104" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="51">
-        <v>1001306717610</v>
+        <v>1001304197608</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
         <v>0.1</v>
       </c>
       <c r="G104" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H104" s="14">
@@ -10779,111 +10923,58 @@
         <v>45</v>
       </c>
       <c r="J104" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="L104" s="129"/>
+    </row>
+    <row r="105" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7610</v>
+      </c>
+      <c r="B105" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E105" s="24"/>
+      <c r="F105" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G105" s="23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H105" s="14">
+        <v>1</v>
+      </c>
+      <c r="I105" s="14">
+        <v>45</v>
+      </c>
+      <c r="J105" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="L104" s="129"/>
-    </row>
-    <row r="105" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="47" t="s">
+      <c r="L105" s="129"/>
+    </row>
+    <row r="106" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B105" s="42" t="s">
+      <c r="B106" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C105" s="42"/>
-      <c r="D105" s="42"/>
-      <c r="E105" s="42"/>
-      <c r="F105" s="41"/>
-      <c r="G105" s="42"/>
-      <c r="H105" s="42"/>
-      <c r="I105" s="42"/>
-      <c r="J105" s="43"/>
-      <c r="K105" s="60"/>
-      <c r="L105" s="129"/>
-      <c r="M105" s="129"/>
-      <c r="N105" s="129"/>
-      <c r="O105" s="129"/>
-      <c r="P105" s="129"/>
-      <c r="Q105" s="129"/>
-      <c r="R105" s="129"/>
-      <c r="S105" s="129"/>
-      <c r="T105" s="129"/>
-      <c r="U105" s="129"/>
-      <c r="V105" s="129"/>
-      <c r="W105" s="129"/>
-      <c r="X105" s="129"/>
-      <c r="Y105" s="129"/>
-      <c r="Z105" s="129"/>
-      <c r="AA105" s="129"/>
-      <c r="AB105" s="129"/>
-      <c r="AC105" s="129"/>
-      <c r="AD105" s="129"/>
-      <c r="AE105" s="129"/>
-      <c r="AF105" s="129"/>
-      <c r="AG105" s="129"/>
-      <c r="AH105" s="129"/>
-      <c r="AI105" s="129"/>
-      <c r="AJ105" s="129"/>
-      <c r="AK105" s="129"/>
-      <c r="AL105" s="129"/>
-      <c r="AM105" s="129"/>
-      <c r="AN105" s="129"/>
-      <c r="AO105" s="129"/>
-      <c r="AP105" s="129"/>
-      <c r="AQ105" s="129"/>
-      <c r="AR105" s="129"/>
-      <c r="AS105" s="129"/>
-      <c r="AT105" s="129"/>
-      <c r="AU105" s="129"/>
-      <c r="AV105" s="129"/>
-      <c r="AW105" s="129"/>
-      <c r="AX105" s="129"/>
-      <c r="AY105" s="129"/>
-      <c r="AZ105" s="129"/>
-      <c r="BA105" s="129"/>
-      <c r="BB105" s="129"/>
-      <c r="BC105" s="129"/>
-      <c r="BD105" s="129"/>
-      <c r="BE105" s="129"/>
-      <c r="BF105" s="129"/>
-      <c r="BG105" s="129"/>
-      <c r="BH105" s="129"/>
-      <c r="BI105" s="129"/>
-      <c r="BJ105" s="129"/>
-      <c r="BK105" s="129"/>
-      <c r="BL105" s="129"/>
-      <c r="BM105" s="129"/>
-      <c r="BN105" s="129"/>
-      <c r="BO105" s="129"/>
-    </row>
-    <row r="106" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="56">
-        <v>3582</v>
-      </c>
-      <c r="B106" s="54" t="s">
-        <v>161</v>
-      </c>
-      <c r="C106" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D106" s="57">
-        <v>1001061973582</v>
-      </c>
-      <c r="E106" s="24"/>
-      <c r="F106" s="58">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G106" s="23">
-        <f>E106</f>
-        <v>0</v>
-      </c>
-      <c r="H106" s="117">
-        <v>3.9</v>
-      </c>
-      <c r="I106" s="116">
-        <v>120</v>
-      </c>
-      <c r="J106" s="59"/>
+      <c r="C106" s="42"/>
+      <c r="D106" s="42"/>
+      <c r="E106" s="42"/>
+      <c r="F106" s="41"/>
+      <c r="G106" s="42"/>
+      <c r="H106" s="42"/>
+      <c r="I106" s="42"/>
+      <c r="J106" s="43"/>
       <c r="K106" s="60"/>
       <c r="L106" s="129"/>
       <c r="M106" s="129"/>
@@ -10942,29 +11033,30 @@
       <c r="BN106" s="129"/>
       <c r="BO106" s="129"/>
     </row>
-    <row r="107" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="56">
-        <v>3986</v>
+    <row r="107" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="56" t="str">
+        <f t="shared" ref="A107:A138" si="21">RIGHT(D107,4)</f>
+        <v>3582</v>
       </c>
       <c r="B107" s="54" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="C107" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D107" s="57">
-        <v>1001061973986</v>
+        <v>1001061973582</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="58">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" ref="G107:G112" si="17">E107*F107</f>
+        <f>E107</f>
         <v>0</v>
       </c>
       <c r="H107" s="117">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I107" s="116">
         <v>120</v>
@@ -11028,59 +11120,117 @@
       <c r="BN107" s="129"/>
       <c r="BO107" s="129"/>
     </row>
-    <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="56">
+    <row r="108" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>3986</v>
+      </c>
+      <c r="B108" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="C108" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="57">
+        <v>1001061973986</v>
+      </c>
+      <c r="E108" s="24"/>
+      <c r="F108" s="58">
+        <v>0.25</v>
+      </c>
+      <c r="G108" s="23">
+        <f t="shared" ref="G108:G113" si="22">E108*F108</f>
+        <v>0</v>
+      </c>
+      <c r="H108" s="117">
+        <v>2</v>
+      </c>
+      <c r="I108" s="116">
+        <v>120</v>
+      </c>
+      <c r="J108" s="59"/>
+      <c r="K108" s="60"/>
+      <c r="L108" s="129"/>
+      <c r="M108" s="129"/>
+      <c r="N108" s="129"/>
+      <c r="O108" s="129"/>
+      <c r="P108" s="129"/>
+      <c r="Q108" s="129"/>
+      <c r="R108" s="129"/>
+      <c r="S108" s="129"/>
+      <c r="T108" s="129"/>
+      <c r="U108" s="129"/>
+      <c r="V108" s="129"/>
+      <c r="W108" s="129"/>
+      <c r="X108" s="129"/>
+      <c r="Y108" s="129"/>
+      <c r="Z108" s="129"/>
+      <c r="AA108" s="129"/>
+      <c r="AB108" s="129"/>
+      <c r="AC108" s="129"/>
+      <c r="AD108" s="129"/>
+      <c r="AE108" s="129"/>
+      <c r="AF108" s="129"/>
+      <c r="AG108" s="129"/>
+      <c r="AH108" s="129"/>
+      <c r="AI108" s="129"/>
+      <c r="AJ108" s="129"/>
+      <c r="AK108" s="129"/>
+      <c r="AL108" s="129"/>
+      <c r="AM108" s="129"/>
+      <c r="AN108" s="129"/>
+      <c r="AO108" s="129"/>
+      <c r="AP108" s="129"/>
+      <c r="AQ108" s="129"/>
+      <c r="AR108" s="129"/>
+      <c r="AS108" s="129"/>
+      <c r="AT108" s="129"/>
+      <c r="AU108" s="129"/>
+      <c r="AV108" s="129"/>
+      <c r="AW108" s="129"/>
+      <c r="AX108" s="129"/>
+      <c r="AY108" s="129"/>
+      <c r="AZ108" s="129"/>
+      <c r="BA108" s="129"/>
+      <c r="BB108" s="129"/>
+      <c r="BC108" s="129"/>
+      <c r="BD108" s="129"/>
+      <c r="BE108" s="129"/>
+      <c r="BF108" s="129"/>
+      <c r="BG108" s="129"/>
+      <c r="BH108" s="129"/>
+      <c r="BI108" s="129"/>
+      <c r="BJ108" s="129"/>
+      <c r="BK108" s="129"/>
+      <c r="BL108" s="129"/>
+      <c r="BM108" s="129"/>
+      <c r="BN108" s="129"/>
+      <c r="BO108" s="129"/>
+    </row>
+    <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="56" t="str">
+        <f t="shared" si="21"/>
         <v>5931</v>
       </c>
-      <c r="B108" s="53" t="s">
+      <c r="B109" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="C108" s="50" t="s">
+      <c r="C109" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D108" s="51">
+      <c r="D109" s="51">
         <v>1001060755931</v>
-      </c>
-      <c r="E108" s="24"/>
-      <c r="F108" s="23">
-        <v>0.22</v>
-      </c>
-      <c r="G108" s="23">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H108" s="115">
-        <v>1.76</v>
-      </c>
-      <c r="I108" s="14">
-        <v>120</v>
-      </c>
-      <c r="J108" s="29"/>
-      <c r="L108" s="129"/>
-    </row>
-    <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="56">
-        <v>5708</v>
-      </c>
-      <c r="B109" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C109" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D109" s="51">
-        <v>1001063145708</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" ref="G109:G110" si="18">E109</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H109" s="14">
-        <v>4</v>
+      <c r="H109" s="115">
+        <v>1.76</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -11089,28 +11239,29 @@
       <c r="L109" s="129"/>
     </row>
     <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="56">
-        <v>3287</v>
+      <c r="A110" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>5708</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C110" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D110" s="51">
-        <v>1001060763287</v>
+        <v>1001063145708</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G110:G111" si="23">E110</f>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -11119,28 +11270,29 @@
       <c r="L110" s="129"/>
     </row>
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="56">
-        <v>4993</v>
+      <c r="A111" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>3287</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="C111" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D111" s="51">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I111" s="14">
         <v>120</v>
@@ -11149,24 +11301,25 @@
       <c r="L111" s="129"/>
     </row>
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="56">
-        <v>5483</v>
+      <c r="A112" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>4993</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="C112" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D112" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
         <v>0.25</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H112" s="14">
@@ -11179,28 +11332,29 @@
       <c r="L112" s="129"/>
     </row>
     <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="56">
-        <v>4117</v>
+      <c r="A113" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>5483</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C113" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D113" s="51">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" ref="G113:G114" si="19">E113</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -11209,28 +11363,29 @@
       <c r="L113" s="129"/>
     </row>
     <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="56">
-        <v>614</v>
+      <c r="A114" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>4117</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D114" s="51">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G114:G115" si="24">E114</f>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -11239,28 +11394,29 @@
       <c r="L114" s="129"/>
     </row>
     <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="56">
-        <v>6967</v>
+      <c r="A115" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>0614</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="C115" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" ref="G115:G124" si="20">E115*F115</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I115" s="14">
         <v>120</v>
@@ -11269,24 +11425,25 @@
       <c r="L115" s="129"/>
     </row>
     <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="56">
-        <v>6937</v>
+      <c r="A116" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>6967</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D116" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
         <v>0.25</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G116:G125" si="25">E116*F116</f>
         <v>0</v>
       </c>
       <c r="H116" s="14">
@@ -11299,28 +11456,29 @@
       <c r="L116" s="129"/>
     </row>
     <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="56">
-        <v>7143</v>
+      <c r="A117" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>6937</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D117" s="51">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I117" s="14">
         <v>120</v>
@@ -11329,24 +11487,25 @@
       <c r="L117" s="129"/>
     </row>
     <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="56">
-        <v>7147</v>
+      <c r="A118" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7143</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D118" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
         <v>0.22</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
@@ -11359,58 +11518,60 @@
       <c r="L118" s="129"/>
     </row>
     <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="56">
-        <v>7456</v>
+      <c r="A119" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7147</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I119" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J119" s="29"/>
       <c r="L119" s="129"/>
     </row>
     <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="56">
-        <v>7364</v>
+      <c r="A120" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7456</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="51">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I120" s="14">
         <v>90</v>
@@ -11419,24 +11580,25 @@
       <c r="L120" s="129"/>
     </row>
     <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="56">
-        <v>7383</v>
+      <c r="A121" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7364</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D121" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
         <v>0.22</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
@@ -11449,58 +11611,60 @@
       <c r="L121" s="129"/>
     </row>
     <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="56">
-        <v>7317</v>
+      <c r="A122" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7383</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D122" s="51">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I122" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J122" s="29"/>
       <c r="L122" s="129"/>
     </row>
     <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="56">
-        <v>7318</v>
+      <c r="A123" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7317</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D123" s="51">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I123" s="14">
         <v>120</v>
@@ -11509,28 +11673,29 @@
       <c r="L123" s="129"/>
     </row>
     <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="56">
-        <v>7316</v>
+      <c r="A124" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7318</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="51">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I124" s="14">
         <v>120</v>
@@ -11539,54 +11704,56 @@
       <c r="L124" s="129"/>
     </row>
     <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="56">
-        <v>6832</v>
+      <c r="A125" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7316</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D125" s="51">
-        <v>1001065616832</v>
+        <v>1001060727316</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G125" s="23">
-        <f t="shared" ref="G125:G126" si="21">E125</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I125" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J125" s="29"/>
       <c r="L125" s="129"/>
     </row>
     <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="56">
-        <v>7299</v>
+      <c r="A126" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>6832</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C126" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D126" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
         <v>0.215</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G126:G127" si="26">E126</f>
         <v>0</v>
       </c>
       <c r="H126" s="14">
@@ -11599,210 +11766,217 @@
       <c r="L126" s="129"/>
     </row>
     <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="56">
-        <v>7386</v>
+      <c r="A127" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7299</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D127" s="51">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G127" s="23">
-        <f t="shared" ref="G127:G137" si="22">E127*F127</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I127" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J127" s="29"/>
       <c r="L127" s="129"/>
     </row>
     <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="133">
-        <v>7613</v>
+      <c r="A128" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7386</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D128" s="51">
-        <v>1001061977613</v>
+        <v>1001067017386</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G128" s="23">
+        <f t="shared" ref="G128:G138" si="27">E128*F128</f>
+        <v>0</v>
+      </c>
+      <c r="H128" s="14">
+        <v>1.35</v>
+      </c>
+      <c r="I128" s="14">
+        <v>90</v>
+      </c>
+      <c r="J128" s="29"/>
+      <c r="L128" s="129"/>
+    </row>
+    <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7613</v>
+      </c>
+      <c r="B129" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="C129" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" s="51">
+        <v>1001061977613</v>
+      </c>
+      <c r="E129" s="24"/>
+      <c r="F129" s="23">
         <v>0.1</v>
       </c>
-      <c r="G128" s="23">
-        <f t="shared" si="22"/>
+      <c r="G129" s="23">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H128" s="14">
+      <c r="H129" s="14">
         <v>1</v>
       </c>
-      <c r="I128" s="14">
+      <c r="I129" s="14">
         <v>60</v>
       </c>
-      <c r="J128" s="52" t="s">
+      <c r="J129" s="52" t="s">
         <v>215</v>
       </c>
-      <c r="L128" s="129"/>
-    </row>
-    <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="135">
+      <c r="L129" s="129"/>
+    </row>
+    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="56" t="str">
+        <f t="shared" si="21"/>
         <v>6834</v>
       </c>
-      <c r="B129" s="136" t="s">
+      <c r="B130" s="134" t="s">
         <v>149</v>
       </c>
-      <c r="C129" s="137" t="s">
+      <c r="C130" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="D129" s="138">
+      <c r="D130" s="136">
         <v>1001203146834</v>
       </c>
-      <c r="E129" s="139"/>
-      <c r="F129" s="140">
+      <c r="E130" s="137"/>
+      <c r="F130" s="138">
         <v>0.1</v>
       </c>
-      <c r="G129" s="140">
-        <f t="shared" si="22"/>
+      <c r="G130" s="138">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H129" s="141">
+      <c r="H130" s="139">
         <v>1</v>
       </c>
-      <c r="I129" s="141">
+      <c r="I130" s="139">
         <v>60</v>
       </c>
-      <c r="J129" s="141" t="s">
+      <c r="J130" s="139" t="s">
         <v>214</v>
       </c>
-      <c r="L129" s="129"/>
-    </row>
-    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="56">
+      <c r="L130" s="129"/>
+    </row>
+    <row r="131" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="56" t="str">
+        <f t="shared" si="21"/>
         <v>7382</v>
       </c>
-      <c r="B130" s="53" t="s">
+      <c r="B131" s="53" t="s">
         <v>85</v>
-      </c>
-      <c r="C130" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D130" s="51">
-        <v>1001203117382</v>
-      </c>
-      <c r="E130" s="24"/>
-      <c r="F130" s="23">
-        <v>0.12</v>
-      </c>
-      <c r="G130" s="23">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="H130" s="14">
-        <v>0.96</v>
-      </c>
-      <c r="I130" s="14">
-        <v>60</v>
-      </c>
-      <c r="J130" s="29"/>
-      <c r="L130" s="129"/>
-    </row>
-    <row r="131" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="133">
-        <v>7616</v>
-      </c>
-      <c r="B131" s="53" t="s">
-        <v>219</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="51">
-        <v>1001062507616</v>
+        <v>1001203117382</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G131" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H131" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I131" s="14">
         <v>60</v>
       </c>
-      <c r="J131" s="52" t="s">
-        <v>216</v>
-      </c>
+      <c r="J131" s="29"/>
       <c r="L131" s="129"/>
     </row>
     <row r="132" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="56">
-        <v>6221</v>
+      <c r="A132" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7616</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D132" s="51">
-        <v>1001205376221</v>
+        <v>1001062507616</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
       </c>
-      <c r="J132" s="29"/>
+      <c r="J132" s="52" t="s">
+        <v>216</v>
+      </c>
       <c r="L132" s="129"/>
     </row>
     <row r="133" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="56">
-        <v>6222</v>
+      <c r="A133" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>6221</v>
       </c>
       <c r="B133" s="53" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C133" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D133" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="23">
         <v>0.09</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H133" s="14">
@@ -11815,28 +11989,29 @@
       <c r="L133" s="129"/>
     </row>
     <row r="134" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="56">
-        <v>6965</v>
+      <c r="A134" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>6222</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D134" s="51">
-        <v>1001206356965</v>
+        <v>1001205386222</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H134" s="14">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="I134" s="14">
         <v>60</v>
@@ -11845,28 +12020,29 @@
       <c r="L134" s="129"/>
     </row>
     <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="56">
-        <v>6557</v>
+      <c r="A135" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>6965</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D135" s="51">
-        <v>1001200756557</v>
+        <v>1001206356965</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="23">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G135" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H135" s="14">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I135" s="14">
         <v>60</v>
@@ -11875,28 +12051,29 @@
       <c r="L135" s="129"/>
     </row>
     <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="56">
-        <v>5679</v>
+      <c r="A136" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>6557</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C136" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D136" s="51">
-        <v>1001190765679</v>
+        <v>1001200756557</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G136" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H136" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="14">
         <v>60</v>
@@ -11904,194 +12081,142 @@
       <c r="J136" s="29"/>
       <c r="L136" s="129"/>
     </row>
-    <row r="137" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="133">
-        <v>7626</v>
+    <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>5679</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="51">
-        <v>1001066607626</v>
+        <v>1001190765679</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G137" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
       </c>
-      <c r="J137" s="52" t="s">
+      <c r="J137" s="29"/>
+      <c r="L137" s="129"/>
+    </row>
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7626</v>
+      </c>
+      <c r="B138" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="C138" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="51">
+        <v>1001066607626</v>
+      </c>
+      <c r="E138" s="24"/>
+      <c r="F138" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G138" s="23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="H138" s="14">
+        <v>1</v>
+      </c>
+      <c r="I138" s="14">
+        <v>60</v>
+      </c>
+      <c r="J138" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="L137" s="129"/>
-    </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="47" t="s">
+      <c r="L138" s="129"/>
+    </row>
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B138" s="42" t="s">
+      <c r="B139" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C138" s="42"/>
-      <c r="D138" s="42"/>
-      <c r="E138" s="42"/>
-      <c r="F138" s="41"/>
-      <c r="G138" s="42"/>
-      <c r="H138" s="42"/>
-      <c r="I138" s="42"/>
-      <c r="J138" s="43"/>
-      <c r="L138" s="129"/>
-    </row>
-    <row r="139" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="56">
+      <c r="C139" s="42"/>
+      <c r="D139" s="42"/>
+      <c r="E139" s="42"/>
+      <c r="F139" s="41"/>
+      <c r="G139" s="42"/>
+      <c r="H139" s="42"/>
+      <c r="I139" s="42"/>
+      <c r="J139" s="43"/>
+      <c r="L139" s="129"/>
+    </row>
+    <row r="140" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="56" t="str">
+        <f t="shared" ref="A140:A152" si="28">RIGHT(D140,4)</f>
         <v>4584</v>
       </c>
-      <c r="B139" s="121" t="s">
+      <c r="B140" s="121" t="s">
         <v>125</v>
       </c>
-      <c r="C139" s="50" t="s">
+      <c r="C140" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D139" s="120">
+      <c r="D140" s="120">
         <v>1001092674584</v>
       </c>
-      <c r="E139" s="24"/>
-      <c r="F139" s="23">
+      <c r="E140" s="24"/>
+      <c r="F140" s="23">
         <v>2.5</v>
       </c>
-      <c r="G139" s="23">
-        <f>E139</f>
+      <c r="G140" s="23">
+        <f>E140</f>
         <v>0</v>
       </c>
-      <c r="H139" s="14">
+      <c r="H140" s="14">
         <v>7.5</v>
       </c>
-      <c r="I139" s="14">
+      <c r="I140" s="14">
         <v>60</v>
       </c>
-      <c r="J139" s="29"/>
-      <c r="L139" s="129"/>
-    </row>
-    <row r="140" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="56">
+      <c r="J140" s="29"/>
+      <c r="L140" s="129"/>
+    </row>
+    <row r="141" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="56" t="str">
+        <f t="shared" si="28"/>
         <v>6495</v>
       </c>
-      <c r="B140" s="122" t="s">
+      <c r="B141" s="122" t="s">
         <v>97</v>
       </c>
-      <c r="C140" s="55" t="s">
+      <c r="C141" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D140" s="70">
+      <c r="D141" s="70">
         <v>1001092436495</v>
-      </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="G140" s="23">
-        <f>E140*F140</f>
-        <v>0</v>
-      </c>
-      <c r="H140" s="59">
-        <v>1.8</v>
-      </c>
-      <c r="I140" s="59">
-        <v>45</v>
-      </c>
-      <c r="J140" s="59"/>
-      <c r="K140" s="60"/>
-      <c r="L140" s="129"/>
-      <c r="M140" s="129"/>
-      <c r="N140" s="129"/>
-      <c r="O140" s="129"/>
-      <c r="P140" s="129"/>
-      <c r="Q140" s="129"/>
-      <c r="R140" s="129"/>
-      <c r="S140" s="129"/>
-      <c r="T140" s="129"/>
-      <c r="U140" s="129"/>
-      <c r="V140" s="129"/>
-      <c r="W140" s="129"/>
-      <c r="X140" s="129"/>
-      <c r="Y140" s="129"/>
-      <c r="Z140" s="129"/>
-      <c r="AA140" s="129"/>
-      <c r="AB140" s="129"/>
-      <c r="AC140" s="129"/>
-      <c r="AD140" s="129"/>
-      <c r="AE140" s="129"/>
-      <c r="AF140" s="129"/>
-      <c r="AG140" s="129"/>
-      <c r="AH140" s="129"/>
-      <c r="AI140" s="129"/>
-      <c r="AJ140" s="129"/>
-      <c r="AK140" s="129"/>
-      <c r="AL140" s="129"/>
-      <c r="AM140" s="129"/>
-      <c r="AN140" s="129"/>
-      <c r="AO140" s="129"/>
-      <c r="AP140" s="129"/>
-      <c r="AQ140" s="129"/>
-      <c r="AR140" s="129"/>
-      <c r="AS140" s="129"/>
-      <c r="AT140" s="129"/>
-      <c r="AU140" s="129"/>
-      <c r="AV140" s="129"/>
-      <c r="AW140" s="129"/>
-      <c r="AX140" s="129"/>
-      <c r="AY140" s="129"/>
-      <c r="AZ140" s="129"/>
-      <c r="BA140" s="129"/>
-      <c r="BB140" s="129"/>
-      <c r="BC140" s="129"/>
-      <c r="BD140" s="129"/>
-      <c r="BE140" s="129"/>
-      <c r="BF140" s="129"/>
-      <c r="BG140" s="129"/>
-      <c r="BH140" s="129"/>
-      <c r="BI140" s="129"/>
-      <c r="BJ140" s="129"/>
-      <c r="BK140" s="129"/>
-      <c r="BL140" s="129"/>
-      <c r="BM140" s="129"/>
-      <c r="BN140" s="129"/>
-      <c r="BO140" s="129"/>
-    </row>
-    <row r="141" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="56">
-        <v>6470</v>
-      </c>
-      <c r="B141" s="118" t="s">
-        <v>126</v>
-      </c>
-      <c r="C141" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D141" s="70">
-        <v>1001092436470</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="58">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G141" s="23">
-        <f t="shared" ref="G141:G142" si="23">E141</f>
+        <f>E141*F141</f>
         <v>0</v>
       </c>
       <c r="H141" s="59">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I141" s="59">
         <v>45</v>
@@ -12156,31 +12281,32 @@
       <c r="BO141" s="129"/>
     </row>
     <row r="142" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="56">
-        <v>5452</v>
+      <c r="A142" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>6470</v>
       </c>
       <c r="B142" s="118" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C142" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D142" s="70">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="58">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="G142" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G142:G143" si="29">E142</f>
         <v>0</v>
       </c>
       <c r="H142" s="59">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="I142" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J142" s="59"/>
       <c r="K142" s="60"/>
@@ -12242,28 +12368,29 @@
       <c r="BO142" s="129"/>
     </row>
     <row r="143" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="56">
-        <v>3215</v>
+      <c r="A143" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>5452</v>
       </c>
       <c r="B143" s="118" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C143" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D143" s="70">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="58">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G143" s="23">
-        <f>E143*F143</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H143" s="59">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I143" s="59">
         <v>60</v>
@@ -12328,28 +12455,29 @@
       <c r="BO143" s="129"/>
     </row>
     <row r="144" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="56">
-        <v>6866</v>
+      <c r="A144" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>3215</v>
       </c>
       <c r="B144" s="118" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C144" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D144" s="70">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="58">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G144" s="23">
-        <f>E144</f>
+        <f>E144*F144</f>
         <v>0</v>
       </c>
       <c r="H144" s="59">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I144" s="59">
         <v>60</v>
@@ -12413,29 +12541,30 @@
       <c r="BN144" s="129"/>
       <c r="BO144" s="129"/>
     </row>
-    <row r="145" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="56">
-        <v>5495</v>
-      </c>
-      <c r="B145" s="54" t="s">
-        <v>96</v>
+    <row r="145" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>6866</v>
+      </c>
+      <c r="B145" s="118" t="s">
+        <v>93</v>
       </c>
       <c r="C145" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D145" s="119">
-        <v>1001093345495</v>
+        <v>23</v>
+      </c>
+      <c r="D145" s="70">
+        <v>1001095716866</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="58">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" ref="G145:G147" si="24">E145*F145</f>
+        <f>E145</f>
         <v>0</v>
       </c>
       <c r="H145" s="59">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I145" s="59">
         <v>60</v>
@@ -12500,31 +12629,32 @@
       <c r="BO145" s="129"/>
     </row>
     <row r="146" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="56">
-        <v>7377</v>
+      <c r="A146" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>5495</v>
       </c>
       <c r="B146" s="54" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C146" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D146" s="119">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="58">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G146" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G146:G149" si="30">E146*F146</f>
         <v>0</v>
       </c>
       <c r="H146" s="59">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I146" s="59">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J146" s="59"/>
       <c r="K146" s="60"/>
@@ -12586,28 +12716,29 @@
       <c r="BO146" s="129"/>
     </row>
     <row r="147" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="56">
-        <v>6925</v>
+      <c r="A147" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>7377</v>
       </c>
       <c r="B147" s="54" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C147" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D147" s="119">
-        <v>1001095226925</v>
+        <v>1001095027377</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="58">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H147" s="59">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I147" s="59">
         <v>45</v>
@@ -12671,33 +12802,30 @@
       <c r="BN147" s="129"/>
       <c r="BO147" s="129"/>
     </row>
-    <row r="148" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="56">
-        <v>6025</v>
+    <row r="148" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>6411</v>
       </c>
       <c r="B148" s="54" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="C148" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D148" s="119">
-        <v>1001094966025</v>
+        <v>1001093316411</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="58">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f>E148</f>
+        <f t="shared" ref="G148" si="31">E148*F148</f>
         <v>0</v>
       </c>
-      <c r="H148" s="59">
-        <v>6</v>
-      </c>
-      <c r="I148" s="59">
-        <v>60</v>
-      </c>
+      <c r="H148" s="59"/>
+      <c r="I148" s="59"/>
       <c r="J148" s="59"/>
       <c r="K148" s="60"/>
       <c r="L148" s="129"/>
@@ -12757,36 +12885,35 @@
       <c r="BN148" s="129"/>
       <c r="BO148" s="129"/>
     </row>
-    <row r="149" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="133">
-        <v>7647</v>
+    <row r="149" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>6925</v>
       </c>
       <c r="B149" s="54" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="C149" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="119">
-        <v>1001097747647</v>
+        <v>1001095226925</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="58">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G149" s="23">
-        <f>E149*F149</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H149" s="59">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="I149" s="59">
-        <v>30</v>
-      </c>
-      <c r="J149" s="132" t="s">
-        <v>208</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J149" s="59"/>
       <c r="K149" s="60"/>
       <c r="L149" s="129"/>
       <c r="M149" s="129"/>
@@ -12845,36 +12972,35 @@
       <c r="BN149" s="129"/>
       <c r="BO149" s="129"/>
     </row>
-    <row r="150" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="133">
-        <v>7651</v>
+    <row r="150" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>6025</v>
       </c>
       <c r="B150" s="54" t="s">
-        <v>207</v>
+        <v>128</v>
       </c>
       <c r="C150" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D150" s="119">
-        <v>1001097767651</v>
+        <v>1001094966025</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="58">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="G150" s="23">
-        <f>E150*F150</f>
+        <f>E150</f>
         <v>0</v>
       </c>
       <c r="H150" s="59">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I150" s="59">
-        <v>30</v>
-      </c>
-      <c r="J150" s="132" t="s">
-        <v>208</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J150" s="59"/>
       <c r="K150" s="60"/>
       <c r="L150" s="129"/>
       <c r="M150" s="129"/>
@@ -12933,288 +13059,413 @@
       <c r="BN150" s="129"/>
       <c r="BO150" s="129"/>
     </row>
-    <row r="151" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="47" t="s">
+    <row r="151" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>7647</v>
+      </c>
+      <c r="B151" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C151" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" s="119">
+        <v>1001097747647</v>
+      </c>
+      <c r="E151" s="24"/>
+      <c r="F151" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G151" s="23">
+        <f>E151*F151</f>
+        <v>0</v>
+      </c>
+      <c r="H151" s="59">
+        <v>1</v>
+      </c>
+      <c r="I151" s="59">
+        <v>30</v>
+      </c>
+      <c r="J151" s="132" t="s">
+        <v>208</v>
+      </c>
+      <c r="K151" s="60"/>
+      <c r="L151" s="129"/>
+      <c r="M151" s="129"/>
+      <c r="N151" s="129"/>
+      <c r="O151" s="129"/>
+      <c r="P151" s="129"/>
+      <c r="Q151" s="129"/>
+      <c r="R151" s="129"/>
+      <c r="S151" s="129"/>
+      <c r="T151" s="129"/>
+      <c r="U151" s="129"/>
+      <c r="V151" s="129"/>
+      <c r="W151" s="129"/>
+      <c r="X151" s="129"/>
+      <c r="Y151" s="129"/>
+      <c r="Z151" s="129"/>
+      <c r="AA151" s="129"/>
+      <c r="AB151" s="129"/>
+      <c r="AC151" s="129"/>
+      <c r="AD151" s="129"/>
+      <c r="AE151" s="129"/>
+      <c r="AF151" s="129"/>
+      <c r="AG151" s="129"/>
+      <c r="AH151" s="129"/>
+      <c r="AI151" s="129"/>
+      <c r="AJ151" s="129"/>
+      <c r="AK151" s="129"/>
+      <c r="AL151" s="129"/>
+      <c r="AM151" s="129"/>
+      <c r="AN151" s="129"/>
+      <c r="AO151" s="129"/>
+      <c r="AP151" s="129"/>
+      <c r="AQ151" s="129"/>
+      <c r="AR151" s="129"/>
+      <c r="AS151" s="129"/>
+      <c r="AT151" s="129"/>
+      <c r="AU151" s="129"/>
+      <c r="AV151" s="129"/>
+      <c r="AW151" s="129"/>
+      <c r="AX151" s="129"/>
+      <c r="AY151" s="129"/>
+      <c r="AZ151" s="129"/>
+      <c r="BA151" s="129"/>
+      <c r="BB151" s="129"/>
+      <c r="BC151" s="129"/>
+      <c r="BD151" s="129"/>
+      <c r="BE151" s="129"/>
+      <c r="BF151" s="129"/>
+      <c r="BG151" s="129"/>
+      <c r="BH151" s="129"/>
+      <c r="BI151" s="129"/>
+      <c r="BJ151" s="129"/>
+      <c r="BK151" s="129"/>
+      <c r="BL151" s="129"/>
+      <c r="BM151" s="129"/>
+      <c r="BN151" s="129"/>
+      <c r="BO151" s="129"/>
+    </row>
+    <row r="152" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="56" t="str">
+        <f t="shared" si="28"/>
+        <v>7651</v>
+      </c>
+      <c r="B152" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="C152" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="119">
+        <v>1001097767651</v>
+      </c>
+      <c r="E152" s="24"/>
+      <c r="F152" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G152" s="23">
+        <f>E152*F152</f>
+        <v>0</v>
+      </c>
+      <c r="H152" s="59">
+        <v>1</v>
+      </c>
+      <c r="I152" s="59">
+        <v>30</v>
+      </c>
+      <c r="J152" s="132" t="s">
+        <v>208</v>
+      </c>
+      <c r="K152" s="60"/>
+      <c r="L152" s="129"/>
+      <c r="M152" s="129"/>
+      <c r="N152" s="129"/>
+      <c r="O152" s="129"/>
+      <c r="P152" s="129"/>
+      <c r="Q152" s="129"/>
+      <c r="R152" s="129"/>
+      <c r="S152" s="129"/>
+      <c r="T152" s="129"/>
+      <c r="U152" s="129"/>
+      <c r="V152" s="129"/>
+      <c r="W152" s="129"/>
+      <c r="X152" s="129"/>
+      <c r="Y152" s="129"/>
+      <c r="Z152" s="129"/>
+      <c r="AA152" s="129"/>
+      <c r="AB152" s="129"/>
+      <c r="AC152" s="129"/>
+      <c r="AD152" s="129"/>
+      <c r="AE152" s="129"/>
+      <c r="AF152" s="129"/>
+      <c r="AG152" s="129"/>
+      <c r="AH152" s="129"/>
+      <c r="AI152" s="129"/>
+      <c r="AJ152" s="129"/>
+      <c r="AK152" s="129"/>
+      <c r="AL152" s="129"/>
+      <c r="AM152" s="129"/>
+      <c r="AN152" s="129"/>
+      <c r="AO152" s="129"/>
+      <c r="AP152" s="129"/>
+      <c r="AQ152" s="129"/>
+      <c r="AR152" s="129"/>
+      <c r="AS152" s="129"/>
+      <c r="AT152" s="129"/>
+      <c r="AU152" s="129"/>
+      <c r="AV152" s="129"/>
+      <c r="AW152" s="129"/>
+      <c r="AX152" s="129"/>
+      <c r="AY152" s="129"/>
+      <c r="AZ152" s="129"/>
+      <c r="BA152" s="129"/>
+      <c r="BB152" s="129"/>
+      <c r="BC152" s="129"/>
+      <c r="BD152" s="129"/>
+      <c r="BE152" s="129"/>
+      <c r="BF152" s="129"/>
+      <c r="BG152" s="129"/>
+      <c r="BH152" s="129"/>
+      <c r="BI152" s="129"/>
+      <c r="BJ152" s="129"/>
+      <c r="BK152" s="129"/>
+      <c r="BL152" s="129"/>
+      <c r="BM152" s="129"/>
+      <c r="BN152" s="129"/>
+      <c r="BO152" s="129"/>
+    </row>
+    <row r="153" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B151" s="42" t="s">
+      <c r="B153" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C151" s="42"/>
-      <c r="D151" s="42"/>
-      <c r="E151" s="42"/>
-      <c r="F151" s="41"/>
-      <c r="G151" s="42"/>
-      <c r="H151" s="42"/>
-      <c r="I151" s="42"/>
-      <c r="J151" s="43"/>
-      <c r="L151" s="129"/>
-    </row>
-    <row r="152" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="56">
+      <c r="C153" s="42"/>
+      <c r="D153" s="42"/>
+      <c r="E153" s="42"/>
+      <c r="F153" s="41"/>
+      <c r="G153" s="42"/>
+      <c r="H153" s="42"/>
+      <c r="I153" s="42"/>
+      <c r="J153" s="43"/>
+      <c r="L153" s="129"/>
+    </row>
+    <row r="154" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="56" t="str">
+        <f t="shared" ref="A154:A165" si="32">RIGHT(D154,4)</f>
         <v>7090</v>
       </c>
-      <c r="B152" s="35" t="s">
+      <c r="B154" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C152" s="50" t="s">
+      <c r="C154" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D152" s="51">
+      <c r="D154" s="51">
         <v>1001084217090</v>
-      </c>
-      <c r="E152" s="24"/>
-      <c r="F152" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G152" s="23">
-        <f t="shared" ref="G152:G153" si="25">E152*F152</f>
-        <v>0</v>
-      </c>
-      <c r="H152" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I152" s="14">
-        <v>50</v>
-      </c>
-      <c r="J152" s="29"/>
-      <c r="L152" s="129"/>
-    </row>
-    <row r="153" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="56">
-        <v>7187</v>
-      </c>
-      <c r="B153" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C153" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D153" s="51">
-        <v>1001085637187</v>
-      </c>
-      <c r="E153" s="24"/>
-      <c r="F153" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G153" s="23">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H153" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I153" s="14">
-        <v>50</v>
-      </c>
-      <c r="J153" s="29"/>
-      <c r="L153" s="129"/>
-    </row>
-    <row r="154" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="133">
-        <v>6008</v>
-      </c>
-      <c r="B154" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="C154" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D154" s="51">
-        <v>1001084856008</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
         <v>0.3</v>
       </c>
       <c r="G154" s="23">
-        <f>E154</f>
+        <f t="shared" ref="G154:G155" si="33">E154*F154</f>
         <v>0</v>
       </c>
       <c r="H154" s="14">
         <v>1.8</v>
       </c>
       <c r="I154" s="14">
-        <v>40</v>
-      </c>
-      <c r="J154" s="132" t="s">
-        <v>208</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J154" s="29"/>
       <c r="L154" s="129"/>
     </row>
     <row r="155" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="56">
-        <v>6620</v>
+      <c r="A155" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>7187</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D155" s="51">
-        <v>1001081596620</v>
+        <v>1001085637187</v>
       </c>
       <c r="E155" s="24"/>
       <c r="F155" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G155" s="23">
-        <f>E155</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="H155" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I155" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J155" s="29"/>
       <c r="L155" s="129"/>
     </row>
     <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="56">
-        <v>7103</v>
+      <c r="A156" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>6008</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D156" s="51">
-        <v>1001223297103</v>
+        <v>1001084856008</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="G156" s="23">
-        <f t="shared" ref="G156:G163" si="26">E156*F156</f>
+        <f>E156</f>
         <v>0</v>
       </c>
       <c r="H156" s="14">
         <v>1.8</v>
       </c>
       <c r="I156" s="14">
-        <v>50</v>
-      </c>
-      <c r="J156" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J156" s="132" t="s">
+        <v>208</v>
+      </c>
       <c r="L156" s="129"/>
     </row>
     <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="56">
-        <v>7092</v>
+      <c r="A157" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>6620</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D157" s="51">
-        <v>1001223297092</v>
+        <v>1001081596620</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.14000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="26"/>
+        <f>E157</f>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1.4</v>
+        <v>3.15</v>
       </c>
       <c r="I157" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J157" s="29"/>
       <c r="L157" s="129"/>
     </row>
     <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="56">
-        <v>6228</v>
+      <c r="A158" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>7103</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001225416228</v>
+        <v>1001223297103</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="G158" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G158:G165" si="34">E158*F158</f>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="I158" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J158" s="29"/>
       <c r="L158" s="129"/>
     </row>
     <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="56">
-        <v>6448</v>
+      <c r="A159" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>7092</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D159" s="51">
-        <v>1001234146448</v>
+        <v>1001223297092</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G159" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I159" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J159" s="29"/>
       <c r="L159" s="129"/>
     </row>
     <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="56">
-        <v>6208</v>
+      <c r="A160" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>6228</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D160" s="51">
-        <v>1001220226208</v>
+        <v>1001225416228</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G160" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -13223,58 +13474,60 @@
       <c r="L160" s="129"/>
     </row>
     <row r="161" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="56">
-        <v>6754</v>
+      <c r="A161" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>6448</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D161" s="51">
-        <v>1001225406754</v>
+        <v>1001234146448</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G161" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I161" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J161" s="29"/>
       <c r="L161" s="129"/>
     </row>
     <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="56">
-        <v>6279</v>
+      <c r="A162" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>6208</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D162" s="51">
-        <v>1001220286279</v>
+        <v>1001220226208</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="23">
         <v>0.15</v>
       </c>
       <c r="G162" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="H162" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I162" s="14">
         <v>45</v>
@@ -13282,79 +13535,122 @@
       <c r="J162" s="29"/>
       <c r="L162" s="129"/>
     </row>
-    <row r="163" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="133">
-        <v>7612</v>
+    <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>6754</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C163" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D163" s="51">
-        <v>1001453907612</v>
+        <v>1001225406754</v>
       </c>
       <c r="E163" s="24"/>
       <c r="F163" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G163" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="H163" s="14">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="I163" s="14">
         <v>60</v>
       </c>
-      <c r="J163" s="52" t="s">
+      <c r="J163" s="29"/>
+      <c r="L163" s="129"/>
+    </row>
+    <row r="164" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>6279</v>
+      </c>
+      <c r="B164" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C164" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164" s="51">
+        <v>1001220286279</v>
+      </c>
+      <c r="E164" s="24"/>
+      <c r="F164" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G164" s="23">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H164" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I164" s="14">
+        <v>45</v>
+      </c>
+      <c r="J164" s="29"/>
+      <c r="L164" s="129"/>
+    </row>
+    <row r="165" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="56" t="str">
+        <f t="shared" si="32"/>
+        <v>7612</v>
+      </c>
+      <c r="B165" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C165" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D165" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E165" s="24"/>
+      <c r="F165" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G165" s="23">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H165" s="14">
+        <v>1</v>
+      </c>
+      <c r="I165" s="14">
+        <v>60</v>
+      </c>
+      <c r="J165" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="L163" s="129"/>
-    </row>
-    <row r="164" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="48"/>
-      <c r="B164" s="45" t="s">
+      <c r="L165" s="129"/>
+    </row>
+    <row r="166" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="48"/>
+      <c r="B166" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C164" s="16"/>
-      <c r="D164" s="36"/>
-      <c r="E164" s="17">
-        <f>SUM(E10:E163)</f>
+      <c r="C166" s="16"/>
+      <c r="D166" s="36"/>
+      <c r="E166" s="17">
+        <f>SUM(E10:E165)</f>
         <v>0</v>
       </c>
-      <c r="F164" s="17"/>
-      <c r="G164" s="17">
-        <f>SUM(G11:G163)</f>
+      <c r="F166" s="17"/>
+      <c r="G166" s="17">
+        <f>SUM(G11:G165)</f>
         <v>0</v>
       </c>
-      <c r="H164" s="17"/>
-      <c r="I164" s="17"/>
-      <c r="J164" s="17"/>
-    </row>
-    <row r="165" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="37"/>
-      <c r="C165" s="18"/>
-      <c r="D165" s="40"/>
-      <c r="F165" s="19"/>
-      <c r="G165" s="19"/>
-      <c r="H165" s="20"/>
-      <c r="I165" s="20"/>
-      <c r="J165" s="21"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B166" s="37"/>
-      <c r="C166" s="18"/>
-      <c r="D166" s="40"/>
-      <c r="F166" s="19"/>
-      <c r="G166" s="19"/>
-      <c r="H166" s="20"/>
-      <c r="I166" s="20"/>
-      <c r="J166" s="21"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H166" s="17"/>
+      <c r="I166" s="17"/>
+      <c r="J166" s="17"/>
+    </row>
+    <row r="167" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B167" s="37"/>
       <c r="C167" s="18"/>
       <c r="D167" s="40"/>
@@ -13396,55 +13692,55 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
-      <c r="C171" s="62"/>
-      <c r="D171" s="63"/>
-      <c r="E171" s="64"/>
-      <c r="F171" s="65"/>
-      <c r="G171" s="65"/>
-      <c r="H171" s="66"/>
-      <c r="I171" s="66"/>
+      <c r="C171" s="18"/>
+      <c r="D171" s="40"/>
+      <c r="F171" s="19"/>
+      <c r="G171" s="19"/>
+      <c r="H171" s="20"/>
+      <c r="I171" s="20"/>
       <c r="J171" s="21"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B172" s="37"/>
-      <c r="C172" s="62"/>
-      <c r="D172" s="63"/>
-      <c r="E172" s="64"/>
-      <c r="F172" s="65"/>
-      <c r="G172" s="65"/>
-      <c r="H172" s="66"/>
-      <c r="I172" s="66"/>
+      <c r="C172" s="18"/>
+      <c r="D172" s="40"/>
+      <c r="F172" s="19"/>
+      <c r="G172" s="19"/>
+      <c r="H172" s="20"/>
+      <c r="I172" s="20"/>
       <c r="J172" s="21"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
       <c r="C173" s="62"/>
-      <c r="D173" s="67"/>
-      <c r="E173" s="68"/>
-      <c r="F173" s="67"/>
-      <c r="G173" s="69"/>
-      <c r="H173" s="70"/>
-      <c r="I173" s="71"/>
+      <c r="D173" s="63"/>
+      <c r="E173" s="64"/>
+      <c r="F173" s="65"/>
+      <c r="G173" s="65"/>
+      <c r="H173" s="66"/>
+      <c r="I173" s="66"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
-      <c r="C174" s="18"/>
-      <c r="D174" s="40"/>
-      <c r="F174" s="19"/>
-      <c r="G174" s="19"/>
-      <c r="H174" s="20"/>
-      <c r="I174" s="20"/>
+      <c r="C174" s="62"/>
+      <c r="D174" s="63"/>
+      <c r="E174" s="64"/>
+      <c r="F174" s="65"/>
+      <c r="G174" s="65"/>
+      <c r="H174" s="66"/>
+      <c r="I174" s="66"/>
       <c r="J174" s="21"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B175" s="37"/>
-      <c r="C175" s="18"/>
-      <c r="D175" s="40"/>
-      <c r="F175" s="19"/>
-      <c r="G175" s="19"/>
-      <c r="H175" s="20"/>
-      <c r="I175" s="20"/>
+      <c r="C175" s="62"/>
+      <c r="D175" s="67"/>
+      <c r="E175" s="68"/>
+      <c r="F175" s="67"/>
+      <c r="G175" s="69"/>
+      <c r="H175" s="70"/>
+      <c r="I175" s="71"/>
       <c r="J175" s="21"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -28577,13 +28873,33 @@
       <c r="I1688" s="20"/>
       <c r="J1688" s="21"/>
     </row>
+    <row r="1689" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1689" s="37"/>
+      <c r="C1689" s="18"/>
+      <c r="D1689" s="40"/>
+      <c r="F1689" s="19"/>
+      <c r="G1689" s="19"/>
+      <c r="H1689" s="20"/>
+      <c r="I1689" s="20"/>
+      <c r="J1689" s="21"/>
+    </row>
+    <row r="1690" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1690" s="37"/>
+      <c r="C1690" s="18"/>
+      <c r="D1690" s="40"/>
+      <c r="F1690" s="19"/>
+      <c r="G1690" s="19"/>
+      <c r="H1690" s="20"/>
+      <c r="I1690" s="20"/>
+      <c r="J1690" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J164" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J166" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D173">
+  <conditionalFormatting sqref="D175">
     <cfRule type="duplicateValues" dxfId="312" priority="1"/>
     <cfRule type="duplicateValues" dxfId="311" priority="2"/>
     <cfRule type="duplicateValues" dxfId="310" priority="3"/>
@@ -28595,7 +28911,7 @@
     <cfRule type="duplicateValues" dxfId="304" priority="10"/>
     <cfRule type="duplicateValues" dxfId="303" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D173">
+  <conditionalFormatting sqref="D175">
     <cfRule type="duplicateValues" dxfId="302" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9F1126-C273-4F8C-9EFA-82DDB1B31AAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5421BD0A-BF5F-4DC3-BEB7-6B706F207328}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$166</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$602</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$602</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$170</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$606</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$606</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="232">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1174,6 +1174,18 @@
   </si>
   <si>
     <t>ДЛЯ ДЕТЕЙ сос п/о мгс 0.33кг 8шт.</t>
+  </si>
+  <si>
+    <t>ВОСКРЕСЕНСКАЯ ВЯЛЕНАЯ в/к в/у срез 1/260</t>
+  </si>
+  <si>
+    <t>КРАКОВСКАЯ ГОСТ Останкино п/к н/о мгс</t>
+  </si>
+  <si>
+    <t>НОВОМОСКОВСКАЯ в/к в/у срез 0.31кг</t>
+  </si>
+  <si>
+    <t>РИЕТ МЯСНОЙ С ГРИБАМИ ПМ п/о 1/150</t>
   </si>
 </sst>
 </file>
@@ -5645,7 +5657,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1690"/>
+  <dimension ref="A1:BO1694"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -10189,7 +10201,7 @@
     </row>
     <row r="81" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A81" s="56" t="str">
-        <f t="shared" ref="A81:A105" si="17">RIGHT(D81,4)</f>
+        <f t="shared" ref="A81:A108" si="17">RIGHT(D81,4)</f>
         <v>7564</v>
       </c>
       <c r="B81" s="53" t="s">
@@ -10239,7 +10251,7 @@
         <v>0.33</v>
       </c>
       <c r="G82" s="23">
-        <f t="shared" ref="G82:G94" si="18">E82*F82</f>
+        <f t="shared" ref="G82:G95" si="18">E82*F82</f>
         <v>0</v>
       </c>
       <c r="H82" s="14">
@@ -10529,147 +10541,141 @@
     <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7236</v>
+        <v>7562</v>
       </c>
       <c r="B92" s="54" t="s">
-        <v>69</v>
+        <v>229</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D92" s="57">
-        <v>1001304507236</v>
+        <v>1001307587562</v>
       </c>
       <c r="E92" s="24"/>
-      <c r="F92" s="23">
-        <v>0.28000000000000003</v>
-      </c>
+      <c r="F92" s="23"/>
       <c r="G92" s="23">
-        <f t="shared" si="18"/>
+        <f>E92</f>
         <v>0</v>
       </c>
-      <c r="H92" s="14">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I92" s="14">
-        <v>45</v>
-      </c>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
       <c r="J92" s="29"/>
       <c r="L92" s="129"/>
     </row>
     <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7489</v>
+        <v>7236</v>
       </c>
       <c r="B93" s="54" t="s">
-        <v>221</v>
+        <v>69</v>
       </c>
       <c r="C93" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D93" s="57">
-        <v>1001307357489</v>
+        <v>1001304507236</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G93" s="23">
-        <f t="shared" ref="G93" si="19">E93*F93</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
+      <c r="H93" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I93" s="14">
+        <v>45</v>
+      </c>
       <c r="J93" s="29"/>
       <c r="L93" s="129"/>
     </row>
     <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>6787</v>
-      </c>
-      <c r="B94" s="123" t="s">
-        <v>66</v>
+        <v>7489</v>
+      </c>
+      <c r="B94" s="54" t="s">
+        <v>221</v>
       </c>
       <c r="C94" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D94" s="57">
-        <v>1001300456787</v>
+        <v>1001307357489</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G94" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G94" si="19">E94*F94</f>
         <v>0</v>
       </c>
-      <c r="H94" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I94" s="14">
-        <v>45</v>
-      </c>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
       <c r="J94" s="29"/>
       <c r="L94" s="129"/>
     </row>
     <row r="95" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7166</v>
+        <v>6787</v>
       </c>
       <c r="B95" s="123" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C95" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D95" s="57">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G95" s="23">
-        <f>E95</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H95" s="14">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I95" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J95" s="29"/>
       <c r="L95" s="129"/>
     </row>
-    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7169</v>
-      </c>
-      <c r="B96" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C96" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D96" s="51">
-        <v>1001303987169</v>
+        <v>7166</v>
+      </c>
+      <c r="B96" s="123" t="s">
+        <v>72</v>
+      </c>
+      <c r="C96" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" s="57">
+        <v>1001303987166</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G96" s="23">
-        <f>E96*F96</f>
+        <f>E96</f>
         <v>0</v>
       </c>
       <c r="H96" s="14">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I96" s="14">
         <v>50</v>
@@ -10680,58 +10686,58 @@
     <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>5544</v>
+        <v>7169</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D97" s="51">
-        <v>1001051875544</v>
+        <v>1001303987169</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G97" s="23">
-        <f>E97</f>
+        <f>E97*F97</f>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>4.8600000000000003</v>
+        <v>2.8</v>
       </c>
       <c r="I97" s="14">
-        <v>45</v>
-      </c>
-      <c r="J97" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J97" s="29"/>
       <c r="L97" s="129"/>
     </row>
     <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>6697</v>
+        <v>5544</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D98" s="51">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G98" s="23">
-        <f t="shared" ref="G98:G105" si="20">E98*F98</f>
+        <f>E98</f>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I98" s="14">
         <v>45</v>
@@ -10742,27 +10748,27 @@
     <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7237</v>
+        <v>6697</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="51">
-        <v>1001304497237</v>
+        <v>1001301876697</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G99" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G99:G108" si="20">E99*F99</f>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I99" s="14">
         <v>45</v>
@@ -10773,27 +10779,27 @@
     <row r="100" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7238</v>
+        <v>7237</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="51">
-        <v>1001305197238</v>
+        <v>1001304497237</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G100" s="23">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>2.48</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I100" s="14">
         <v>45</v>
@@ -10804,30 +10810,30 @@
     <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7177</v>
+        <v>7238</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D101" s="51">
-        <v>1001302347177</v>
+        <v>1001305197238</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G101" s="23">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I101" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J101" s="49"/>
       <c r="L101" s="129"/>
@@ -10835,58 +10841,54 @@
     <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7332</v>
+        <v>7516</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="51">
-        <v>1001301777332</v>
+        <v>1001307107516</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G102" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G102" si="21">E102*F102</f>
         <v>0</v>
       </c>
-      <c r="H102" s="14">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I102" s="14">
-        <v>50</v>
-      </c>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
       <c r="J102" s="49"/>
       <c r="L102" s="129"/>
     </row>
     <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7333</v>
+        <v>7177</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D103" s="51">
-        <v>1001303987333</v>
+        <v>1001302347177</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G103" s="23">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I103" s="14">
         <v>50</v>
@@ -10897,433 +10899,429 @@
     <row r="104" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7608</v>
+        <v>7332</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>220</v>
+        <v>63</v>
       </c>
       <c r="C104" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="51">
-        <v>1001304197608</v>
+        <v>1001301777332</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G104" s="23">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H104" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I104" s="14">
-        <v>45</v>
-      </c>
-      <c r="J104" s="52" t="s">
-        <v>210</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J104" s="49"/>
       <c r="L104" s="129"/>
     </row>
-    <row r="105" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="56" t="str">
         <f t="shared" si="17"/>
-        <v>7610</v>
+        <v>7513</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C105" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D105" s="51">
-        <v>1001306717610</v>
+        <v>1001307077513</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="G105" s="23">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H105" s="14">
+      <c r="H105" s="14"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="49"/>
+      <c r="L105" s="129"/>
+    </row>
+    <row r="106" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7333</v>
+      </c>
+      <c r="B106" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="C106" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" s="51">
+        <v>1001303987333</v>
+      </c>
+      <c r="E106" s="24"/>
+      <c r="F106" s="23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G106" s="23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H106" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I106" s="14">
+        <v>50</v>
+      </c>
+      <c r="J106" s="49"/>
+      <c r="L106" s="129"/>
+    </row>
+    <row r="107" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7608</v>
+      </c>
+      <c r="B107" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="C107" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" s="51">
+        <v>1001304197608</v>
+      </c>
+      <c r="E107" s="24"/>
+      <c r="F107" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G107" s="23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H107" s="14">
         <v>1</v>
       </c>
-      <c r="I105" s="14">
+      <c r="I107" s="14">
         <v>45</v>
       </c>
-      <c r="J105" s="52" t="s">
+      <c r="J107" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="L107" s="129"/>
+    </row>
+    <row r="108" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7610</v>
+      </c>
+      <c r="B108" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="C108" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E108" s="24"/>
+      <c r="F108" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G108" s="23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H108" s="14">
+        <v>1</v>
+      </c>
+      <c r="I108" s="14">
+        <v>45</v>
+      </c>
+      <c r="J108" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="L105" s="129"/>
-    </row>
-    <row r="106" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="47" t="s">
+      <c r="L108" s="129"/>
+    </row>
+    <row r="109" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B106" s="42" t="s">
+      <c r="B109" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C106" s="42"/>
-      <c r="D106" s="42"/>
-      <c r="E106" s="42"/>
-      <c r="F106" s="41"/>
-      <c r="G106" s="42"/>
-      <c r="H106" s="42"/>
-      <c r="I106" s="42"/>
-      <c r="J106" s="43"/>
-      <c r="K106" s="60"/>
-      <c r="L106" s="129"/>
-      <c r="M106" s="129"/>
-      <c r="N106" s="129"/>
-      <c r="O106" s="129"/>
-      <c r="P106" s="129"/>
-      <c r="Q106" s="129"/>
-      <c r="R106" s="129"/>
-      <c r="S106" s="129"/>
-      <c r="T106" s="129"/>
-      <c r="U106" s="129"/>
-      <c r="V106" s="129"/>
-      <c r="W106" s="129"/>
-      <c r="X106" s="129"/>
-      <c r="Y106" s="129"/>
-      <c r="Z106" s="129"/>
-      <c r="AA106" s="129"/>
-      <c r="AB106" s="129"/>
-      <c r="AC106" s="129"/>
-      <c r="AD106" s="129"/>
-      <c r="AE106" s="129"/>
-      <c r="AF106" s="129"/>
-      <c r="AG106" s="129"/>
-      <c r="AH106" s="129"/>
-      <c r="AI106" s="129"/>
-      <c r="AJ106" s="129"/>
-      <c r="AK106" s="129"/>
-      <c r="AL106" s="129"/>
-      <c r="AM106" s="129"/>
-      <c r="AN106" s="129"/>
-      <c r="AO106" s="129"/>
-      <c r="AP106" s="129"/>
-      <c r="AQ106" s="129"/>
-      <c r="AR106" s="129"/>
-      <c r="AS106" s="129"/>
-      <c r="AT106" s="129"/>
-      <c r="AU106" s="129"/>
-      <c r="AV106" s="129"/>
-      <c r="AW106" s="129"/>
-      <c r="AX106" s="129"/>
-      <c r="AY106" s="129"/>
-      <c r="AZ106" s="129"/>
-      <c r="BA106" s="129"/>
-      <c r="BB106" s="129"/>
-      <c r="BC106" s="129"/>
-      <c r="BD106" s="129"/>
-      <c r="BE106" s="129"/>
-      <c r="BF106" s="129"/>
-      <c r="BG106" s="129"/>
-      <c r="BH106" s="129"/>
-      <c r="BI106" s="129"/>
-      <c r="BJ106" s="129"/>
-      <c r="BK106" s="129"/>
-      <c r="BL106" s="129"/>
-      <c r="BM106" s="129"/>
-      <c r="BN106" s="129"/>
-      <c r="BO106" s="129"/>
-    </row>
-    <row r="107" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="56" t="str">
-        <f t="shared" ref="A107:A138" si="21">RIGHT(D107,4)</f>
+      <c r="C109" s="42"/>
+      <c r="D109" s="42"/>
+      <c r="E109" s="42"/>
+      <c r="F109" s="41"/>
+      <c r="G109" s="42"/>
+      <c r="H109" s="42"/>
+      <c r="I109" s="42"/>
+      <c r="J109" s="43"/>
+      <c r="K109" s="60"/>
+      <c r="L109" s="129"/>
+      <c r="M109" s="129"/>
+      <c r="N109" s="129"/>
+      <c r="O109" s="129"/>
+      <c r="P109" s="129"/>
+      <c r="Q109" s="129"/>
+      <c r="R109" s="129"/>
+      <c r="S109" s="129"/>
+      <c r="T109" s="129"/>
+      <c r="U109" s="129"/>
+      <c r="V109" s="129"/>
+      <c r="W109" s="129"/>
+      <c r="X109" s="129"/>
+      <c r="Y109" s="129"/>
+      <c r="Z109" s="129"/>
+      <c r="AA109" s="129"/>
+      <c r="AB109" s="129"/>
+      <c r="AC109" s="129"/>
+      <c r="AD109" s="129"/>
+      <c r="AE109" s="129"/>
+      <c r="AF109" s="129"/>
+      <c r="AG109" s="129"/>
+      <c r="AH109" s="129"/>
+      <c r="AI109" s="129"/>
+      <c r="AJ109" s="129"/>
+      <c r="AK109" s="129"/>
+      <c r="AL109" s="129"/>
+      <c r="AM109" s="129"/>
+      <c r="AN109" s="129"/>
+      <c r="AO109" s="129"/>
+      <c r="AP109" s="129"/>
+      <c r="AQ109" s="129"/>
+      <c r="AR109" s="129"/>
+      <c r="AS109" s="129"/>
+      <c r="AT109" s="129"/>
+      <c r="AU109" s="129"/>
+      <c r="AV109" s="129"/>
+      <c r="AW109" s="129"/>
+      <c r="AX109" s="129"/>
+      <c r="AY109" s="129"/>
+      <c r="AZ109" s="129"/>
+      <c r="BA109" s="129"/>
+      <c r="BB109" s="129"/>
+      <c r="BC109" s="129"/>
+      <c r="BD109" s="129"/>
+      <c r="BE109" s="129"/>
+      <c r="BF109" s="129"/>
+      <c r="BG109" s="129"/>
+      <c r="BH109" s="129"/>
+      <c r="BI109" s="129"/>
+      <c r="BJ109" s="129"/>
+      <c r="BK109" s="129"/>
+      <c r="BL109" s="129"/>
+      <c r="BM109" s="129"/>
+      <c r="BN109" s="129"/>
+      <c r="BO109" s="129"/>
+    </row>
+    <row r="110" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="56" t="str">
+        <f t="shared" ref="A110:A141" si="22">RIGHT(D110,4)</f>
         <v>3582</v>
       </c>
-      <c r="B107" s="54" t="s">
+      <c r="B110" s="54" t="s">
         <v>161</v>
       </c>
-      <c r="C107" s="55" t="s">
+      <c r="C110" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="D107" s="57">
+      <c r="D110" s="57">
         <v>1001061973582</v>
       </c>
-      <c r="E107" s="24"/>
-      <c r="F107" s="58">
+      <c r="E110" s="24"/>
+      <c r="F110" s="58">
         <v>0.48799999999999999</v>
       </c>
-      <c r="G107" s="23">
-        <f>E107</f>
+      <c r="G110" s="23">
+        <f>E110</f>
         <v>0</v>
       </c>
-      <c r="H107" s="117">
+      <c r="H110" s="117">
         <v>3.9</v>
       </c>
-      <c r="I107" s="116">
+      <c r="I110" s="116">
         <v>120</v>
       </c>
-      <c r="J107" s="59"/>
-      <c r="K107" s="60"/>
-      <c r="L107" s="129"/>
-      <c r="M107" s="129"/>
-      <c r="N107" s="129"/>
-      <c r="O107" s="129"/>
-      <c r="P107" s="129"/>
-      <c r="Q107" s="129"/>
-      <c r="R107" s="129"/>
-      <c r="S107" s="129"/>
-      <c r="T107" s="129"/>
-      <c r="U107" s="129"/>
-      <c r="V107" s="129"/>
-      <c r="W107" s="129"/>
-      <c r="X107" s="129"/>
-      <c r="Y107" s="129"/>
-      <c r="Z107" s="129"/>
-      <c r="AA107" s="129"/>
-      <c r="AB107" s="129"/>
-      <c r="AC107" s="129"/>
-      <c r="AD107" s="129"/>
-      <c r="AE107" s="129"/>
-      <c r="AF107" s="129"/>
-      <c r="AG107" s="129"/>
-      <c r="AH107" s="129"/>
-      <c r="AI107" s="129"/>
-      <c r="AJ107" s="129"/>
-      <c r="AK107" s="129"/>
-      <c r="AL107" s="129"/>
-      <c r="AM107" s="129"/>
-      <c r="AN107" s="129"/>
-      <c r="AO107" s="129"/>
-      <c r="AP107" s="129"/>
-      <c r="AQ107" s="129"/>
-      <c r="AR107" s="129"/>
-      <c r="AS107" s="129"/>
-      <c r="AT107" s="129"/>
-      <c r="AU107" s="129"/>
-      <c r="AV107" s="129"/>
-      <c r="AW107" s="129"/>
-      <c r="AX107" s="129"/>
-      <c r="AY107" s="129"/>
-      <c r="AZ107" s="129"/>
-      <c r="BA107" s="129"/>
-      <c r="BB107" s="129"/>
-      <c r="BC107" s="129"/>
-      <c r="BD107" s="129"/>
-      <c r="BE107" s="129"/>
-      <c r="BF107" s="129"/>
-      <c r="BG107" s="129"/>
-      <c r="BH107" s="129"/>
-      <c r="BI107" s="129"/>
-      <c r="BJ107" s="129"/>
-      <c r="BK107" s="129"/>
-      <c r="BL107" s="129"/>
-      <c r="BM107" s="129"/>
-      <c r="BN107" s="129"/>
-      <c r="BO107" s="129"/>
-    </row>
-    <row r="108" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="56" t="str">
-        <f t="shared" si="21"/>
+      <c r="J110" s="59"/>
+      <c r="K110" s="60"/>
+      <c r="L110" s="129"/>
+      <c r="M110" s="129"/>
+      <c r="N110" s="129"/>
+      <c r="O110" s="129"/>
+      <c r="P110" s="129"/>
+      <c r="Q110" s="129"/>
+      <c r="R110" s="129"/>
+      <c r="S110" s="129"/>
+      <c r="T110" s="129"/>
+      <c r="U110" s="129"/>
+      <c r="V110" s="129"/>
+      <c r="W110" s="129"/>
+      <c r="X110" s="129"/>
+      <c r="Y110" s="129"/>
+      <c r="Z110" s="129"/>
+      <c r="AA110" s="129"/>
+      <c r="AB110" s="129"/>
+      <c r="AC110" s="129"/>
+      <c r="AD110" s="129"/>
+      <c r="AE110" s="129"/>
+      <c r="AF110" s="129"/>
+      <c r="AG110" s="129"/>
+      <c r="AH110" s="129"/>
+      <c r="AI110" s="129"/>
+      <c r="AJ110" s="129"/>
+      <c r="AK110" s="129"/>
+      <c r="AL110" s="129"/>
+      <c r="AM110" s="129"/>
+      <c r="AN110" s="129"/>
+      <c r="AO110" s="129"/>
+      <c r="AP110" s="129"/>
+      <c r="AQ110" s="129"/>
+      <c r="AR110" s="129"/>
+      <c r="AS110" s="129"/>
+      <c r="AT110" s="129"/>
+      <c r="AU110" s="129"/>
+      <c r="AV110" s="129"/>
+      <c r="AW110" s="129"/>
+      <c r="AX110" s="129"/>
+      <c r="AY110" s="129"/>
+      <c r="AZ110" s="129"/>
+      <c r="BA110" s="129"/>
+      <c r="BB110" s="129"/>
+      <c r="BC110" s="129"/>
+      <c r="BD110" s="129"/>
+      <c r="BE110" s="129"/>
+      <c r="BF110" s="129"/>
+      <c r="BG110" s="129"/>
+      <c r="BH110" s="129"/>
+      <c r="BI110" s="129"/>
+      <c r="BJ110" s="129"/>
+      <c r="BK110" s="129"/>
+      <c r="BL110" s="129"/>
+      <c r="BM110" s="129"/>
+      <c r="BN110" s="129"/>
+      <c r="BO110" s="129"/>
+    </row>
+    <row r="111" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="56" t="str">
+        <f t="shared" si="22"/>
         <v>3986</v>
       </c>
-      <c r="B108" s="54" t="s">
+      <c r="B111" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="C108" s="55" t="s">
+      <c r="C111" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D108" s="57">
+      <c r="D111" s="57">
         <v>1001061973986</v>
       </c>
-      <c r="E108" s="24"/>
-      <c r="F108" s="58">
+      <c r="E111" s="24"/>
+      <c r="F111" s="58">
         <v>0.25</v>
       </c>
-      <c r="G108" s="23">
-        <f t="shared" ref="G108:G113" si="22">E108*F108</f>
+      <c r="G111" s="23">
+        <f t="shared" ref="G111:G116" si="23">E111*F111</f>
         <v>0</v>
       </c>
-      <c r="H108" s="117">
+      <c r="H111" s="117">
         <v>2</v>
       </c>
-      <c r="I108" s="116">
+      <c r="I111" s="116">
         <v>120</v>
       </c>
-      <c r="J108" s="59"/>
-      <c r="K108" s="60"/>
-      <c r="L108" s="129"/>
-      <c r="M108" s="129"/>
-      <c r="N108" s="129"/>
-      <c r="O108" s="129"/>
-      <c r="P108" s="129"/>
-      <c r="Q108" s="129"/>
-      <c r="R108" s="129"/>
-      <c r="S108" s="129"/>
-      <c r="T108" s="129"/>
-      <c r="U108" s="129"/>
-      <c r="V108" s="129"/>
-      <c r="W108" s="129"/>
-      <c r="X108" s="129"/>
-      <c r="Y108" s="129"/>
-      <c r="Z108" s="129"/>
-      <c r="AA108" s="129"/>
-      <c r="AB108" s="129"/>
-      <c r="AC108" s="129"/>
-      <c r="AD108" s="129"/>
-      <c r="AE108" s="129"/>
-      <c r="AF108" s="129"/>
-      <c r="AG108" s="129"/>
-      <c r="AH108" s="129"/>
-      <c r="AI108" s="129"/>
-      <c r="AJ108" s="129"/>
-      <c r="AK108" s="129"/>
-      <c r="AL108" s="129"/>
-      <c r="AM108" s="129"/>
-      <c r="AN108" s="129"/>
-      <c r="AO108" s="129"/>
-      <c r="AP108" s="129"/>
-      <c r="AQ108" s="129"/>
-      <c r="AR108" s="129"/>
-      <c r="AS108" s="129"/>
-      <c r="AT108" s="129"/>
-      <c r="AU108" s="129"/>
-      <c r="AV108" s="129"/>
-      <c r="AW108" s="129"/>
-      <c r="AX108" s="129"/>
-      <c r="AY108" s="129"/>
-      <c r="AZ108" s="129"/>
-      <c r="BA108" s="129"/>
-      <c r="BB108" s="129"/>
-      <c r="BC108" s="129"/>
-      <c r="BD108" s="129"/>
-      <c r="BE108" s="129"/>
-      <c r="BF108" s="129"/>
-      <c r="BG108" s="129"/>
-      <c r="BH108" s="129"/>
-      <c r="BI108" s="129"/>
-      <c r="BJ108" s="129"/>
-      <c r="BK108" s="129"/>
-      <c r="BL108" s="129"/>
-      <c r="BM108" s="129"/>
-      <c r="BN108" s="129"/>
-      <c r="BO108" s="129"/>
-    </row>
-    <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="56" t="str">
-        <f t="shared" si="21"/>
+      <c r="J111" s="59"/>
+      <c r="K111" s="60"/>
+      <c r="L111" s="129"/>
+      <c r="M111" s="129"/>
+      <c r="N111" s="129"/>
+      <c r="O111" s="129"/>
+      <c r="P111" s="129"/>
+      <c r="Q111" s="129"/>
+      <c r="R111" s="129"/>
+      <c r="S111" s="129"/>
+      <c r="T111" s="129"/>
+      <c r="U111" s="129"/>
+      <c r="V111" s="129"/>
+      <c r="W111" s="129"/>
+      <c r="X111" s="129"/>
+      <c r="Y111" s="129"/>
+      <c r="Z111" s="129"/>
+      <c r="AA111" s="129"/>
+      <c r="AB111" s="129"/>
+      <c r="AC111" s="129"/>
+      <c r="AD111" s="129"/>
+      <c r="AE111" s="129"/>
+      <c r="AF111" s="129"/>
+      <c r="AG111" s="129"/>
+      <c r="AH111" s="129"/>
+      <c r="AI111" s="129"/>
+      <c r="AJ111" s="129"/>
+      <c r="AK111" s="129"/>
+      <c r="AL111" s="129"/>
+      <c r="AM111" s="129"/>
+      <c r="AN111" s="129"/>
+      <c r="AO111" s="129"/>
+      <c r="AP111" s="129"/>
+      <c r="AQ111" s="129"/>
+      <c r="AR111" s="129"/>
+      <c r="AS111" s="129"/>
+      <c r="AT111" s="129"/>
+      <c r="AU111" s="129"/>
+      <c r="AV111" s="129"/>
+      <c r="AW111" s="129"/>
+      <c r="AX111" s="129"/>
+      <c r="AY111" s="129"/>
+      <c r="AZ111" s="129"/>
+      <c r="BA111" s="129"/>
+      <c r="BB111" s="129"/>
+      <c r="BC111" s="129"/>
+      <c r="BD111" s="129"/>
+      <c r="BE111" s="129"/>
+      <c r="BF111" s="129"/>
+      <c r="BG111" s="129"/>
+      <c r="BH111" s="129"/>
+      <c r="BI111" s="129"/>
+      <c r="BJ111" s="129"/>
+      <c r="BK111" s="129"/>
+      <c r="BL111" s="129"/>
+      <c r="BM111" s="129"/>
+      <c r="BN111" s="129"/>
+      <c r="BO111" s="129"/>
+    </row>
+    <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="56" t="str">
+        <f t="shared" si="22"/>
         <v>5931</v>
       </c>
-      <c r="B109" s="53" t="s">
+      <c r="B112" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="C109" s="50" t="s">
+      <c r="C112" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D109" s="51">
+      <c r="D112" s="51">
         <v>1001060755931</v>
       </c>
-      <c r="E109" s="24"/>
-      <c r="F109" s="23">
+      <c r="E112" s="24"/>
+      <c r="F112" s="23">
         <v>0.22</v>
       </c>
-      <c r="G109" s="23">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="H109" s="115">
-        <v>1.76</v>
-      </c>
-      <c r="I109" s="14">
-        <v>120</v>
-      </c>
-      <c r="J109" s="29"/>
-      <c r="L109" s="129"/>
-    </row>
-    <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>5708</v>
-      </c>
-      <c r="B110" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C110" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D110" s="51">
-        <v>1001063145708</v>
-      </c>
-      <c r="E110" s="24"/>
-      <c r="F110" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G110" s="23">
-        <f t="shared" ref="G110:G111" si="23">E110</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="14">
-        <v>4</v>
-      </c>
-      <c r="I110" s="14">
-        <v>120</v>
-      </c>
-      <c r="J110" s="29"/>
-      <c r="L110" s="129"/>
-    </row>
-    <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>3287</v>
-      </c>
-      <c r="B111" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C111" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D111" s="51">
-        <v>1001060763287</v>
-      </c>
-      <c r="E111" s="24"/>
-      <c r="F111" s="23">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G111" s="23">
+      <c r="G112" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="H111" s="14">
-        <v>3.9</v>
-      </c>
-      <c r="I111" s="14">
-        <v>120</v>
-      </c>
-      <c r="J111" s="29"/>
-      <c r="L111" s="129"/>
-    </row>
-    <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>4993</v>
-      </c>
-      <c r="B112" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="C112" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D112" s="51">
-        <v>1001060764993</v>
-      </c>
-      <c r="E112" s="24"/>
-      <c r="F112" s="23">
-        <v>0.25</v>
-      </c>
-      <c r="G112" s="23">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="H112" s="14">
-        <v>2</v>
+      <c r="H112" s="115">
+        <v>1.76</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -11333,28 +11331,28 @@
     </row>
     <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>5483</v>
+        <f t="shared" si="22"/>
+        <v>5708</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C113" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D113" s="51">
-        <v>1001062505483</v>
+        <v>1001063145708</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G113:G114" si="24">E113</f>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -11364,28 +11362,28 @@
     </row>
     <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>4117</v>
+        <f t="shared" si="22"/>
+        <v>3287</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D114" s="51">
-        <v>1001062504117</v>
+        <v>1001060763287</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" ref="G114:G115" si="24">E114</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -11395,28 +11393,28 @@
     </row>
     <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>0614</v>
+        <f t="shared" si="22"/>
+        <v>4993</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C115" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D115" s="51">
-        <v>1001060720614</v>
+        <v>1001060764993</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>3.64</v>
+        <v>2</v>
       </c>
       <c r="I115" s="14">
         <v>120</v>
@@ -11426,24 +11424,24 @@
     </row>
     <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6967</v>
+        <f t="shared" si="22"/>
+        <v>5483</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D116" s="51">
-        <v>1001063656967</v>
+        <v>1001062505483</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
         <v>0.25</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" ref="G116:G125" si="25">E116*F116</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
@@ -11457,28 +11455,28 @@
     </row>
     <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6937</v>
+        <f t="shared" si="22"/>
+        <v>4117</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>164</v>
+        <v>88</v>
       </c>
       <c r="C117" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D117" s="51">
-        <v>1001063106937</v>
+        <v>1001062504117</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.25</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G117:G118" si="25">E117</f>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="I117" s="14">
         <v>120</v>
@@ -11488,28 +11486,28 @@
     </row>
     <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7143</v>
+        <f t="shared" si="22"/>
+        <v>0614</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C118" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D118" s="51">
-        <v>1001060717143</v>
+        <v>1001060720614</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
       <c r="G118" s="23">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>1.76</v>
+        <v>3.64</v>
       </c>
       <c r="I118" s="14">
         <v>120</v>
@@ -11519,28 +11517,28 @@
     </row>
     <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7147</v>
+        <f t="shared" si="22"/>
+        <v>6967</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="51">
-        <v>1001063237147</v>
+        <v>1001063656967</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G119:G128" si="26">E119*F119</f>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I119" s="14">
         <v>120</v>
@@ -11550,468 +11548,466 @@
     </row>
     <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7456</v>
+        <f t="shared" si="22"/>
+        <v>6937</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="51">
-        <v>1001063097456</v>
+        <v>1001063106937</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I120" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J120" s="29"/>
       <c r="L120" s="129"/>
     </row>
     <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7364</v>
+        <f t="shared" si="22"/>
+        <v>7143</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D121" s="51">
-        <v>1001063217364</v>
+        <v>1001060717143</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
         <v>0.22</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
         <v>1.76</v>
       </c>
       <c r="I121" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J121" s="29"/>
       <c r="L121" s="129"/>
     </row>
     <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7383</v>
+        <f t="shared" si="22"/>
+        <v>7147</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D122" s="51">
-        <v>1001065467383</v>
+        <v>1001063237147</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
         <v>0.22</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
         <v>1.76</v>
       </c>
       <c r="I122" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J122" s="29"/>
       <c r="L122" s="129"/>
     </row>
     <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7317</v>
+        <f t="shared" si="22"/>
+        <v>7456</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D123" s="51">
-        <v>1001066567317</v>
+        <v>1001063097456</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.54</v>
+        <v>0.15</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>3.78</v>
+        <v>1.8</v>
       </c>
       <c r="I123" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J123" s="29"/>
       <c r="L123" s="129"/>
     </row>
     <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7318</v>
+        <f t="shared" si="22"/>
+        <v>7364</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="51">
-        <v>1001060727318</v>
+        <v>1001063217364</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="I124" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J124" s="29"/>
       <c r="L124" s="129"/>
     </row>
     <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7316</v>
+        <f t="shared" si="22"/>
+        <v>7383</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D125" s="51">
-        <v>1001060727316</v>
+        <v>1001065467383</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G125" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I125" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J125" s="29"/>
       <c r="L125" s="129"/>
     </row>
     <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6832</v>
+        <f t="shared" si="22"/>
+        <v>7317</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D126" s="51">
-        <v>1001065616832</v>
+        <v>1001066567317</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" ref="G126:G127" si="26">E126</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I126" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J126" s="29"/>
       <c r="L126" s="129"/>
     </row>
     <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7299</v>
+        <f t="shared" si="22"/>
+        <v>7318</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D127" s="51">
-        <v>1001060677299</v>
+        <v>1001060727318</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
-        <v>0.215</v>
+        <v>0.27</v>
       </c>
       <c r="G127" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="I127" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J127" s="29"/>
       <c r="L127" s="129"/>
     </row>
     <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7386</v>
+        <f t="shared" si="22"/>
+        <v>7316</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D128" s="51">
-        <v>1001067017386</v>
+        <v>1001060727316</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.15</v>
+        <v>0.54</v>
       </c>
       <c r="G128" s="23">
-        <f t="shared" ref="G128:G138" si="27">E128*F128</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>1.35</v>
+        <v>3.78</v>
       </c>
       <c r="I128" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J128" s="29"/>
       <c r="L128" s="129"/>
     </row>
     <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7613</v>
+        <f t="shared" si="22"/>
+        <v>6832</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D129" s="51">
-        <v>1001061977613</v>
+        <v>1001065616832</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
-        <v>0.1</v>
+        <v>0.215</v>
       </c>
       <c r="G129" s="23">
+        <f t="shared" ref="G129:G130" si="27">E129</f>
+        <v>0</v>
+      </c>
+      <c r="H129" s="14">
+        <v>2.15</v>
+      </c>
+      <c r="I129" s="14">
+        <v>30</v>
+      </c>
+      <c r="J129" s="29"/>
+      <c r="L129" s="129"/>
+    </row>
+    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="56" t="str">
+        <f t="shared" si="22"/>
+        <v>7299</v>
+      </c>
+      <c r="B130" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="C130" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D130" s="51">
+        <v>1001060677299</v>
+      </c>
+      <c r="E130" s="24"/>
+      <c r="F130" s="23">
+        <v>0.215</v>
+      </c>
+      <c r="G130" s="23">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H129" s="14">
-        <v>1</v>
-      </c>
-      <c r="I129" s="14">
-        <v>60</v>
-      </c>
-      <c r="J129" s="52" t="s">
-        <v>215</v>
-      </c>
-      <c r="L129" s="129"/>
-    </row>
-    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6834</v>
-      </c>
-      <c r="B130" s="134" t="s">
-        <v>149</v>
-      </c>
-      <c r="C130" s="135" t="s">
-        <v>21</v>
-      </c>
-      <c r="D130" s="136">
-        <v>1001203146834</v>
-      </c>
-      <c r="E130" s="137"/>
-      <c r="F130" s="138">
-        <v>0.1</v>
-      </c>
-      <c r="G130" s="138">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="H130" s="139">
-        <v>1</v>
-      </c>
-      <c r="I130" s="139">
-        <v>60</v>
-      </c>
-      <c r="J130" s="139" t="s">
-        <v>214</v>
-      </c>
+      <c r="H130" s="14">
+        <v>2.15</v>
+      </c>
+      <c r="I130" s="14">
+        <v>30</v>
+      </c>
+      <c r="J130" s="29"/>
       <c r="L130" s="129"/>
     </row>
     <row r="131" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7382</v>
+        <f t="shared" si="22"/>
+        <v>7386</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="51">
-        <v>1001203117382</v>
+        <v>1001067017386</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G131" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="G131:G141" si="28">E131*F131</f>
         <v>0</v>
       </c>
       <c r="H131" s="14">
-        <v>0.96</v>
+        <v>1.35</v>
       </c>
       <c r="I131" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J131" s="29"/>
       <c r="L131" s="129"/>
     </row>
     <row r="132" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7616</v>
+        <f t="shared" si="22"/>
+        <v>7613</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D132" s="51">
-        <v>1001062507616</v>
+        <v>1001061977613</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
         <v>0.1</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
       </c>
       <c r="J132" s="52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L132" s="129"/>
     </row>
     <row r="133" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6221</v>
-      </c>
-      <c r="B133" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C133" s="50" t="s">
+        <f t="shared" si="22"/>
+        <v>6834</v>
+      </c>
+      <c r="B133" s="134" t="s">
+        <v>149</v>
+      </c>
+      <c r="C133" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="D133" s="51">
-        <v>1001205376221</v>
-      </c>
-      <c r="E133" s="24"/>
-      <c r="F133" s="23">
-        <v>0.09</v>
-      </c>
-      <c r="G133" s="23">
-        <f t="shared" si="27"/>
+      <c r="D133" s="136">
+        <v>1001203146834</v>
+      </c>
+      <c r="E133" s="137"/>
+      <c r="F133" s="138">
+        <v>0.1</v>
+      </c>
+      <c r="G133" s="138">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H133" s="14">
-        <v>0.9</v>
-      </c>
-      <c r="I133" s="14">
+      <c r="H133" s="139">
+        <v>1</v>
+      </c>
+      <c r="I133" s="139">
         <v>60</v>
       </c>
-      <c r="J133" s="29"/>
+      <c r="J133" s="139" t="s">
+        <v>214</v>
+      </c>
       <c r="L133" s="129"/>
     </row>
     <row r="134" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6222</v>
+        <f t="shared" si="22"/>
+        <v>7382</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D134" s="51">
-        <v>1001205386222</v>
+        <v>1001203117382</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H134" s="14">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="I134" s="14">
         <v>60</v>
@@ -12021,59 +12017,61 @@
     </row>
     <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6965</v>
+        <f t="shared" si="22"/>
+        <v>7616</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D135" s="51">
-        <v>1001206356965</v>
+        <v>1001062507616</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="G135" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H135" s="14">
-        <v>0.98</v>
+        <v>1.4</v>
       </c>
       <c r="I135" s="14">
         <v>60</v>
       </c>
-      <c r="J135" s="29"/>
+      <c r="J135" s="52" t="s">
+        <v>216</v>
+      </c>
       <c r="L135" s="129"/>
     </row>
     <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6557</v>
+        <f t="shared" si="22"/>
+        <v>6221</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="C136" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D136" s="51">
-        <v>1001200756557</v>
+        <v>1001205376221</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G136" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H136" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I136" s="14">
         <v>60</v>
@@ -12083,28 +12081,28 @@
     </row>
     <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>5679</v>
+        <f t="shared" si="22"/>
+        <v>6222</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="51">
-        <v>1001190765679</v>
+        <v>1001205386222</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G137" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
@@ -12112,80 +12110,92 @@
       <c r="J137" s="29"/>
       <c r="L137" s="129"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7626</v>
+        <f t="shared" si="22"/>
+        <v>6965</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="51">
-        <v>1001066607626</v>
+        <v>1001206356965</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G138" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H138" s="14">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I138" s="14">
         <v>60</v>
       </c>
-      <c r="J138" s="52" t="s">
-        <v>217</v>
-      </c>
+      <c r="J138" s="29"/>
       <c r="L138" s="129"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="B139" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C139" s="42"/>
-      <c r="D139" s="42"/>
-      <c r="E139" s="42"/>
-      <c r="F139" s="41"/>
-      <c r="G139" s="42"/>
-      <c r="H139" s="42"/>
-      <c r="I139" s="42"/>
-      <c r="J139" s="43"/>
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="56" t="str">
+        <f t="shared" si="22"/>
+        <v>6557</v>
+      </c>
+      <c r="B139" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C139" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" s="51">
+        <v>1001200756557</v>
+      </c>
+      <c r="E139" s="24"/>
+      <c r="F139" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G139" s="23">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H139" s="14">
+        <v>1</v>
+      </c>
+      <c r="I139" s="14">
+        <v>60</v>
+      </c>
+      <c r="J139" s="29"/>
       <c r="L139" s="129"/>
     </row>
-    <row r="140" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="56" t="str">
-        <f t="shared" ref="A140:A152" si="28">RIGHT(D140,4)</f>
-        <v>4584</v>
-      </c>
-      <c r="B140" s="121" t="s">
-        <v>125</v>
+        <f t="shared" si="22"/>
+        <v>5679</v>
+      </c>
+      <c r="B140" s="53" t="s">
+        <v>156</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D140" s="120">
-        <v>1001092674584</v>
+        <v>21</v>
+      </c>
+      <c r="D140" s="51">
+        <v>1001190765679</v>
       </c>
       <c r="E140" s="24"/>
       <c r="F140" s="23">
-        <v>2.5</v>
+        <v>0.15</v>
       </c>
       <c r="G140" s="23">
-        <f>E140</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H140" s="14">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="I140" s="14">
         <v>60</v>
@@ -12193,294 +12203,114 @@
       <c r="J140" s="29"/>
       <c r="L140" s="129"/>
     </row>
-    <row r="141" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="56" t="str">
+        <f t="shared" si="22"/>
+        <v>7626</v>
+      </c>
+      <c r="B141" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="C141" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" s="51">
+        <v>1001066607626</v>
+      </c>
+      <c r="E141" s="24"/>
+      <c r="F141" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G141" s="23">
         <f t="shared" si="28"/>
-        <v>6495</v>
-      </c>
-      <c r="B141" s="122" t="s">
-        <v>97</v>
-      </c>
-      <c r="C141" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D141" s="70">
-        <v>1001092436495</v>
-      </c>
-      <c r="E141" s="24"/>
-      <c r="F141" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="G141" s="23">
-        <f>E141*F141</f>
         <v>0</v>
       </c>
-      <c r="H141" s="59">
-        <v>1.8</v>
-      </c>
-      <c r="I141" s="59">
-        <v>45</v>
-      </c>
-      <c r="J141" s="59"/>
-      <c r="K141" s="60"/>
+      <c r="H141" s="14">
+        <v>1</v>
+      </c>
+      <c r="I141" s="14">
+        <v>60</v>
+      </c>
+      <c r="J141" s="52" t="s">
+        <v>217</v>
+      </c>
       <c r="L141" s="129"/>
-      <c r="M141" s="129"/>
-      <c r="N141" s="129"/>
-      <c r="O141" s="129"/>
-      <c r="P141" s="129"/>
-      <c r="Q141" s="129"/>
-      <c r="R141" s="129"/>
-      <c r="S141" s="129"/>
-      <c r="T141" s="129"/>
-      <c r="U141" s="129"/>
-      <c r="V141" s="129"/>
-      <c r="W141" s="129"/>
-      <c r="X141" s="129"/>
-      <c r="Y141" s="129"/>
-      <c r="Z141" s="129"/>
-      <c r="AA141" s="129"/>
-      <c r="AB141" s="129"/>
-      <c r="AC141" s="129"/>
-      <c r="AD141" s="129"/>
-      <c r="AE141" s="129"/>
-      <c r="AF141" s="129"/>
-      <c r="AG141" s="129"/>
-      <c r="AH141" s="129"/>
-      <c r="AI141" s="129"/>
-      <c r="AJ141" s="129"/>
-      <c r="AK141" s="129"/>
-      <c r="AL141" s="129"/>
-      <c r="AM141" s="129"/>
-      <c r="AN141" s="129"/>
-      <c r="AO141" s="129"/>
-      <c r="AP141" s="129"/>
-      <c r="AQ141" s="129"/>
-      <c r="AR141" s="129"/>
-      <c r="AS141" s="129"/>
-      <c r="AT141" s="129"/>
-      <c r="AU141" s="129"/>
-      <c r="AV141" s="129"/>
-      <c r="AW141" s="129"/>
-      <c r="AX141" s="129"/>
-      <c r="AY141" s="129"/>
-      <c r="AZ141" s="129"/>
-      <c r="BA141" s="129"/>
-      <c r="BB141" s="129"/>
-      <c r="BC141" s="129"/>
-      <c r="BD141" s="129"/>
-      <c r="BE141" s="129"/>
-      <c r="BF141" s="129"/>
-      <c r="BG141" s="129"/>
-      <c r="BH141" s="129"/>
-      <c r="BI141" s="129"/>
-      <c r="BJ141" s="129"/>
-      <c r="BK141" s="129"/>
-      <c r="BL141" s="129"/>
-      <c r="BM141" s="129"/>
-      <c r="BN141" s="129"/>
-      <c r="BO141" s="129"/>
-    </row>
-    <row r="142" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>6470</v>
-      </c>
-      <c r="B142" s="118" t="s">
-        <v>126</v>
-      </c>
-      <c r="C142" s="55" t="s">
+    </row>
+    <row r="142" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B142" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C142" s="42"/>
+      <c r="D142" s="42"/>
+      <c r="E142" s="42"/>
+      <c r="F142" s="41"/>
+      <c r="G142" s="42"/>
+      <c r="H142" s="42"/>
+      <c r="I142" s="42"/>
+      <c r="J142" s="43"/>
+      <c r="L142" s="129"/>
+    </row>
+    <row r="143" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="56" t="str">
+        <f t="shared" ref="A143:A156" si="29">RIGHT(D143,4)</f>
+        <v>4584</v>
+      </c>
+      <c r="B143" s="121" t="s">
+        <v>125</v>
+      </c>
+      <c r="C143" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D142" s="70">
-        <v>1001092436470</v>
-      </c>
-      <c r="E142" s="24"/>
-      <c r="F142" s="58">
-        <v>1.2</v>
-      </c>
-      <c r="G142" s="23">
-        <f t="shared" ref="G142:G143" si="29">E142</f>
+      <c r="D143" s="120">
+        <v>1001092674584</v>
+      </c>
+      <c r="E143" s="24"/>
+      <c r="F143" s="23">
+        <v>2.5</v>
+      </c>
+      <c r="G143" s="23">
+        <f>E143</f>
         <v>0</v>
       </c>
-      <c r="H142" s="59">
-        <v>4.8</v>
-      </c>
-      <c r="I142" s="59">
-        <v>45</v>
-      </c>
-      <c r="J142" s="59"/>
-      <c r="K142" s="60"/>
-      <c r="L142" s="129"/>
-      <c r="M142" s="129"/>
-      <c r="N142" s="129"/>
-      <c r="O142" s="129"/>
-      <c r="P142" s="129"/>
-      <c r="Q142" s="129"/>
-      <c r="R142" s="129"/>
-      <c r="S142" s="129"/>
-      <c r="T142" s="129"/>
-      <c r="U142" s="129"/>
-      <c r="V142" s="129"/>
-      <c r="W142" s="129"/>
-      <c r="X142" s="129"/>
-      <c r="Y142" s="129"/>
-      <c r="Z142" s="129"/>
-      <c r="AA142" s="129"/>
-      <c r="AB142" s="129"/>
-      <c r="AC142" s="129"/>
-      <c r="AD142" s="129"/>
-      <c r="AE142" s="129"/>
-      <c r="AF142" s="129"/>
-      <c r="AG142" s="129"/>
-      <c r="AH142" s="129"/>
-      <c r="AI142" s="129"/>
-      <c r="AJ142" s="129"/>
-      <c r="AK142" s="129"/>
-      <c r="AL142" s="129"/>
-      <c r="AM142" s="129"/>
-      <c r="AN142" s="129"/>
-      <c r="AO142" s="129"/>
-      <c r="AP142" s="129"/>
-      <c r="AQ142" s="129"/>
-      <c r="AR142" s="129"/>
-      <c r="AS142" s="129"/>
-      <c r="AT142" s="129"/>
-      <c r="AU142" s="129"/>
-      <c r="AV142" s="129"/>
-      <c r="AW142" s="129"/>
-      <c r="AX142" s="129"/>
-      <c r="AY142" s="129"/>
-      <c r="AZ142" s="129"/>
-      <c r="BA142" s="129"/>
-      <c r="BB142" s="129"/>
-      <c r="BC142" s="129"/>
-      <c r="BD142" s="129"/>
-      <c r="BE142" s="129"/>
-      <c r="BF142" s="129"/>
-      <c r="BG142" s="129"/>
-      <c r="BH142" s="129"/>
-      <c r="BI142" s="129"/>
-      <c r="BJ142" s="129"/>
-      <c r="BK142" s="129"/>
-      <c r="BL142" s="129"/>
-      <c r="BM142" s="129"/>
-      <c r="BN142" s="129"/>
-      <c r="BO142" s="129"/>
-    </row>
-    <row r="143" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>5452</v>
-      </c>
-      <c r="B143" s="118" t="s">
-        <v>95</v>
-      </c>
-      <c r="C143" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D143" s="70">
-        <v>1001092485452</v>
-      </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="58">
-        <v>1.35</v>
-      </c>
-      <c r="G143" s="23">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="H143" s="59">
-        <v>4.05</v>
-      </c>
-      <c r="I143" s="59">
+      <c r="H143" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I143" s="14">
         <v>60</v>
       </c>
-      <c r="J143" s="59"/>
-      <c r="K143" s="60"/>
+      <c r="J143" s="29"/>
       <c r="L143" s="129"/>
-      <c r="M143" s="129"/>
-      <c r="N143" s="129"/>
-      <c r="O143" s="129"/>
-      <c r="P143" s="129"/>
-      <c r="Q143" s="129"/>
-      <c r="R143" s="129"/>
-      <c r="S143" s="129"/>
-      <c r="T143" s="129"/>
-      <c r="U143" s="129"/>
-      <c r="V143" s="129"/>
-      <c r="W143" s="129"/>
-      <c r="X143" s="129"/>
-      <c r="Y143" s="129"/>
-      <c r="Z143" s="129"/>
-      <c r="AA143" s="129"/>
-      <c r="AB143" s="129"/>
-      <c r="AC143" s="129"/>
-      <c r="AD143" s="129"/>
-      <c r="AE143" s="129"/>
-      <c r="AF143" s="129"/>
-      <c r="AG143" s="129"/>
-      <c r="AH143" s="129"/>
-      <c r="AI143" s="129"/>
-      <c r="AJ143" s="129"/>
-      <c r="AK143" s="129"/>
-      <c r="AL143" s="129"/>
-      <c r="AM143" s="129"/>
-      <c r="AN143" s="129"/>
-      <c r="AO143" s="129"/>
-      <c r="AP143" s="129"/>
-      <c r="AQ143" s="129"/>
-      <c r="AR143" s="129"/>
-      <c r="AS143" s="129"/>
-      <c r="AT143" s="129"/>
-      <c r="AU143" s="129"/>
-      <c r="AV143" s="129"/>
-      <c r="AW143" s="129"/>
-      <c r="AX143" s="129"/>
-      <c r="AY143" s="129"/>
-      <c r="AZ143" s="129"/>
-      <c r="BA143" s="129"/>
-      <c r="BB143" s="129"/>
-      <c r="BC143" s="129"/>
-      <c r="BD143" s="129"/>
-      <c r="BE143" s="129"/>
-      <c r="BF143" s="129"/>
-      <c r="BG143" s="129"/>
-      <c r="BH143" s="129"/>
-      <c r="BI143" s="129"/>
-      <c r="BJ143" s="129"/>
-      <c r="BK143" s="129"/>
-      <c r="BL143" s="129"/>
-      <c r="BM143" s="129"/>
-      <c r="BN143" s="129"/>
-      <c r="BO143" s="129"/>
     </row>
     <row r="144" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>3215</v>
-      </c>
-      <c r="B144" s="118" t="s">
-        <v>94</v>
+        <f t="shared" si="29"/>
+        <v>6495</v>
+      </c>
+      <c r="B144" s="122" t="s">
+        <v>97</v>
       </c>
       <c r="C144" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D144" s="70">
-        <v>1001094053215</v>
+        <v>1001092436495</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="58">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G144" s="23">
         <f>E144*F144</f>
         <v>0</v>
       </c>
       <c r="H144" s="59">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="I144" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J144" s="59"/>
       <c r="K144" s="60"/>
@@ -12543,31 +12373,31 @@
     </row>
     <row r="145" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>6866</v>
+        <f t="shared" si="29"/>
+        <v>6470</v>
       </c>
       <c r="B145" s="118" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C145" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D145" s="70">
-        <v>1001095716866</v>
+        <v>1001092436470</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="58">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G145" s="23">
-        <f>E145</f>
+        <f t="shared" ref="G145:G146" si="30">E145</f>
         <v>0</v>
       </c>
       <c r="H145" s="59">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I145" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J145" s="59"/>
       <c r="K145" s="60"/>
@@ -12628,30 +12458,30 @@
       <c r="BN145" s="129"/>
       <c r="BO145" s="129"/>
     </row>
-    <row r="146" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>5495</v>
-      </c>
-      <c r="B146" s="54" t="s">
-        <v>96</v>
+        <f t="shared" si="29"/>
+        <v>5452</v>
+      </c>
+      <c r="B146" s="118" t="s">
+        <v>95</v>
       </c>
       <c r="C146" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D146" s="119">
-        <v>1001093345495</v>
+        <v>23</v>
+      </c>
+      <c r="D146" s="70">
+        <v>1001092485452</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="58">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G146" s="23">
-        <f t="shared" ref="G146:G149" si="30">E146*F146</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H146" s="59">
-        <v>2.4</v>
+        <v>4.05</v>
       </c>
       <c r="I146" s="59">
         <v>60</v>
@@ -12715,33 +12545,33 @@
       <c r="BN146" s="129"/>
       <c r="BO146" s="129"/>
     </row>
-    <row r="147" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>7377</v>
-      </c>
-      <c r="B147" s="54" t="s">
-        <v>127</v>
+        <f t="shared" si="29"/>
+        <v>3215</v>
+      </c>
+      <c r="B147" s="118" t="s">
+        <v>94</v>
       </c>
       <c r="C147" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D147" s="119">
-        <v>1001095027377</v>
+      <c r="D147" s="70">
+        <v>1001094053215</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="58">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" si="30"/>
+        <f>E147*F147</f>
         <v>0</v>
       </c>
       <c r="H147" s="59">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="I147" s="59">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J147" s="59"/>
       <c r="K147" s="60"/>
@@ -12802,30 +12632,34 @@
       <c r="BN147" s="129"/>
       <c r="BO147" s="129"/>
     </row>
-    <row r="148" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>6411</v>
-      </c>
-      <c r="B148" s="54" t="s">
-        <v>226</v>
+        <f t="shared" si="29"/>
+        <v>6866</v>
+      </c>
+      <c r="B148" s="118" t="s">
+        <v>93</v>
       </c>
       <c r="C148" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D148" s="119">
-        <v>1001093316411</v>
+        <v>23</v>
+      </c>
+      <c r="D148" s="70">
+        <v>1001095716866</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="58">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" ref="G148" si="31">E148*F148</f>
+        <f>E148</f>
         <v>0</v>
       </c>
-      <c r="H148" s="59"/>
-      <c r="I148" s="59"/>
+      <c r="H148" s="59">
+        <v>6</v>
+      </c>
+      <c r="I148" s="59">
+        <v>60</v>
+      </c>
       <c r="J148" s="59"/>
       <c r="K148" s="60"/>
       <c r="L148" s="129"/>
@@ -12887,31 +12721,31 @@
     </row>
     <row r="149" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>6925</v>
+        <f t="shared" si="29"/>
+        <v>5495</v>
       </c>
       <c r="B149" s="54" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C149" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="119">
-        <v>1001095226925</v>
+        <v>1001093345495</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="58">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G149" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="G149:G152" si="31">E149*F149</f>
         <v>0</v>
       </c>
       <c r="H149" s="59">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I149" s="59">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J149" s="59"/>
       <c r="K149" s="60"/>
@@ -12972,33 +12806,33 @@
       <c r="BN149" s="129"/>
       <c r="BO149" s="129"/>
     </row>
-    <row r="150" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>6025</v>
+        <f t="shared" si="29"/>
+        <v>7377</v>
       </c>
       <c r="B150" s="54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C150" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D150" s="119">
-        <v>1001094966025</v>
+        <v>1001095027377</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="58">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="G150" s="23">
-        <f>E150</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H150" s="59">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="I150" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J150" s="59"/>
       <c r="K150" s="60"/>
@@ -13059,37 +12893,31 @@
       <c r="BN150" s="129"/>
       <c r="BO150" s="129"/>
     </row>
-    <row r="151" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>7647</v>
+        <f t="shared" si="29"/>
+        <v>6411</v>
       </c>
       <c r="B151" s="54" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C151" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D151" s="119">
-        <v>1001097747647</v>
+        <v>1001093316411</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="58">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G151" s="23">
-        <f>E151*F151</f>
+        <f t="shared" ref="G151" si="32">E151*F151</f>
         <v>0</v>
       </c>
-      <c r="H151" s="59">
-        <v>1</v>
-      </c>
-      <c r="I151" s="59">
-        <v>30</v>
-      </c>
-      <c r="J151" s="132" t="s">
-        <v>208</v>
-      </c>
+      <c r="H151" s="59"/>
+      <c r="I151" s="59"/>
+      <c r="J151" s="59"/>
       <c r="K151" s="60"/>
       <c r="L151" s="129"/>
       <c r="M151" s="129"/>
@@ -13148,37 +12976,35 @@
       <c r="BN151" s="129"/>
       <c r="BO151" s="129"/>
     </row>
-    <row r="152" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="56" t="str">
-        <f t="shared" si="28"/>
-        <v>7651</v>
+        <f t="shared" si="29"/>
+        <v>6925</v>
       </c>
       <c r="B152" s="54" t="s">
-        <v>207</v>
+        <v>108</v>
       </c>
       <c r="C152" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D152" s="119">
-        <v>1001097767651</v>
+        <v>1001095226925</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="58">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G152" s="23">
-        <f>E152*F152</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H152" s="59">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="I152" s="59">
-        <v>30</v>
-      </c>
-      <c r="J152" s="132" t="s">
-        <v>208</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J152" s="59"/>
       <c r="K152" s="60"/>
       <c r="L152" s="129"/>
       <c r="M152" s="129"/>
@@ -13237,169 +13063,391 @@
       <c r="BN152" s="129"/>
       <c r="BO152" s="129"/>
     </row>
-    <row r="153" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="B153" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C153" s="42"/>
-      <c r="D153" s="42"/>
-      <c r="E153" s="42"/>
-      <c r="F153" s="41"/>
-      <c r="G153" s="42"/>
-      <c r="H153" s="42"/>
-      <c r="I153" s="42"/>
-      <c r="J153" s="43"/>
+    <row r="153" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="56" t="str">
+        <f t="shared" si="29"/>
+        <v>6025</v>
+      </c>
+      <c r="B153" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C153" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D153" s="119">
+        <v>1001094966025</v>
+      </c>
+      <c r="E153" s="24"/>
+      <c r="F153" s="58">
+        <v>3</v>
+      </c>
+      <c r="G153" s="23">
+        <f>E153</f>
+        <v>0</v>
+      </c>
+      <c r="H153" s="59">
+        <v>6</v>
+      </c>
+      <c r="I153" s="59">
+        <v>60</v>
+      </c>
+      <c r="J153" s="59"/>
+      <c r="K153" s="60"/>
       <c r="L153" s="129"/>
-    </row>
-    <row r="154" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M153" s="129"/>
+      <c r="N153" s="129"/>
+      <c r="O153" s="129"/>
+      <c r="P153" s="129"/>
+      <c r="Q153" s="129"/>
+      <c r="R153" s="129"/>
+      <c r="S153" s="129"/>
+      <c r="T153" s="129"/>
+      <c r="U153" s="129"/>
+      <c r="V153" s="129"/>
+      <c r="W153" s="129"/>
+      <c r="X153" s="129"/>
+      <c r="Y153" s="129"/>
+      <c r="Z153" s="129"/>
+      <c r="AA153" s="129"/>
+      <c r="AB153" s="129"/>
+      <c r="AC153" s="129"/>
+      <c r="AD153" s="129"/>
+      <c r="AE153" s="129"/>
+      <c r="AF153" s="129"/>
+      <c r="AG153" s="129"/>
+      <c r="AH153" s="129"/>
+      <c r="AI153" s="129"/>
+      <c r="AJ153" s="129"/>
+      <c r="AK153" s="129"/>
+      <c r="AL153" s="129"/>
+      <c r="AM153" s="129"/>
+      <c r="AN153" s="129"/>
+      <c r="AO153" s="129"/>
+      <c r="AP153" s="129"/>
+      <c r="AQ153" s="129"/>
+      <c r="AR153" s="129"/>
+      <c r="AS153" s="129"/>
+      <c r="AT153" s="129"/>
+      <c r="AU153" s="129"/>
+      <c r="AV153" s="129"/>
+      <c r="AW153" s="129"/>
+      <c r="AX153" s="129"/>
+      <c r="AY153" s="129"/>
+      <c r="AZ153" s="129"/>
+      <c r="BA153" s="129"/>
+      <c r="BB153" s="129"/>
+      <c r="BC153" s="129"/>
+      <c r="BD153" s="129"/>
+      <c r="BE153" s="129"/>
+      <c r="BF153" s="129"/>
+      <c r="BG153" s="129"/>
+      <c r="BH153" s="129"/>
+      <c r="BI153" s="129"/>
+      <c r="BJ153" s="129"/>
+      <c r="BK153" s="129"/>
+      <c r="BL153" s="129"/>
+      <c r="BM153" s="129"/>
+      <c r="BN153" s="129"/>
+      <c r="BO153" s="129"/>
+    </row>
+    <row r="154" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="56" t="str">
-        <f t="shared" ref="A154:A165" si="32">RIGHT(D154,4)</f>
-        <v>7090</v>
-      </c>
-      <c r="B154" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C154" s="50" t="s">
+        <f t="shared" si="29"/>
+        <v>7485</v>
+      </c>
+      <c r="B154" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C154" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D154" s="51">
-        <v>1001084217090</v>
+      <c r="D154" s="119">
+        <v>1001107397485</v>
       </c>
       <c r="E154" s="24"/>
-      <c r="F154" s="23">
-        <v>0.3</v>
+      <c r="F154" s="58">
+        <v>0.15</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" ref="G154:G155" si="33">E154*F154</f>
+        <f>F154*E154</f>
         <v>0</v>
       </c>
-      <c r="H154" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I154" s="14">
-        <v>50</v>
-      </c>
-      <c r="J154" s="29"/>
+      <c r="H154" s="59"/>
+      <c r="I154" s="59"/>
+      <c r="J154" s="59"/>
+      <c r="K154" s="60"/>
       <c r="L154" s="129"/>
-    </row>
-    <row r="155" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M154" s="129"/>
+      <c r="N154" s="129"/>
+      <c r="O154" s="129"/>
+      <c r="P154" s="129"/>
+      <c r="Q154" s="129"/>
+      <c r="R154" s="129"/>
+      <c r="S154" s="129"/>
+      <c r="T154" s="129"/>
+      <c r="U154" s="129"/>
+      <c r="V154" s="129"/>
+      <c r="W154" s="129"/>
+      <c r="X154" s="129"/>
+      <c r="Y154" s="129"/>
+      <c r="Z154" s="129"/>
+      <c r="AA154" s="129"/>
+      <c r="AB154" s="129"/>
+      <c r="AC154" s="129"/>
+      <c r="AD154" s="129"/>
+      <c r="AE154" s="129"/>
+      <c r="AF154" s="129"/>
+      <c r="AG154" s="129"/>
+      <c r="AH154" s="129"/>
+      <c r="AI154" s="129"/>
+      <c r="AJ154" s="129"/>
+      <c r="AK154" s="129"/>
+      <c r="AL154" s="129"/>
+      <c r="AM154" s="129"/>
+      <c r="AN154" s="129"/>
+      <c r="AO154" s="129"/>
+      <c r="AP154" s="129"/>
+      <c r="AQ154" s="129"/>
+      <c r="AR154" s="129"/>
+      <c r="AS154" s="129"/>
+      <c r="AT154" s="129"/>
+      <c r="AU154" s="129"/>
+      <c r="AV154" s="129"/>
+      <c r="AW154" s="129"/>
+      <c r="AX154" s="129"/>
+      <c r="AY154" s="129"/>
+      <c r="AZ154" s="129"/>
+      <c r="BA154" s="129"/>
+      <c r="BB154" s="129"/>
+      <c r="BC154" s="129"/>
+      <c r="BD154" s="129"/>
+      <c r="BE154" s="129"/>
+      <c r="BF154" s="129"/>
+      <c r="BG154" s="129"/>
+      <c r="BH154" s="129"/>
+      <c r="BI154" s="129"/>
+      <c r="BJ154" s="129"/>
+      <c r="BK154" s="129"/>
+      <c r="BL154" s="129"/>
+      <c r="BM154" s="129"/>
+      <c r="BN154" s="129"/>
+      <c r="BO154" s="129"/>
+    </row>
+    <row r="155" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>7187</v>
-      </c>
-      <c r="B155" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C155" s="50" t="s">
+        <f t="shared" si="29"/>
+        <v>7647</v>
+      </c>
+      <c r="B155" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C155" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D155" s="51">
-        <v>1001085637187</v>
+      <c r="D155" s="119">
+        <v>1001097747647</v>
       </c>
       <c r="E155" s="24"/>
-      <c r="F155" s="23">
-        <v>0.3</v>
+      <c r="F155" s="58">
+        <v>0.1</v>
       </c>
       <c r="G155" s="23">
-        <f t="shared" si="33"/>
+        <f>E155*F155</f>
         <v>0</v>
       </c>
-      <c r="H155" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I155" s="14">
-        <v>50</v>
-      </c>
-      <c r="J155" s="29"/>
+      <c r="H155" s="59">
+        <v>1</v>
+      </c>
+      <c r="I155" s="59">
+        <v>30</v>
+      </c>
+      <c r="J155" s="132" t="s">
+        <v>208</v>
+      </c>
+      <c r="K155" s="60"/>
       <c r="L155" s="129"/>
-    </row>
-    <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M155" s="129"/>
+      <c r="N155" s="129"/>
+      <c r="O155" s="129"/>
+      <c r="P155" s="129"/>
+      <c r="Q155" s="129"/>
+      <c r="R155" s="129"/>
+      <c r="S155" s="129"/>
+      <c r="T155" s="129"/>
+      <c r="U155" s="129"/>
+      <c r="V155" s="129"/>
+      <c r="W155" s="129"/>
+      <c r="X155" s="129"/>
+      <c r="Y155" s="129"/>
+      <c r="Z155" s="129"/>
+      <c r="AA155" s="129"/>
+      <c r="AB155" s="129"/>
+      <c r="AC155" s="129"/>
+      <c r="AD155" s="129"/>
+      <c r="AE155" s="129"/>
+      <c r="AF155" s="129"/>
+      <c r="AG155" s="129"/>
+      <c r="AH155" s="129"/>
+      <c r="AI155" s="129"/>
+      <c r="AJ155" s="129"/>
+      <c r="AK155" s="129"/>
+      <c r="AL155" s="129"/>
+      <c r="AM155" s="129"/>
+      <c r="AN155" s="129"/>
+      <c r="AO155" s="129"/>
+      <c r="AP155" s="129"/>
+      <c r="AQ155" s="129"/>
+      <c r="AR155" s="129"/>
+      <c r="AS155" s="129"/>
+      <c r="AT155" s="129"/>
+      <c r="AU155" s="129"/>
+      <c r="AV155" s="129"/>
+      <c r="AW155" s="129"/>
+      <c r="AX155" s="129"/>
+      <c r="AY155" s="129"/>
+      <c r="AZ155" s="129"/>
+      <c r="BA155" s="129"/>
+      <c r="BB155" s="129"/>
+      <c r="BC155" s="129"/>
+      <c r="BD155" s="129"/>
+      <c r="BE155" s="129"/>
+      <c r="BF155" s="129"/>
+      <c r="BG155" s="129"/>
+      <c r="BH155" s="129"/>
+      <c r="BI155" s="129"/>
+      <c r="BJ155" s="129"/>
+      <c r="BK155" s="129"/>
+      <c r="BL155" s="129"/>
+      <c r="BM155" s="129"/>
+      <c r="BN155" s="129"/>
+      <c r="BO155" s="129"/>
+    </row>
+    <row r="156" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>6008</v>
-      </c>
-      <c r="B156" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="C156" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D156" s="51">
-        <v>1001084856008</v>
+        <f t="shared" si="29"/>
+        <v>7651</v>
+      </c>
+      <c r="B156" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="C156" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" s="119">
+        <v>1001097767651</v>
       </c>
       <c r="E156" s="24"/>
-      <c r="F156" s="23">
-        <v>0.3</v>
+      <c r="F156" s="58">
+        <v>0.1</v>
       </c>
       <c r="G156" s="23">
-        <f>E156</f>
+        <f>E156*F156</f>
         <v>0</v>
       </c>
-      <c r="H156" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I156" s="14">
-        <v>40</v>
+      <c r="H156" s="59">
+        <v>1</v>
+      </c>
+      <c r="I156" s="59">
+        <v>30</v>
       </c>
       <c r="J156" s="132" t="s">
         <v>208</v>
       </c>
+      <c r="K156" s="60"/>
       <c r="L156" s="129"/>
-    </row>
-    <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>6620</v>
-      </c>
-      <c r="B157" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C157" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D157" s="51">
-        <v>1001081596620</v>
-      </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="23">
-        <v>1.05</v>
-      </c>
-      <c r="G157" s="23">
-        <f>E157</f>
-        <v>0</v>
-      </c>
-      <c r="H157" s="14">
-        <v>3.15</v>
-      </c>
-      <c r="I157" s="14">
-        <v>30</v>
-      </c>
-      <c r="J157" s="29"/>
+      <c r="M156" s="129"/>
+      <c r="N156" s="129"/>
+      <c r="O156" s="129"/>
+      <c r="P156" s="129"/>
+      <c r="Q156" s="129"/>
+      <c r="R156" s="129"/>
+      <c r="S156" s="129"/>
+      <c r="T156" s="129"/>
+      <c r="U156" s="129"/>
+      <c r="V156" s="129"/>
+      <c r="W156" s="129"/>
+      <c r="X156" s="129"/>
+      <c r="Y156" s="129"/>
+      <c r="Z156" s="129"/>
+      <c r="AA156" s="129"/>
+      <c r="AB156" s="129"/>
+      <c r="AC156" s="129"/>
+      <c r="AD156" s="129"/>
+      <c r="AE156" s="129"/>
+      <c r="AF156" s="129"/>
+      <c r="AG156" s="129"/>
+      <c r="AH156" s="129"/>
+      <c r="AI156" s="129"/>
+      <c r="AJ156" s="129"/>
+      <c r="AK156" s="129"/>
+      <c r="AL156" s="129"/>
+      <c r="AM156" s="129"/>
+      <c r="AN156" s="129"/>
+      <c r="AO156" s="129"/>
+      <c r="AP156" s="129"/>
+      <c r="AQ156" s="129"/>
+      <c r="AR156" s="129"/>
+      <c r="AS156" s="129"/>
+      <c r="AT156" s="129"/>
+      <c r="AU156" s="129"/>
+      <c r="AV156" s="129"/>
+      <c r="AW156" s="129"/>
+      <c r="AX156" s="129"/>
+      <c r="AY156" s="129"/>
+      <c r="AZ156" s="129"/>
+      <c r="BA156" s="129"/>
+      <c r="BB156" s="129"/>
+      <c r="BC156" s="129"/>
+      <c r="BD156" s="129"/>
+      <c r="BE156" s="129"/>
+      <c r="BF156" s="129"/>
+      <c r="BG156" s="129"/>
+      <c r="BH156" s="129"/>
+      <c r="BI156" s="129"/>
+      <c r="BJ156" s="129"/>
+      <c r="BK156" s="129"/>
+      <c r="BL156" s="129"/>
+      <c r="BM156" s="129"/>
+      <c r="BN156" s="129"/>
+      <c r="BO156" s="129"/>
+    </row>
+    <row r="157" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B157" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C157" s="42"/>
+      <c r="D157" s="42"/>
+      <c r="E157" s="42"/>
+      <c r="F157" s="41"/>
+      <c r="G157" s="42"/>
+      <c r="H157" s="42"/>
+      <c r="I157" s="42"/>
+      <c r="J157" s="43"/>
       <c r="L157" s="129"/>
     </row>
-    <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A158" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>7103</v>
+        <f t="shared" ref="A158:A169" si="33">RIGHT(D158,4)</f>
+        <v>7090</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001223297103</v>
+        <v>1001084217090</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="G158" s="23">
-        <f t="shared" ref="G158:G165" si="34">E158*F158</f>
+        <f t="shared" ref="G158:G159" si="34">E158*F158</f>
         <v>0</v>
       </c>
       <c r="H158" s="14">
@@ -13413,28 +13461,28 @@
     </row>
     <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>7092</v>
+        <f t="shared" si="33"/>
+        <v>7187</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D159" s="51">
-        <v>1001223297092</v>
+        <v>1001085637187</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="G159" s="23">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I159" s="14">
         <v>50</v>
@@ -13444,152 +13492,154 @@
     </row>
     <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>6228</v>
+        <f t="shared" si="33"/>
+        <v>6008</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D160" s="51">
-        <v>1001225416228</v>
+        <v>1001084856008</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="G160" s="23">
-        <f t="shared" si="34"/>
+        <f>E160</f>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="I160" s="14">
-        <v>45</v>
-      </c>
-      <c r="J160" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J160" s="132" t="s">
+        <v>208</v>
+      </c>
       <c r="L160" s="129"/>
     </row>
     <row r="161" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>6448</v>
+        <f t="shared" si="33"/>
+        <v>6620</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D161" s="51">
-        <v>1001234146448</v>
+        <v>1001081596620</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.1</v>
+        <v>1.05</v>
       </c>
       <c r="G161" s="23">
-        <f t="shared" si="34"/>
+        <f>E161</f>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>1</v>
+        <v>3.15</v>
       </c>
       <c r="I161" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J161" s="29"/>
       <c r="L161" s="129"/>
     </row>
     <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>6208</v>
+        <f t="shared" si="33"/>
+        <v>7103</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D162" s="51">
-        <v>1001220226208</v>
+        <v>1001223297103</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="23">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="G162" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="G162:G169" si="35">E162*F162</f>
         <v>0</v>
       </c>
       <c r="H162" s="14">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I162" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J162" s="29"/>
       <c r="L162" s="129"/>
     </row>
     <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>6754</v>
+        <f t="shared" si="33"/>
+        <v>7092</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="C163" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D163" s="51">
-        <v>1001225406754</v>
+        <v>1001223297092</v>
       </c>
       <c r="E163" s="24"/>
       <c r="F163" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G163" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="H163" s="14">
-        <v>0.72</v>
+        <v>1.4</v>
       </c>
       <c r="I163" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J163" s="29"/>
       <c r="L163" s="129"/>
     </row>
     <row r="164" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>6279</v>
+        <f t="shared" si="33"/>
+        <v>6228</v>
       </c>
       <c r="B164" s="35" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C164" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D164" s="51">
-        <v>1001220286279</v>
+        <v>1001225416228</v>
       </c>
       <c r="E164" s="24"/>
       <c r="F164" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G164" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="H164" s="14">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I164" s="14">
         <v>45</v>
@@ -13597,100 +13647,184 @@
       <c r="J164" s="29"/>
       <c r="L164" s="129"/>
     </row>
-    <row r="165" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v>7612</v>
+        <f t="shared" si="33"/>
+        <v>6448</v>
       </c>
       <c r="B165" s="35" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C165" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D165" s="51">
-        <v>1001453907612</v>
+        <v>1001234146448</v>
       </c>
       <c r="E165" s="24"/>
       <c r="F165" s="23">
         <v>0.1</v>
       </c>
       <c r="G165" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="H165" s="14">
         <v>1</v>
       </c>
       <c r="I165" s="14">
+        <v>45</v>
+      </c>
+      <c r="J165" s="29"/>
+      <c r="L165" s="129"/>
+    </row>
+    <row r="166" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v>6208</v>
+      </c>
+      <c r="B166" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C166" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D166" s="51">
+        <v>1001220226208</v>
+      </c>
+      <c r="E166" s="24"/>
+      <c r="F166" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G166" s="23">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="H166" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="I166" s="14">
+        <v>45</v>
+      </c>
+      <c r="J166" s="29"/>
+      <c r="L166" s="129"/>
+    </row>
+    <row r="167" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v>6754</v>
+      </c>
+      <c r="B167" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="C167" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D167" s="51">
+        <v>1001225406754</v>
+      </c>
+      <c r="E167" s="24"/>
+      <c r="F167" s="23">
+        <v>0.09</v>
+      </c>
+      <c r="G167" s="23">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="H167" s="14">
+        <v>0.72</v>
+      </c>
+      <c r="I167" s="14">
         <v>60</v>
       </c>
-      <c r="J165" s="52" t="s">
+      <c r="J167" s="29"/>
+      <c r="L167" s="129"/>
+    </row>
+    <row r="168" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v>6279</v>
+      </c>
+      <c r="B168" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C168" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" s="51">
+        <v>1001220286279</v>
+      </c>
+      <c r="E168" s="24"/>
+      <c r="F168" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G168" s="23">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="H168" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I168" s="14">
+        <v>45</v>
+      </c>
+      <c r="J168" s="29"/>
+      <c r="L168" s="129"/>
+    </row>
+    <row r="169" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v>7612</v>
+      </c>
+      <c r="B169" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C169" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D169" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E169" s="24"/>
+      <c r="F169" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G169" s="23">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="H169" s="14">
+        <v>1</v>
+      </c>
+      <c r="I169" s="14">
+        <v>60</v>
+      </c>
+      <c r="J169" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="L165" s="129"/>
-    </row>
-    <row r="166" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="48"/>
-      <c r="B166" s="45" t="s">
+      <c r="L169" s="129"/>
+    </row>
+    <row r="170" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="48"/>
+      <c r="B170" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C166" s="16"/>
-      <c r="D166" s="36"/>
-      <c r="E166" s="17">
-        <f>SUM(E10:E165)</f>
+      <c r="C170" s="16"/>
+      <c r="D170" s="36"/>
+      <c r="E170" s="17">
+        <f>SUM(E10:E169)</f>
         <v>0</v>
       </c>
-      <c r="F166" s="17"/>
-      <c r="G166" s="17">
-        <f>SUM(G11:G165)</f>
+      <c r="F170" s="17"/>
+      <c r="G170" s="17">
+        <f>SUM(G11:G169)</f>
         <v>0</v>
       </c>
-      <c r="H166" s="17"/>
-      <c r="I166" s="17"/>
-      <c r="J166" s="17"/>
-    </row>
-    <row r="167" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="37"/>
-      <c r="C167" s="18"/>
-      <c r="D167" s="40"/>
-      <c r="F167" s="19"/>
-      <c r="G167" s="19"/>
-      <c r="H167" s="20"/>
-      <c r="I167" s="20"/>
-      <c r="J167" s="21"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B168" s="37"/>
-      <c r="C168" s="18"/>
-      <c r="D168" s="40"/>
-      <c r="F168" s="19"/>
-      <c r="G168" s="19"/>
-      <c r="H168" s="20"/>
-      <c r="I168" s="20"/>
-      <c r="J168" s="21"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B169" s="37"/>
-      <c r="C169" s="18"/>
-      <c r="D169" s="40"/>
-      <c r="F169" s="19"/>
-      <c r="G169" s="19"/>
-      <c r="H169" s="20"/>
-      <c r="I169" s="20"/>
-      <c r="J169" s="21"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B170" s="37"/>
-      <c r="C170" s="18"/>
-      <c r="D170" s="40"/>
-      <c r="F170" s="19"/>
-      <c r="G170" s="19"/>
-      <c r="H170" s="20"/>
-      <c r="I170" s="20"/>
-      <c r="J170" s="21"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H170" s="17"/>
+      <c r="I170" s="17"/>
+      <c r="J170" s="17"/>
+    </row>
+    <row r="171" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
       <c r="C171" s="18"/>
       <c r="D171" s="40"/>
@@ -13712,35 +13846,32 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
-      <c r="C173" s="62"/>
-      <c r="D173" s="63"/>
-      <c r="E173" s="64"/>
-      <c r="F173" s="65"/>
-      <c r="G173" s="65"/>
-      <c r="H173" s="66"/>
-      <c r="I173" s="66"/>
+      <c r="C173" s="18"/>
+      <c r="D173" s="40"/>
+      <c r="F173" s="19"/>
+      <c r="G173" s="19"/>
+      <c r="H173" s="20"/>
+      <c r="I173" s="20"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
-      <c r="C174" s="62"/>
-      <c r="D174" s="63"/>
-      <c r="E174" s="64"/>
-      <c r="F174" s="65"/>
-      <c r="G174" s="65"/>
-      <c r="H174" s="66"/>
-      <c r="I174" s="66"/>
+      <c r="C174" s="18"/>
+      <c r="D174" s="40"/>
+      <c r="F174" s="19"/>
+      <c r="G174" s="19"/>
+      <c r="H174" s="20"/>
+      <c r="I174" s="20"/>
       <c r="J174" s="21"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B175" s="37"/>
-      <c r="C175" s="62"/>
-      <c r="D175" s="67"/>
-      <c r="E175" s="68"/>
-      <c r="F175" s="67"/>
-      <c r="G175" s="69"/>
-      <c r="H175" s="70"/>
-      <c r="I175" s="71"/>
+      <c r="C175" s="18"/>
+      <c r="D175" s="40"/>
+      <c r="F175" s="19"/>
+      <c r="G175" s="19"/>
+      <c r="H175" s="20"/>
+      <c r="I175" s="20"/>
       <c r="J175" s="21"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -13755,32 +13886,35 @@
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="37"/>
-      <c r="C177" s="18"/>
-      <c r="D177" s="40"/>
-      <c r="F177" s="19"/>
-      <c r="G177" s="19"/>
-      <c r="H177" s="20"/>
-      <c r="I177" s="20"/>
+      <c r="C177" s="62"/>
+      <c r="D177" s="63"/>
+      <c r="E177" s="64"/>
+      <c r="F177" s="65"/>
+      <c r="G177" s="65"/>
+      <c r="H177" s="66"/>
+      <c r="I177" s="66"/>
       <c r="J177" s="21"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="37"/>
-      <c r="C178" s="18"/>
-      <c r="D178" s="40"/>
-      <c r="F178" s="19"/>
-      <c r="G178" s="19"/>
-      <c r="H178" s="20"/>
-      <c r="I178" s="20"/>
+      <c r="C178" s="62"/>
+      <c r="D178" s="63"/>
+      <c r="E178" s="64"/>
+      <c r="F178" s="65"/>
+      <c r="G178" s="65"/>
+      <c r="H178" s="66"/>
+      <c r="I178" s="66"/>
       <c r="J178" s="21"/>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="37"/>
-      <c r="C179" s="18"/>
-      <c r="D179" s="40"/>
-      <c r="F179" s="19"/>
-      <c r="G179" s="19"/>
-      <c r="H179" s="20"/>
-      <c r="I179" s="20"/>
+      <c r="C179" s="62"/>
+      <c r="D179" s="67"/>
+      <c r="E179" s="68"/>
+      <c r="F179" s="67"/>
+      <c r="G179" s="69"/>
+      <c r="H179" s="70"/>
+      <c r="I179" s="71"/>
       <c r="J179" s="21"/>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.25">
@@ -28893,13 +29027,53 @@
       <c r="I1690" s="20"/>
       <c r="J1690" s="21"/>
     </row>
+    <row r="1691" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1691" s="37"/>
+      <c r="C1691" s="18"/>
+      <c r="D1691" s="40"/>
+      <c r="F1691" s="19"/>
+      <c r="G1691" s="19"/>
+      <c r="H1691" s="20"/>
+      <c r="I1691" s="20"/>
+      <c r="J1691" s="21"/>
+    </row>
+    <row r="1692" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1692" s="37"/>
+      <c r="C1692" s="18"/>
+      <c r="D1692" s="40"/>
+      <c r="F1692" s="19"/>
+      <c r="G1692" s="19"/>
+      <c r="H1692" s="20"/>
+      <c r="I1692" s="20"/>
+      <c r="J1692" s="21"/>
+    </row>
+    <row r="1693" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1693" s="37"/>
+      <c r="C1693" s="18"/>
+      <c r="D1693" s="40"/>
+      <c r="F1693" s="19"/>
+      <c r="G1693" s="19"/>
+      <c r="H1693" s="20"/>
+      <c r="I1693" s="20"/>
+      <c r="J1693" s="21"/>
+    </row>
+    <row r="1694" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1694" s="37"/>
+      <c r="C1694" s="18"/>
+      <c r="D1694" s="40"/>
+      <c r="F1694" s="19"/>
+      <c r="G1694" s="19"/>
+      <c r="H1694" s="20"/>
+      <c r="I1694" s="20"/>
+      <c r="J1694" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J166" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J170" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D175">
+  <conditionalFormatting sqref="D179">
     <cfRule type="duplicateValues" dxfId="312" priority="1"/>
     <cfRule type="duplicateValues" dxfId="311" priority="2"/>
     <cfRule type="duplicateValues" dxfId="310" priority="3"/>
@@ -28911,7 +29085,7 @@
     <cfRule type="duplicateValues" dxfId="304" priority="10"/>
     <cfRule type="duplicateValues" dxfId="303" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D175">
+  <conditionalFormatting sqref="D179">
     <cfRule type="duplicateValues" dxfId="302" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457C6F29-4803-44DD-BD59-626ADD33857A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E239A513-8616-4598-B54F-11F9AB62ED5B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$132</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$568</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$568</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$133</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$569</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$569</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="230">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1178,6 +1178,9 @@
   <si>
     <t>Ротация кода 7284</t>
   </si>
+  <si>
+    <t>ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.</t>
+  </si>
 </sst>
 </file>
 
@@ -1689,7 +1692,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2070,6 +2073,9 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2078,8 +2084,14 @@
     <xf numFmtId="165" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5620,7 +5632,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1656"/>
+  <dimension ref="A1:BO1657"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -5643,16 +5655,17 @@
         <v>0</v>
       </c>
       <c r="D1" s="133">
+        <f>K1</f>
         <v>130438122</v>
       </c>
-      <c r="E1" s="134" t="s">
+      <c r="E1" s="135" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="137"/>
       <c r="K1" s="129">
         <v>130438122</v>
       </c>
@@ -5683,13 +5696,13 @@
         <f>D3+3</f>
         <v>46219</v>
       </c>
-      <c r="G3" s="137" t="str">
+      <c r="G3" s="138" t="str">
         <f>VLOOKUP(D1,K:L,2,0)</f>
         <v>130438122 ООО "НОВОЕ ВРЕМЯ"  272151 Бердянский р-н 90  Трояны</v>
       </c>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="137"/>
       <c r="K3" s="129">
         <v>130438120</v>
       </c>
@@ -9231,7 +9244,7 @@
         <f t="shared" si="13"/>
         <v>7059</v>
       </c>
-      <c r="B63" s="138" t="s">
+      <c r="B63" s="134" t="s">
         <v>177</v>
       </c>
       <c r="C63" s="50" t="s">
@@ -10689,7 +10702,7 @@
     </row>
     <row r="108" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A108" s="56" t="str">
-        <f t="shared" ref="A108:A120" si="27">RIGHT(D108,4)</f>
+        <f t="shared" ref="A108:A121" si="27">RIGHT(D108,4)</f>
         <v>4584</v>
       </c>
       <c r="B108" s="120" t="s">
@@ -11172,7 +11185,7 @@
         <v>0.4</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" ref="G114:G116" si="29">E114*F114</f>
+        <f t="shared" ref="G114:G117" si="29">E114*F114</f>
         <v>0</v>
       </c>
       <c r="H114" s="59">
@@ -11327,120 +11340,115 @@
       <c r="BN115" s="128"/>
       <c r="BO115" s="128"/>
     </row>
-    <row r="116" spans="1:67" s="60" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="56" t="str">
+    <row r="116" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="139" t="str">
         <f t="shared" si="27"/>
-        <v>6925</v>
-      </c>
-      <c r="B116" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C116" s="55" t="s">
+        <v>6411</v>
+      </c>
+      <c r="B116" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D116" s="118">
-        <v>1001095226925</v>
+      <c r="D116" s="140">
+        <v>1001093316411</v>
       </c>
       <c r="E116" s="24"/>
-      <c r="F116" s="58">
-        <v>0.6</v>
+      <c r="F116" s="141">
+        <v>0.3</v>
       </c>
       <c r="G116" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H116" s="59">
-        <v>4.8</v>
-      </c>
-      <c r="I116" s="59">
-        <v>45</v>
-      </c>
-      <c r="J116" s="59"/>
-      <c r="K116" s="27"/>
-      <c r="L116" s="128"/>
-      <c r="M116" s="128"/>
-      <c r="N116" s="128"/>
-      <c r="O116" s="128"/>
-      <c r="P116" s="128"/>
-      <c r="Q116" s="128"/>
-      <c r="R116" s="128"/>
-      <c r="S116" s="128"/>
-      <c r="T116" s="128"/>
-      <c r="U116" s="128"/>
-      <c r="V116" s="128"/>
-      <c r="W116" s="128"/>
-      <c r="X116" s="128"/>
-      <c r="Y116" s="128"/>
-      <c r="Z116" s="128"/>
-      <c r="AA116" s="128"/>
-      <c r="AB116" s="128"/>
-      <c r="AC116" s="128"/>
-      <c r="AD116" s="128"/>
-      <c r="AE116" s="128"/>
-      <c r="AF116" s="128"/>
-      <c r="AG116" s="128"/>
-      <c r="AH116" s="128"/>
-      <c r="AI116" s="128"/>
-      <c r="AJ116" s="128"/>
-      <c r="AK116" s="128"/>
-      <c r="AL116" s="128"/>
-      <c r="AM116" s="128"/>
-      <c r="AN116" s="128"/>
-      <c r="AO116" s="128"/>
-      <c r="AP116" s="128"/>
-      <c r="AQ116" s="128"/>
-      <c r="AR116" s="128"/>
-      <c r="AS116" s="128"/>
-      <c r="AT116" s="128"/>
-      <c r="AU116" s="128"/>
-      <c r="AV116" s="128"/>
-      <c r="AW116" s="128"/>
-      <c r="AX116" s="128"/>
-      <c r="AY116" s="128"/>
-      <c r="AZ116" s="128"/>
-      <c r="BA116" s="128"/>
-      <c r="BB116" s="128"/>
-      <c r="BC116" s="128"/>
-      <c r="BD116" s="128"/>
-      <c r="BE116" s="128"/>
-      <c r="BF116" s="128"/>
-      <c r="BG116" s="128"/>
-      <c r="BH116" s="128"/>
-      <c r="BI116" s="128"/>
-      <c r="BJ116" s="128"/>
-      <c r="BK116" s="128"/>
-      <c r="BL116" s="128"/>
-      <c r="BM116" s="128"/>
-      <c r="BN116" s="128"/>
-      <c r="BO116" s="128"/>
-    </row>
-    <row r="117" spans="1:67" s="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H116" s="29"/>
+      <c r="I116" s="29"/>
+      <c r="J116" s="29"/>
+      <c r="L116"/>
+      <c r="M116"/>
+      <c r="N116"/>
+      <c r="O116"/>
+      <c r="P116"/>
+      <c r="Q116"/>
+      <c r="R116"/>
+      <c r="S116"/>
+      <c r="T116"/>
+      <c r="U116"/>
+      <c r="V116"/>
+      <c r="W116"/>
+      <c r="X116"/>
+      <c r="Y116"/>
+      <c r="Z116"/>
+      <c r="AA116"/>
+      <c r="AB116"/>
+      <c r="AC116"/>
+      <c r="AD116"/>
+      <c r="AE116"/>
+      <c r="AF116"/>
+      <c r="AG116"/>
+      <c r="AH116"/>
+      <c r="AI116"/>
+      <c r="AJ116"/>
+      <c r="AK116"/>
+      <c r="AL116"/>
+      <c r="AM116"/>
+      <c r="AN116"/>
+      <c r="AO116"/>
+      <c r="AP116"/>
+      <c r="AQ116"/>
+      <c r="AR116"/>
+      <c r="AS116"/>
+      <c r="AT116"/>
+      <c r="AU116"/>
+      <c r="AV116"/>
+      <c r="AW116"/>
+      <c r="AX116"/>
+      <c r="AY116"/>
+      <c r="AZ116"/>
+      <c r="BA116"/>
+      <c r="BB116"/>
+      <c r="BC116"/>
+      <c r="BD116"/>
+      <c r="BE116"/>
+      <c r="BF116"/>
+      <c r="BG116"/>
+      <c r="BH116"/>
+      <c r="BI116"/>
+      <c r="BJ116"/>
+      <c r="BK116"/>
+      <c r="BL116"/>
+      <c r="BM116"/>
+      <c r="BN116"/>
+      <c r="BO116"/>
+    </row>
+    <row r="117" spans="1:67" s="60" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="56" t="str">
         <f t="shared" si="27"/>
-        <v>6025</v>
+        <v>6925</v>
       </c>
       <c r="B117" s="54" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C117" s="55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D117" s="118">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="58">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G117" s="23">
-        <f>E117</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H117" s="59">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I117" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J117" s="59"/>
       <c r="K117" s="27"/>
@@ -11504,30 +11512,32 @@
     <row r="118" spans="1:67" s="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="56" t="str">
         <f t="shared" si="27"/>
-        <v>7485</v>
+        <v>6025</v>
       </c>
       <c r="B118" s="54" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="C118" s="55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D118" s="118">
-        <v>1001107397485</v>
+        <v>1001094966025</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="58">
-        <v>0.15</v>
+        <v>3</v>
       </c>
       <c r="G118" s="23">
-        <f>F118*E118</f>
+        <f>E118</f>
         <v>0</v>
       </c>
-      <c r="H118" s="59"/>
-      <c r="I118" s="59"/>
-      <c r="J118" s="131" t="s">
-        <v>207</v>
-      </c>
+      <c r="H118" s="59">
+        <v>6</v>
+      </c>
+      <c r="I118" s="59">
+        <v>60</v>
+      </c>
+      <c r="J118" s="59"/>
       <c r="K118" s="27"/>
       <c r="L118" s="128"/>
       <c r="M118" s="128"/>
@@ -11589,31 +11599,27 @@
     <row r="119" spans="1:67" s="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="56" t="str">
         <f t="shared" si="27"/>
-        <v>7647</v>
+        <v>7485</v>
       </c>
       <c r="B119" s="54" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C119" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="118">
-        <v>1001097747647</v>
+        <v>1001107397485</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="58">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G119" s="23">
-        <f>E119*F119</f>
+        <f>F119*E119</f>
         <v>0</v>
       </c>
-      <c r="H119" s="59">
-        <v>1</v>
-      </c>
-      <c r="I119" s="59">
-        <v>30</v>
-      </c>
+      <c r="H119" s="59"/>
+      <c r="I119" s="59"/>
       <c r="J119" s="131" t="s">
         <v>207</v>
       </c>
@@ -11675,19 +11681,19 @@
       <c r="BN119" s="128"/>
       <c r="BO119" s="128"/>
     </row>
-    <row r="120" spans="1:67" s="60" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:67" s="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="56" t="str">
         <f t="shared" si="27"/>
-        <v>7651</v>
+        <v>7647</v>
       </c>
       <c r="B120" s="54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C120" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="118">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="58">
@@ -11764,74 +11770,132 @@
       <c r="BN120" s="128"/>
       <c r="BO120" s="128"/>
     </row>
-    <row r="121" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="47" t="s">
+    <row r="121" spans="1:67" s="60" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="56" t="str">
+        <f t="shared" si="27"/>
+        <v>7651</v>
+      </c>
+      <c r="B121" s="54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C121" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="118">
+        <v>1001097767651</v>
+      </c>
+      <c r="E121" s="24"/>
+      <c r="F121" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G121" s="23">
+        <f>E121*F121</f>
+        <v>0</v>
+      </c>
+      <c r="H121" s="59">
+        <v>1</v>
+      </c>
+      <c r="I121" s="59">
+        <v>30</v>
+      </c>
+      <c r="J121" s="131" t="s">
+        <v>207</v>
+      </c>
+      <c r="K121" s="27"/>
+      <c r="L121" s="128"/>
+      <c r="M121" s="128"/>
+      <c r="N121" s="128"/>
+      <c r="O121" s="128"/>
+      <c r="P121" s="128"/>
+      <c r="Q121" s="128"/>
+      <c r="R121" s="128"/>
+      <c r="S121" s="128"/>
+      <c r="T121" s="128"/>
+      <c r="U121" s="128"/>
+      <c r="V121" s="128"/>
+      <c r="W121" s="128"/>
+      <c r="X121" s="128"/>
+      <c r="Y121" s="128"/>
+      <c r="Z121" s="128"/>
+      <c r="AA121" s="128"/>
+      <c r="AB121" s="128"/>
+      <c r="AC121" s="128"/>
+      <c r="AD121" s="128"/>
+      <c r="AE121" s="128"/>
+      <c r="AF121" s="128"/>
+      <c r="AG121" s="128"/>
+      <c r="AH121" s="128"/>
+      <c r="AI121" s="128"/>
+      <c r="AJ121" s="128"/>
+      <c r="AK121" s="128"/>
+      <c r="AL121" s="128"/>
+      <c r="AM121" s="128"/>
+      <c r="AN121" s="128"/>
+      <c r="AO121" s="128"/>
+      <c r="AP121" s="128"/>
+      <c r="AQ121" s="128"/>
+      <c r="AR121" s="128"/>
+      <c r="AS121" s="128"/>
+      <c r="AT121" s="128"/>
+      <c r="AU121" s="128"/>
+      <c r="AV121" s="128"/>
+      <c r="AW121" s="128"/>
+      <c r="AX121" s="128"/>
+      <c r="AY121" s="128"/>
+      <c r="AZ121" s="128"/>
+      <c r="BA121" s="128"/>
+      <c r="BB121" s="128"/>
+      <c r="BC121" s="128"/>
+      <c r="BD121" s="128"/>
+      <c r="BE121" s="128"/>
+      <c r="BF121" s="128"/>
+      <c r="BG121" s="128"/>
+      <c r="BH121" s="128"/>
+      <c r="BI121" s="128"/>
+      <c r="BJ121" s="128"/>
+      <c r="BK121" s="128"/>
+      <c r="BL121" s="128"/>
+      <c r="BM121" s="128"/>
+      <c r="BN121" s="128"/>
+      <c r="BO121" s="128"/>
+    </row>
+    <row r="122" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B121" s="42" t="s">
+      <c r="B122" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C121" s="42"/>
-      <c r="D121" s="42"/>
-      <c r="E121" s="42"/>
-      <c r="F121" s="41"/>
-      <c r="G121" s="42"/>
-      <c r="H121" s="42"/>
-      <c r="I121" s="42"/>
-      <c r="J121" s="43"/>
-      <c r="L121" s="128"/>
-    </row>
-    <row r="122" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="56" t="str">
-        <f t="shared" ref="A122:A131" si="30">RIGHT(D122,4)</f>
+      <c r="C122" s="42"/>
+      <c r="D122" s="42"/>
+      <c r="E122" s="42"/>
+      <c r="F122" s="41"/>
+      <c r="G122" s="42"/>
+      <c r="H122" s="42"/>
+      <c r="I122" s="42"/>
+      <c r="J122" s="43"/>
+      <c r="L122" s="128"/>
+    </row>
+    <row r="123" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="56" t="str">
+        <f t="shared" ref="A123:A132" si="30">RIGHT(D123,4)</f>
         <v>7090</v>
       </c>
-      <c r="B122" s="35" t="s">
+      <c r="B123" s="35" t="s">
         <v>102</v>
-      </c>
-      <c r="C122" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D122" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E122" s="24"/>
-      <c r="F122" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G122" s="23">
-        <f t="shared" ref="G122:G123" si="31">E122*F122</f>
-        <v>0</v>
-      </c>
-      <c r="H122" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I122" s="14">
-        <v>50</v>
-      </c>
-      <c r="J122" s="29"/>
-      <c r="L122" s="128"/>
-    </row>
-    <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="56" t="str">
-        <f t="shared" si="30"/>
-        <v>7187</v>
-      </c>
-      <c r="B123" s="35" t="s">
-        <v>103</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D123" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
         <v>0.3</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="G123:G124" si="31">E123*F123</f>
         <v>0</v>
       </c>
       <c r="H123" s="14">
@@ -11846,94 +11910,94 @@
     <row r="124" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="56" t="str">
         <f t="shared" si="30"/>
-        <v>6008</v>
+        <v>7187</v>
       </c>
       <c r="B124" s="35" t="s">
-        <v>208</v>
+        <v>103</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D124" s="51">
-        <v>1001084856008</v>
+        <v>1001085637187</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
         <v>0.3</v>
       </c>
       <c r="G124" s="23">
-        <f>E124</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
         <v>1.8</v>
       </c>
       <c r="I124" s="14">
-        <v>40</v>
-      </c>
-      <c r="J124" s="131" t="s">
-        <v>207</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J124" s="29"/>
       <c r="L124" s="128"/>
     </row>
     <row r="125" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="56" t="str">
         <f t="shared" si="30"/>
-        <v>6620</v>
+        <v>6008</v>
       </c>
       <c r="B125" s="35" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D125" s="51">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G125" s="23">
         <f>E125</f>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I125" s="14">
-        <v>30</v>
-      </c>
-      <c r="J125" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J125" s="131" t="s">
+        <v>207</v>
+      </c>
       <c r="L125" s="128"/>
     </row>
     <row r="126" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="56" t="str">
         <f t="shared" si="30"/>
-        <v>7103</v>
+        <v>6620</v>
       </c>
       <c r="B126" s="35" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D126" s="51">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" ref="G126:G131" si="32">E126*F126</f>
+        <f>E126</f>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I126" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J126" s="29"/>
       <c r="L126" s="128"/>
@@ -11941,27 +12005,27 @@
     <row r="127" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="56" t="str">
         <f t="shared" si="30"/>
-        <v>7092</v>
+        <v>7103</v>
       </c>
       <c r="B127" s="35" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D127" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G127" s="23">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="G127:G132" si="32">E127*F127</f>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I127" s="14">
         <v>50</v>
@@ -11972,30 +12036,30 @@
     <row r="128" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="56" t="str">
         <f t="shared" si="30"/>
-        <v>6228</v>
+        <v>7092</v>
       </c>
       <c r="B128" s="35" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D128" s="51">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G128" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I128" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J128" s="29"/>
       <c r="L128" s="128"/>
@@ -12003,27 +12067,27 @@
     <row r="129" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="56" t="str">
         <f t="shared" si="30"/>
-        <v>6208</v>
+        <v>6228</v>
       </c>
       <c r="B129" s="35" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D129" s="51">
-        <v>1001220226208</v>
+        <v>1001225416228</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G129" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H129" s="14">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I129" s="14">
         <v>45</v>
@@ -12034,16 +12098,16 @@
     <row r="130" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="56" t="str">
         <f t="shared" si="30"/>
-        <v>6279</v>
+        <v>6208</v>
       </c>
       <c r="B130" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D130" s="51">
-        <v>1001220286279</v>
+        <v>1001220226208</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
@@ -12054,7 +12118,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I130" s="14">
         <v>45</v>
@@ -12062,70 +12126,91 @@
       <c r="J130" s="29"/>
       <c r="L130" s="128"/>
     </row>
-    <row r="131" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="56" t="str">
         <f t="shared" si="30"/>
-        <v>7612</v>
+        <v>6279</v>
       </c>
       <c r="B131" s="35" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="51">
-        <v>1001453907612</v>
+        <v>1001220286279</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G131" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H131" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I131" s="14">
+        <v>45</v>
+      </c>
+      <c r="J131" s="29"/>
+      <c r="L131" s="128"/>
+    </row>
+    <row r="132" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="56" t="str">
+        <f t="shared" si="30"/>
+        <v>7612</v>
+      </c>
+      <c r="B132" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C132" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D132" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E132" s="24"/>
+      <c r="F132" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G132" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H132" s="14">
         <v>1</v>
       </c>
-      <c r="I131" s="14">
+      <c r="I132" s="14">
         <v>60</v>
       </c>
-      <c r="J131" s="52" t="s">
+      <c r="J132" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="L131" s="128"/>
-    </row>
-    <row r="132" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="48"/>
-      <c r="B132" s="45" t="s">
+      <c r="L132" s="128"/>
+    </row>
+    <row r="133" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="48"/>
+      <c r="B133" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C132" s="16"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="17">
-        <f>SUM(E10:E131)</f>
+      <c r="C133" s="16"/>
+      <c r="D133" s="36"/>
+      <c r="E133" s="17">
+        <f>SUM(E10:E132)</f>
         <v>0</v>
       </c>
-      <c r="F132" s="17"/>
-      <c r="G132" s="17">
-        <f>SUM(G11:G131)</f>
+      <c r="F133" s="17"/>
+      <c r="G133" s="17">
+        <f>SUM(G11:G132)</f>
         <v>0</v>
       </c>
-      <c r="H132" s="17"/>
-      <c r="I132" s="17"/>
-      <c r="J132" s="17"/>
-    </row>
-    <row r="133" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="37"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="40"/>
-      <c r="F133" s="19"/>
-      <c r="G133" s="19"/>
-      <c r="H133" s="20"/>
-      <c r="I133" s="20"/>
-      <c r="J133" s="21"/>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H133" s="17"/>
+      <c r="I133" s="17"/>
+      <c r="J133" s="17"/>
+    </row>
+    <row r="134" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B134" s="37"/>
       <c r="C134" s="18"/>
       <c r="D134" s="40"/>
@@ -12177,13 +12262,12 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B139" s="37"/>
-      <c r="C139" s="61"/>
-      <c r="D139" s="62"/>
-      <c r="E139" s="63"/>
-      <c r="F139" s="64"/>
-      <c r="G139" s="64"/>
-      <c r="H139" s="65"/>
-      <c r="I139" s="65"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="40"/>
+      <c r="F139" s="19"/>
+      <c r="G139" s="19"/>
+      <c r="H139" s="20"/>
+      <c r="I139" s="20"/>
       <c r="J139" s="21"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -12200,22 +12284,23 @@
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B141" s="37"/>
       <c r="C141" s="61"/>
-      <c r="D141" s="66"/>
-      <c r="E141" s="67"/>
-      <c r="F141" s="66"/>
-      <c r="G141" s="68"/>
-      <c r="H141" s="69"/>
-      <c r="I141" s="70"/>
+      <c r="D141" s="62"/>
+      <c r="E141" s="63"/>
+      <c r="F141" s="64"/>
+      <c r="G141" s="64"/>
+      <c r="H141" s="65"/>
+      <c r="I141" s="65"/>
       <c r="J141" s="21"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B142" s="37"/>
-      <c r="C142" s="18"/>
-      <c r="D142" s="40"/>
-      <c r="F142" s="19"/>
-      <c r="G142" s="19"/>
-      <c r="H142" s="20"/>
-      <c r="I142" s="20"/>
+      <c r="C142" s="61"/>
+      <c r="D142" s="66"/>
+      <c r="E142" s="67"/>
+      <c r="F142" s="66"/>
+      <c r="G142" s="68"/>
+      <c r="H142" s="69"/>
+      <c r="I142" s="70"/>
       <c r="J142" s="21"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -27358,13 +27443,23 @@
       <c r="I1656" s="20"/>
       <c r="J1656" s="21"/>
     </row>
+    <row r="1657" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1657" s="37"/>
+      <c r="C1657" s="18"/>
+      <c r="D1657" s="40"/>
+      <c r="F1657" s="19"/>
+      <c r="G1657" s="19"/>
+      <c r="H1657" s="20"/>
+      <c r="I1657" s="20"/>
+      <c r="J1657" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J132" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J133" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D141">
+  <conditionalFormatting sqref="D142">
     <cfRule type="duplicateValues" dxfId="312" priority="1"/>
     <cfRule type="duplicateValues" dxfId="311" priority="2"/>
     <cfRule type="duplicateValues" dxfId="310" priority="3"/>
@@ -27376,7 +27471,7 @@
     <cfRule type="duplicateValues" dxfId="304" priority="10"/>
     <cfRule type="duplicateValues" dxfId="303" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D141">
+  <conditionalFormatting sqref="D142">
     <cfRule type="duplicateValues" dxfId="302" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F579125-2CC7-4A94-8DBA-971F3A4ED182}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833400DA-08FA-4689-B870-E009EF02D520}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$133</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$569</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$569</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$134</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$570</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$570</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="233">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1186,6 +1186,9 @@
   </si>
   <si>
     <t>ВОСКРЕСЕНСКАЯ ВЯЛЕНАЯ в/к в/у срез 1/260</t>
+  </si>
+  <si>
+    <t>КРАКОВСКАЯ ГОСТ Останкино п/к н/о мгс</t>
   </si>
 </sst>
 </file>
@@ -5468,7 +5471,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1657"/>
+  <dimension ref="A1:BO1658"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -9390,7 +9393,7 @@
     </row>
     <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A74" s="109" t="str">
-        <f t="shared" ref="A74:A100" si="14">RIGHT(D74,4)</f>
+        <f t="shared" ref="A74:A101" si="14">RIGHT(D74,4)</f>
         <v>7564</v>
       </c>
       <c r="B74" s="53" t="s">
@@ -9440,7 +9443,7 @@
         <v>0.33</v>
       </c>
       <c r="G75" s="23">
-        <f t="shared" ref="G75:G87" si="15">E75*F75</f>
+        <f t="shared" ref="G75:G88" si="15">E75*F75</f>
         <v>0</v>
       </c>
       <c r="H75" s="14">
@@ -9730,47 +9733,41 @@
     <row r="85" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7236</v>
+        <v>7562</v>
       </c>
       <c r="B85" s="53" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D85" s="51">
-        <v>1001304507236</v>
+        <v>1001307587562</v>
       </c>
       <c r="E85" s="24"/>
-      <c r="F85" s="23">
-        <v>0.28000000000000003</v>
-      </c>
+      <c r="F85" s="23"/>
       <c r="G85" s="23">
-        <f t="shared" si="15"/>
+        <f>E85</f>
         <v>0</v>
       </c>
-      <c r="H85" s="14">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I85" s="14">
-        <v>45</v>
-      </c>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
       <c r="J85" s="29"/>
       <c r="L85" s="102"/>
     </row>
     <row r="86" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7489</v>
+        <v>7236</v>
       </c>
       <c r="B86" s="53" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="C86" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D86" s="51">
-        <v>1001307357489</v>
+        <v>1001304507236</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="23">
@@ -9780,175 +9777,119 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H86" s="14"/>
-      <c r="I86" s="14"/>
-      <c r="J86" s="105" t="s">
-        <v>205</v>
-      </c>
+      <c r="H86" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I86" s="14">
+        <v>45</v>
+      </c>
+      <c r="J86" s="29"/>
       <c r="L86" s="102"/>
     </row>
     <row r="87" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>6787</v>
-      </c>
-      <c r="B87" s="113" t="s">
-        <v>66</v>
+        <v>7489</v>
+      </c>
+      <c r="B87" s="53" t="s">
+        <v>217</v>
       </c>
       <c r="C87" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D87" s="51">
-        <v>1001300456787</v>
+        <v>1001307357489</v>
       </c>
       <c r="E87" s="24"/>
       <c r="F87" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G87" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H87" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I87" s="14">
-        <v>45</v>
-      </c>
-      <c r="J87" s="29"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="105" t="s">
+        <v>205</v>
+      </c>
       <c r="L87" s="102"/>
     </row>
     <row r="88" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7166</v>
+        <v>6787</v>
       </c>
       <c r="B88" s="113" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D88" s="51">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="23">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G88" s="23">
-        <f>E88</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H88" s="14">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I88" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J88" s="29"/>
       <c r="L88" s="102"/>
     </row>
-    <row r="89" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7169</v>
-      </c>
-      <c r="B89" s="53" t="s">
-        <v>71</v>
+        <v>7166</v>
+      </c>
+      <c r="B89" s="113" t="s">
+        <v>72</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D89" s="51">
-        <v>1001303987169</v>
+        <v>1001303987166</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="23">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G89" s="23">
-        <f>E89*F89</f>
+        <f>E89</f>
         <v>0</v>
       </c>
       <c r="H89" s="14">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I89" s="14">
         <v>50</v>
       </c>
       <c r="J89" s="29"/>
-      <c r="K89" s="27"/>
       <c r="L89" s="102"/>
-      <c r="M89" s="102"/>
-      <c r="N89" s="102"/>
-      <c r="O89" s="102"/>
-      <c r="P89" s="102"/>
-      <c r="Q89" s="102"/>
-      <c r="R89" s="102"/>
-      <c r="S89" s="102"/>
-      <c r="T89" s="102"/>
-      <c r="U89" s="102"/>
-      <c r="V89" s="102"/>
-      <c r="W89" s="102"/>
-      <c r="X89" s="102"/>
-      <c r="Y89" s="102"/>
-      <c r="Z89" s="102"/>
-      <c r="AA89" s="102"/>
-      <c r="AB89" s="102"/>
-      <c r="AC89" s="102"/>
-      <c r="AD89" s="102"/>
-      <c r="AE89" s="102"/>
-      <c r="AF89" s="102"/>
-      <c r="AG89" s="102"/>
-      <c r="AH89" s="102"/>
-      <c r="AI89" s="102"/>
-      <c r="AJ89" s="102"/>
-      <c r="AK89" s="102"/>
-      <c r="AL89" s="102"/>
-      <c r="AM89" s="102"/>
-      <c r="AN89" s="102"/>
-      <c r="AO89" s="102"/>
-      <c r="AP89" s="102"/>
-      <c r="AQ89" s="102"/>
-      <c r="AR89" s="102"/>
-      <c r="AS89" s="102"/>
-      <c r="AT89" s="102"/>
-      <c r="AU89" s="102"/>
-      <c r="AV89" s="102"/>
-      <c r="AW89" s="102"/>
-      <c r="AX89" s="102"/>
-      <c r="AY89" s="102"/>
-      <c r="AZ89" s="102"/>
-      <c r="BA89" s="102"/>
-      <c r="BB89" s="102"/>
-      <c r="BC89" s="102"/>
-      <c r="BD89" s="102"/>
-      <c r="BE89" s="102"/>
-      <c r="BF89" s="102"/>
-      <c r="BG89" s="102"/>
-      <c r="BH89" s="102"/>
-      <c r="BI89" s="102"/>
-      <c r="BJ89" s="102"/>
-      <c r="BK89" s="102"/>
-      <c r="BL89" s="102"/>
-      <c r="BM89" s="102"/>
-      <c r="BN89" s="102"/>
-      <c r="BO89" s="102"/>
     </row>
     <row r="90" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7156</v>
+        <v>7169</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>228</v>
+        <v>71</v>
       </c>
       <c r="C90" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D90" s="51">
-        <v>1001304237156</v>
+        <v>1001303987169</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
@@ -9958,9 +9899,13 @@
         <f>E90*F90</f>
         <v>0</v>
       </c>
-      <c r="H90" s="14"/>
-      <c r="I90" s="14"/>
-      <c r="J90" s="49"/>
+      <c r="H90" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="I90" s="14">
+        <v>50</v>
+      </c>
+      <c r="J90" s="29"/>
       <c r="K90" s="27"/>
       <c r="L90" s="102"/>
       <c r="M90" s="102"/>
@@ -10019,61 +9964,113 @@
       <c r="BN90" s="102"/>
       <c r="BO90" s="102"/>
     </row>
-    <row r="91" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>5544</v>
+        <v>7156</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D91" s="51">
-        <v>1001051875544</v>
+        <v>1001304237156</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G91" s="23">
-        <f>E91</f>
+        <f>E91*F91</f>
         <v>0</v>
       </c>
-      <c r="H91" s="14">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="I91" s="14">
-        <v>45</v>
-      </c>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
       <c r="J91" s="49"/>
+      <c r="K91" s="27"/>
       <c r="L91" s="102"/>
+      <c r="M91" s="102"/>
+      <c r="N91" s="102"/>
+      <c r="O91" s="102"/>
+      <c r="P91" s="102"/>
+      <c r="Q91" s="102"/>
+      <c r="R91" s="102"/>
+      <c r="S91" s="102"/>
+      <c r="T91" s="102"/>
+      <c r="U91" s="102"/>
+      <c r="V91" s="102"/>
+      <c r="W91" s="102"/>
+      <c r="X91" s="102"/>
+      <c r="Y91" s="102"/>
+      <c r="Z91" s="102"/>
+      <c r="AA91" s="102"/>
+      <c r="AB91" s="102"/>
+      <c r="AC91" s="102"/>
+      <c r="AD91" s="102"/>
+      <c r="AE91" s="102"/>
+      <c r="AF91" s="102"/>
+      <c r="AG91" s="102"/>
+      <c r="AH91" s="102"/>
+      <c r="AI91" s="102"/>
+      <c r="AJ91" s="102"/>
+      <c r="AK91" s="102"/>
+      <c r="AL91" s="102"/>
+      <c r="AM91" s="102"/>
+      <c r="AN91" s="102"/>
+      <c r="AO91" s="102"/>
+      <c r="AP91" s="102"/>
+      <c r="AQ91" s="102"/>
+      <c r="AR91" s="102"/>
+      <c r="AS91" s="102"/>
+      <c r="AT91" s="102"/>
+      <c r="AU91" s="102"/>
+      <c r="AV91" s="102"/>
+      <c r="AW91" s="102"/>
+      <c r="AX91" s="102"/>
+      <c r="AY91" s="102"/>
+      <c r="AZ91" s="102"/>
+      <c r="BA91" s="102"/>
+      <c r="BB91" s="102"/>
+      <c r="BC91" s="102"/>
+      <c r="BD91" s="102"/>
+      <c r="BE91" s="102"/>
+      <c r="BF91" s="102"/>
+      <c r="BG91" s="102"/>
+      <c r="BH91" s="102"/>
+      <c r="BI91" s="102"/>
+      <c r="BJ91" s="102"/>
+      <c r="BK91" s="102"/>
+      <c r="BL91" s="102"/>
+      <c r="BM91" s="102"/>
+      <c r="BN91" s="102"/>
+      <c r="BO91" s="102"/>
     </row>
     <row r="92" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>6697</v>
+        <v>5544</v>
       </c>
       <c r="B92" s="53" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D92" s="51">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" ref="G92:G100" si="16">E92*F92</f>
+        <f>E92</f>
         <v>0</v>
       </c>
       <c r="H92" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I92" s="14">
         <v>45</v>
@@ -10084,27 +10081,27 @@
     <row r="93" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7238</v>
+        <v>6697</v>
       </c>
       <c r="B93" s="53" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="C93" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D93" s="51">
-        <v>1001305197238</v>
+        <v>1001301876697</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G93" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G93:G101" si="16">E93*F93</f>
         <v>0</v>
       </c>
       <c r="H93" s="14">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I93" s="14">
         <v>45</v>
@@ -10115,16 +10112,16 @@
     <row r="94" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7516</v>
+        <v>7238</v>
       </c>
       <c r="B94" s="53" t="s">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="C94" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D94" s="51">
-        <v>1001307107516</v>
+        <v>1001305197238</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
@@ -10134,28 +10131,32 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H94" s="14"/>
-      <c r="I94" s="14"/>
+      <c r="H94" s="14">
+        <v>2.48</v>
+      </c>
+      <c r="I94" s="14">
+        <v>45</v>
+      </c>
       <c r="J94" s="49"/>
       <c r="L94" s="102"/>
     </row>
     <row r="95" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7513</v>
+        <v>7516</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C95" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D95" s="51">
-        <v>1001307077513</v>
+        <v>1001307107516</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="G95" s="23">
         <f t="shared" si="16"/>
@@ -10169,58 +10170,54 @@
     <row r="96" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7177</v>
+        <v>7513</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="C96" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D96" s="51">
-        <v>1001302347177</v>
+        <v>1001307077513</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="G96" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H96" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I96" s="14">
-        <v>50</v>
-      </c>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
       <c r="J96" s="49"/>
       <c r="L96" s="102"/>
     </row>
     <row r="97" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7332</v>
+        <v>7177</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D97" s="51">
-        <v>1001301777332</v>
+        <v>1001302347177</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G97" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I97" s="14">
         <v>50</v>
@@ -10231,16 +10228,16 @@
     <row r="98" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7333</v>
+        <v>7332</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
@@ -10262,49 +10259,47 @@
     <row r="99" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7608</v>
+        <v>7333</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>216</v>
+        <v>70</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="51">
-        <v>1001304197608</v>
+        <v>1001303987333</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G99" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I99" s="14">
-        <v>45</v>
-      </c>
-      <c r="J99" s="52" t="s">
-        <v>207</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J99" s="49"/>
       <c r="L99" s="102"/>
     </row>
-    <row r="100" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7610</v>
+        <v>7608</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="51">
-        <v>1001306717610</v>
+        <v>1001304197608</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
@@ -10321,84 +10316,86 @@
         <v>45</v>
       </c>
       <c r="J100" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="L100" s="102"/>
+    </row>
+    <row r="101" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="109" t="str">
+        <f t="shared" si="14"/>
+        <v>7610</v>
+      </c>
+      <c r="B101" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="C101" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E101" s="24"/>
+      <c r="F101" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G101" s="23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H101" s="14">
+        <v>1</v>
+      </c>
+      <c r="I101" s="14">
+        <v>45</v>
+      </c>
+      <c r="J101" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="L100" s="102"/>
-    </row>
-    <row r="101" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="47" t="s">
+      <c r="L101" s="102"/>
+    </row>
+    <row r="102" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B101" s="42" t="s">
+      <c r="B102" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C101" s="42"/>
-      <c r="D101" s="42"/>
-      <c r="E101" s="42"/>
-      <c r="F101" s="41"/>
-      <c r="G101" s="42"/>
-      <c r="H101" s="42"/>
-      <c r="I101" s="42"/>
-      <c r="J101" s="43"/>
-      <c r="L101" s="102"/>
-    </row>
-    <row r="102" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="109" t="str">
-        <f t="shared" ref="A102:A129" si="17">RIGHT(D102,4)</f>
+      <c r="C102" s="42"/>
+      <c r="D102" s="42"/>
+      <c r="E102" s="42"/>
+      <c r="F102" s="41"/>
+      <c r="G102" s="42"/>
+      <c r="H102" s="42"/>
+      <c r="I102" s="42"/>
+      <c r="J102" s="43"/>
+      <c r="L102" s="102"/>
+    </row>
+    <row r="103" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="109" t="str">
+        <f t="shared" ref="A103:A130" si="17">RIGHT(D103,4)</f>
         <v>3986</v>
       </c>
-      <c r="B102" s="53" t="s">
+      <c r="B103" s="53" t="s">
         <v>80</v>
-      </c>
-      <c r="C102" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D102" s="51">
-        <v>1001061973986</v>
-      </c>
-      <c r="E102" s="24"/>
-      <c r="F102" s="111">
-        <v>0.25</v>
-      </c>
-      <c r="G102" s="23">
-        <f t="shared" ref="G102:G107" si="18">E102*F102</f>
-        <v>0</v>
-      </c>
-      <c r="H102" s="114">
-        <v>2</v>
-      </c>
-      <c r="I102" s="115">
-        <v>120</v>
-      </c>
-      <c r="J102" s="29"/>
-      <c r="L102" s="102"/>
-    </row>
-    <row r="103" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="109" t="str">
-        <f t="shared" si="17"/>
-        <v>5931</v>
-      </c>
-      <c r="B103" s="53" t="s">
-        <v>78</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D103" s="51">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E103" s="24"/>
-      <c r="F103" s="23">
-        <v>0.22</v>
+      <c r="F103" s="111">
+        <v>0.25</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G103:G108" si="18">E103*F103</f>
         <v>0</v>
       </c>
-      <c r="H103" s="97">
-        <v>1.76</v>
-      </c>
-      <c r="I103" s="14">
+      <c r="H103" s="114">
+        <v>2</v>
+      </c>
+      <c r="I103" s="115">
         <v>120</v>
       </c>
       <c r="J103" s="29"/>
@@ -10407,27 +10404,27 @@
     <row r="104" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>5708</v>
+        <v>5931</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D104" s="51">
-        <v>1001063145708</v>
+        <v>1001060755931</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G104" s="23">
-        <f t="shared" ref="G104:G105" si="19">E104</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H104" s="14">
-        <v>4</v>
+      <c r="H104" s="97">
+        <v>1.76</v>
       </c>
       <c r="I104" s="14">
         <v>120</v>
@@ -10438,27 +10435,27 @@
     <row r="105" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>3287</v>
+        <v>5708</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C105" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D105" s="51">
-        <v>1001060763287</v>
+        <v>1001063145708</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G105" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G105:G106" si="19">E105</f>
         <v>0</v>
       </c>
       <c r="H105" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I105" s="14">
         <v>120</v>
@@ -10469,27 +10466,27 @@
     <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>4993</v>
+        <v>3287</v>
       </c>
       <c r="B106" s="53" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D106" s="51">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H106" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I106" s="14">
         <v>120</v>
@@ -10500,16 +10497,16 @@
     <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>5483</v>
+        <v>4993</v>
       </c>
       <c r="B107" s="53" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="C107" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D107" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="23">
@@ -10528,30 +10525,30 @@
       <c r="J107" s="29"/>
       <c r="L107" s="102"/>
     </row>
-    <row r="108" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>4117</v>
+        <v>5483</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D108" s="51">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" ref="G108:G109" si="20">E108</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H108" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I108" s="14">
         <v>120</v>
@@ -10559,117 +10556,61 @@
       <c r="J108" s="29"/>
       <c r="L108" s="102"/>
     </row>
-    <row r="109" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>0614</v>
+        <v>4117</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="C109" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D109" s="51">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G109:G110" si="20">E109</f>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
       </c>
       <c r="J109" s="29"/>
-      <c r="K109" s="27"/>
       <c r="L109" s="102"/>
-      <c r="M109" s="102"/>
-      <c r="N109" s="102"/>
-      <c r="O109" s="102"/>
-      <c r="P109" s="102"/>
-      <c r="Q109" s="102"/>
-      <c r="R109" s="102"/>
-      <c r="S109" s="102"/>
-      <c r="T109" s="102"/>
-      <c r="U109" s="102"/>
-      <c r="V109" s="102"/>
-      <c r="W109" s="102"/>
-      <c r="X109" s="102"/>
-      <c r="Y109" s="102"/>
-      <c r="Z109" s="102"/>
-      <c r="AA109" s="102"/>
-      <c r="AB109" s="102"/>
-      <c r="AC109" s="102"/>
-      <c r="AD109" s="102"/>
-      <c r="AE109" s="102"/>
-      <c r="AF109" s="102"/>
-      <c r="AG109" s="102"/>
-      <c r="AH109" s="102"/>
-      <c r="AI109" s="102"/>
-      <c r="AJ109" s="102"/>
-      <c r="AK109" s="102"/>
-      <c r="AL109" s="102"/>
-      <c r="AM109" s="102"/>
-      <c r="AN109" s="102"/>
-      <c r="AO109" s="102"/>
-      <c r="AP109" s="102"/>
-      <c r="AQ109" s="102"/>
-      <c r="AR109" s="102"/>
-      <c r="AS109" s="102"/>
-      <c r="AT109" s="102"/>
-      <c r="AU109" s="102"/>
-      <c r="AV109" s="102"/>
-      <c r="AW109" s="102"/>
-      <c r="AX109" s="102"/>
-      <c r="AY109" s="102"/>
-      <c r="AZ109" s="102"/>
-      <c r="BA109" s="102"/>
-      <c r="BB109" s="102"/>
-      <c r="BC109" s="102"/>
-      <c r="BD109" s="102"/>
-      <c r="BE109" s="102"/>
-      <c r="BF109" s="102"/>
-      <c r="BG109" s="102"/>
-      <c r="BH109" s="102"/>
-      <c r="BI109" s="102"/>
-      <c r="BJ109" s="102"/>
-      <c r="BK109" s="102"/>
-      <c r="BL109" s="102"/>
-      <c r="BM109" s="102"/>
-      <c r="BN109" s="102"/>
-      <c r="BO109" s="102"/>
     </row>
     <row r="110" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6967</v>
+        <v>0614</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="C110" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D110" s="51">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" ref="G110:G119" si="21">E110*F110</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -10736,23 +10677,23 @@
     <row r="111" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6937</v>
+        <v>6967</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="C111" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D111" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
         <v>0.25</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G111:G120" si="21">E111*F111</f>
         <v>0</v>
       </c>
       <c r="H111" s="14">
@@ -10823,27 +10764,27 @@
     <row r="112" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7143</v>
+        <v>6937</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C112" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D112" s="51">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G112" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H112" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -10910,16 +10851,16 @@
     <row r="113" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7147</v>
+        <v>7143</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D113" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
@@ -10994,33 +10935,33 @@
       <c r="BN113" s="102"/>
       <c r="BO113" s="102"/>
     </row>
-    <row r="114" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7456</v>
+        <v>7147</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D114" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G114" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I114" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J114" s="29"/>
       <c r="K114" s="27"/>
@@ -11084,27 +11025,27 @@
     <row r="115" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7364</v>
+        <v>7456</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G115" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I115" s="14">
         <v>90</v>
@@ -11168,19 +11109,19 @@
       <c r="BN115" s="102"/>
       <c r="BO115" s="102"/>
     </row>
-    <row r="116" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7383</v>
+        <v>7364</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D116" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
@@ -11197,174 +11138,174 @@
         <v>90</v>
       </c>
       <c r="J116" s="29"/>
-      <c r="L116"/>
-      <c r="M116"/>
-      <c r="N116"/>
-      <c r="O116"/>
-      <c r="P116"/>
-      <c r="Q116"/>
-      <c r="R116"/>
-      <c r="S116"/>
-      <c r="T116"/>
-      <c r="U116"/>
-      <c r="V116"/>
-      <c r="W116"/>
-      <c r="X116"/>
-      <c r="Y116"/>
-      <c r="Z116"/>
-      <c r="AA116"/>
-      <c r="AB116"/>
-      <c r="AC116"/>
-      <c r="AD116"/>
-      <c r="AE116"/>
-      <c r="AF116"/>
-      <c r="AG116"/>
-      <c r="AH116"/>
-      <c r="AI116"/>
-      <c r="AJ116"/>
-      <c r="AK116"/>
-      <c r="AL116"/>
-      <c r="AM116"/>
-      <c r="AN116"/>
-      <c r="AO116"/>
-      <c r="AP116"/>
-      <c r="AQ116"/>
-      <c r="AR116"/>
-      <c r="AS116"/>
-      <c r="AT116"/>
-      <c r="AU116"/>
-      <c r="AV116"/>
-      <c r="AW116"/>
-      <c r="AX116"/>
-      <c r="AY116"/>
-      <c r="AZ116"/>
-      <c r="BA116"/>
-      <c r="BB116"/>
-      <c r="BC116"/>
-      <c r="BD116"/>
-      <c r="BE116"/>
-      <c r="BF116"/>
-      <c r="BG116"/>
-      <c r="BH116"/>
-      <c r="BI116"/>
-      <c r="BJ116"/>
-      <c r="BK116"/>
-      <c r="BL116"/>
-      <c r="BM116"/>
-      <c r="BN116"/>
-      <c r="BO116"/>
-    </row>
-    <row r="117" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K116" s="27"/>
+      <c r="L116" s="102"/>
+      <c r="M116" s="102"/>
+      <c r="N116" s="102"/>
+      <c r="O116" s="102"/>
+      <c r="P116" s="102"/>
+      <c r="Q116" s="102"/>
+      <c r="R116" s="102"/>
+      <c r="S116" s="102"/>
+      <c r="T116" s="102"/>
+      <c r="U116" s="102"/>
+      <c r="V116" s="102"/>
+      <c r="W116" s="102"/>
+      <c r="X116" s="102"/>
+      <c r="Y116" s="102"/>
+      <c r="Z116" s="102"/>
+      <c r="AA116" s="102"/>
+      <c r="AB116" s="102"/>
+      <c r="AC116" s="102"/>
+      <c r="AD116" s="102"/>
+      <c r="AE116" s="102"/>
+      <c r="AF116" s="102"/>
+      <c r="AG116" s="102"/>
+      <c r="AH116" s="102"/>
+      <c r="AI116" s="102"/>
+      <c r="AJ116" s="102"/>
+      <c r="AK116" s="102"/>
+      <c r="AL116" s="102"/>
+      <c r="AM116" s="102"/>
+      <c r="AN116" s="102"/>
+      <c r="AO116" s="102"/>
+      <c r="AP116" s="102"/>
+      <c r="AQ116" s="102"/>
+      <c r="AR116" s="102"/>
+      <c r="AS116" s="102"/>
+      <c r="AT116" s="102"/>
+      <c r="AU116" s="102"/>
+      <c r="AV116" s="102"/>
+      <c r="AW116" s="102"/>
+      <c r="AX116" s="102"/>
+      <c r="AY116" s="102"/>
+      <c r="AZ116" s="102"/>
+      <c r="BA116" s="102"/>
+      <c r="BB116" s="102"/>
+      <c r="BC116" s="102"/>
+      <c r="BD116" s="102"/>
+      <c r="BE116" s="102"/>
+      <c r="BF116" s="102"/>
+      <c r="BG116" s="102"/>
+      <c r="BH116" s="102"/>
+      <c r="BI116" s="102"/>
+      <c r="BJ116" s="102"/>
+      <c r="BK116" s="102"/>
+      <c r="BL116" s="102"/>
+      <c r="BM116" s="102"/>
+      <c r="BN116" s="102"/>
+      <c r="BO116" s="102"/>
+    </row>
+    <row r="117" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7317</v>
+        <v>7383</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D117" s="51">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G117" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I117" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J117" s="29"/>
-      <c r="K117" s="27"/>
-      <c r="L117" s="102"/>
-      <c r="M117" s="102"/>
-      <c r="N117" s="102"/>
-      <c r="O117" s="102"/>
-      <c r="P117" s="102"/>
-      <c r="Q117" s="102"/>
-      <c r="R117" s="102"/>
-      <c r="S117" s="102"/>
-      <c r="T117" s="102"/>
-      <c r="U117" s="102"/>
-      <c r="V117" s="102"/>
-      <c r="W117" s="102"/>
-      <c r="X117" s="102"/>
-      <c r="Y117" s="102"/>
-      <c r="Z117" s="102"/>
-      <c r="AA117" s="102"/>
-      <c r="AB117" s="102"/>
-      <c r="AC117" s="102"/>
-      <c r="AD117" s="102"/>
-      <c r="AE117" s="102"/>
-      <c r="AF117" s="102"/>
-      <c r="AG117" s="102"/>
-      <c r="AH117" s="102"/>
-      <c r="AI117" s="102"/>
-      <c r="AJ117" s="102"/>
-      <c r="AK117" s="102"/>
-      <c r="AL117" s="102"/>
-      <c r="AM117" s="102"/>
-      <c r="AN117" s="102"/>
-      <c r="AO117" s="102"/>
-      <c r="AP117" s="102"/>
-      <c r="AQ117" s="102"/>
-      <c r="AR117" s="102"/>
-      <c r="AS117" s="102"/>
-      <c r="AT117" s="102"/>
-      <c r="AU117" s="102"/>
-      <c r="AV117" s="102"/>
-      <c r="AW117" s="102"/>
-      <c r="AX117" s="102"/>
-      <c r="AY117" s="102"/>
-      <c r="AZ117" s="102"/>
-      <c r="BA117" s="102"/>
-      <c r="BB117" s="102"/>
-      <c r="BC117" s="102"/>
-      <c r="BD117" s="102"/>
-      <c r="BE117" s="102"/>
-      <c r="BF117" s="102"/>
-      <c r="BG117" s="102"/>
-      <c r="BH117" s="102"/>
-      <c r="BI117" s="102"/>
-      <c r="BJ117" s="102"/>
-      <c r="BK117" s="102"/>
-      <c r="BL117" s="102"/>
-      <c r="BM117" s="102"/>
-      <c r="BN117" s="102"/>
-      <c r="BO117" s="102"/>
-    </row>
-    <row r="118" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L117"/>
+      <c r="M117"/>
+      <c r="N117"/>
+      <c r="O117"/>
+      <c r="P117"/>
+      <c r="Q117"/>
+      <c r="R117"/>
+      <c r="S117"/>
+      <c r="T117"/>
+      <c r="U117"/>
+      <c r="V117"/>
+      <c r="W117"/>
+      <c r="X117"/>
+      <c r="Y117"/>
+      <c r="Z117"/>
+      <c r="AA117"/>
+      <c r="AB117"/>
+      <c r="AC117"/>
+      <c r="AD117"/>
+      <c r="AE117"/>
+      <c r="AF117"/>
+      <c r="AG117"/>
+      <c r="AH117"/>
+      <c r="AI117"/>
+      <c r="AJ117"/>
+      <c r="AK117"/>
+      <c r="AL117"/>
+      <c r="AM117"/>
+      <c r="AN117"/>
+      <c r="AO117"/>
+      <c r="AP117"/>
+      <c r="AQ117"/>
+      <c r="AR117"/>
+      <c r="AS117"/>
+      <c r="AT117"/>
+      <c r="AU117"/>
+      <c r="AV117"/>
+      <c r="AW117"/>
+      <c r="AX117"/>
+      <c r="AY117"/>
+      <c r="AZ117"/>
+      <c r="BA117"/>
+      <c r="BB117"/>
+      <c r="BC117"/>
+      <c r="BD117"/>
+      <c r="BE117"/>
+      <c r="BF117"/>
+      <c r="BG117"/>
+      <c r="BH117"/>
+      <c r="BI117"/>
+      <c r="BJ117"/>
+      <c r="BK117"/>
+      <c r="BL117"/>
+      <c r="BM117"/>
+      <c r="BN117"/>
+      <c r="BO117"/>
+    </row>
+    <row r="118" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7318</v>
+        <v>7317</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D118" s="51">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G118" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I118" s="14">
         <v>120</v>
@@ -11431,27 +11372,27 @@
     <row r="119" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7316</v>
+        <v>7318</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="51">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G119" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I119" s="14">
         <v>120</v>
@@ -11518,30 +11459,30 @@
     <row r="120" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6832</v>
+        <v>7316</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D120" s="51">
-        <v>1001065616832</v>
+        <v>1001060727316</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" ref="G120:G121" si="22">E120</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I120" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J120" s="29"/>
       <c r="K120" s="27"/>
@@ -11605,23 +11546,23 @@
     <row r="121" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7299</v>
+        <v>6832</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D121" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
         <v>0.215</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G121:G122" si="22">E121</f>
         <v>0</v>
       </c>
       <c r="H121" s="14">
@@ -11689,178 +11630,234 @@
       <c r="BN121" s="102"/>
       <c r="BO121" s="102"/>
     </row>
-    <row r="122" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7386</v>
+        <v>7299</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D122" s="51">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" ref="G122:G129" si="23">E122*F122</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I122" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J122" s="29"/>
+      <c r="K122" s="27"/>
       <c r="L122" s="102"/>
+      <c r="M122" s="102"/>
+      <c r="N122" s="102"/>
+      <c r="O122" s="102"/>
+      <c r="P122" s="102"/>
+      <c r="Q122" s="102"/>
+      <c r="R122" s="102"/>
+      <c r="S122" s="102"/>
+      <c r="T122" s="102"/>
+      <c r="U122" s="102"/>
+      <c r="V122" s="102"/>
+      <c r="W122" s="102"/>
+      <c r="X122" s="102"/>
+      <c r="Y122" s="102"/>
+      <c r="Z122" s="102"/>
+      <c r="AA122" s="102"/>
+      <c r="AB122" s="102"/>
+      <c r="AC122" s="102"/>
+      <c r="AD122" s="102"/>
+      <c r="AE122" s="102"/>
+      <c r="AF122" s="102"/>
+      <c r="AG122" s="102"/>
+      <c r="AH122" s="102"/>
+      <c r="AI122" s="102"/>
+      <c r="AJ122" s="102"/>
+      <c r="AK122" s="102"/>
+      <c r="AL122" s="102"/>
+      <c r="AM122" s="102"/>
+      <c r="AN122" s="102"/>
+      <c r="AO122" s="102"/>
+      <c r="AP122" s="102"/>
+      <c r="AQ122" s="102"/>
+      <c r="AR122" s="102"/>
+      <c r="AS122" s="102"/>
+      <c r="AT122" s="102"/>
+      <c r="AU122" s="102"/>
+      <c r="AV122" s="102"/>
+      <c r="AW122" s="102"/>
+      <c r="AX122" s="102"/>
+      <c r="AY122" s="102"/>
+      <c r="AZ122" s="102"/>
+      <c r="BA122" s="102"/>
+      <c r="BB122" s="102"/>
+      <c r="BC122" s="102"/>
+      <c r="BD122" s="102"/>
+      <c r="BE122" s="102"/>
+      <c r="BF122" s="102"/>
+      <c r="BG122" s="102"/>
+      <c r="BH122" s="102"/>
+      <c r="BI122" s="102"/>
+      <c r="BJ122" s="102"/>
+      <c r="BK122" s="102"/>
+      <c r="BL122" s="102"/>
+      <c r="BM122" s="102"/>
+      <c r="BN122" s="102"/>
+      <c r="BO122" s="102"/>
     </row>
     <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7613</v>
+        <v>7386</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D123" s="51">
-        <v>1001061977613</v>
+        <v>1001067017386</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G123:G130" si="23">E123*F123</f>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I123" s="14">
-        <v>60</v>
-      </c>
-      <c r="J123" s="52" t="s">
-        <v>211</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J123" s="29"/>
       <c r="L123" s="102"/>
     </row>
     <row r="124" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7382</v>
+        <v>7613</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="51">
-        <v>1001203117382</v>
+        <v>1001061977613</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G124" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I124" s="14">
         <v>60</v>
       </c>
-      <c r="J124" s="29"/>
+      <c r="J124" s="52" t="s">
+        <v>211</v>
+      </c>
       <c r="L124" s="102"/>
     </row>
     <row r="125" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7616</v>
+        <v>7382</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D125" s="51">
-        <v>1001062507616</v>
+        <v>1001203117382</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G125" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I125" s="14">
         <v>60</v>
       </c>
-      <c r="J125" s="52" t="s">
-        <v>212</v>
-      </c>
+      <c r="J125" s="29"/>
       <c r="L125" s="102"/>
     </row>
     <row r="126" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6221</v>
+        <v>7616</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>87</v>
+        <v>215</v>
       </c>
       <c r="C126" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D126" s="51">
-        <v>1001205376221</v>
+        <v>1001062507616</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G126" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I126" s="14">
         <v>60</v>
       </c>
-      <c r="J126" s="29"/>
+      <c r="J126" s="52" t="s">
+        <v>212</v>
+      </c>
       <c r="L126" s="102"/>
     </row>
     <row r="127" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D127" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
@@ -11882,27 +11879,27 @@
     <row r="128" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>5679</v>
+        <v>6222</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D128" s="51">
-        <v>1001190765679</v>
+        <v>1001205386222</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G128" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I128" s="14">
         <v>60</v>
@@ -11910,114 +11907,114 @@
       <c r="J128" s="29"/>
       <c r="L128" s="102"/>
     </row>
-    <row r="129" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7626</v>
+        <v>5679</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D129" s="51">
-        <v>1001066607626</v>
+        <v>1001190765679</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G129" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H129" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I129" s="14">
         <v>60</v>
       </c>
-      <c r="J129" s="52" t="s">
+      <c r="J129" s="29"/>
+      <c r="L129" s="102"/>
+    </row>
+    <row r="130" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="109" t="str">
+        <f t="shared" si="17"/>
+        <v>7626</v>
+      </c>
+      <c r="B130" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="C130" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" s="51">
+        <v>1001066607626</v>
+      </c>
+      <c r="E130" s="24"/>
+      <c r="F130" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G130" s="23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="H130" s="14">
+        <v>1</v>
+      </c>
+      <c r="I130" s="14">
+        <v>60</v>
+      </c>
+      <c r="J130" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="L129" s="102"/>
-    </row>
-    <row r="130" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="47" t="s">
+      <c r="L130" s="102"/>
+    </row>
+    <row r="131" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B130" s="42" t="s">
+      <c r="B131" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C130" s="42"/>
-      <c r="D130" s="42"/>
-      <c r="E130" s="42"/>
-      <c r="F130" s="41"/>
-      <c r="G130" s="42"/>
-      <c r="H130" s="42"/>
-      <c r="I130" s="42"/>
-      <c r="J130" s="43"/>
-      <c r="L130" s="102"/>
-    </row>
-    <row r="131" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="109" t="str">
-        <f t="shared" ref="A131:A145" si="24">RIGHT(D131,4)</f>
+      <c r="C131" s="42"/>
+      <c r="D131" s="42"/>
+      <c r="E131" s="42"/>
+      <c r="F131" s="41"/>
+      <c r="G131" s="42"/>
+      <c r="H131" s="42"/>
+      <c r="I131" s="42"/>
+      <c r="J131" s="43"/>
+      <c r="L131" s="102"/>
+    </row>
+    <row r="132" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="109" t="str">
+        <f t="shared" ref="A132:A146" si="24">RIGHT(D132,4)</f>
         <v>4584</v>
       </c>
-      <c r="B131" s="98" t="s">
+      <c r="B132" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="C131" s="50" t="s">
+      <c r="C132" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D131" s="116">
+      <c r="D132" s="116">
         <v>1001092674584</v>
       </c>
-      <c r="E131" s="24"/>
-      <c r="F131" s="23">
+      <c r="E132" s="24"/>
+      <c r="F132" s="23">
         <v>2.5</v>
       </c>
-      <c r="G131" s="23">
-        <f>E131</f>
+      <c r="G132" s="23">
+        <f>E132</f>
         <v>0</v>
       </c>
-      <c r="H131" s="14">
+      <c r="H132" s="14">
         <v>7.5</v>
       </c>
-      <c r="I131" s="14">
+      <c r="I132" s="14">
         <v>60</v>
-      </c>
-      <c r="J131" s="29"/>
-      <c r="L131" s="102"/>
-    </row>
-    <row r="132" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="109" t="str">
-        <f t="shared" si="24"/>
-        <v>6495</v>
-      </c>
-      <c r="B132" s="98" t="s">
-        <v>97</v>
-      </c>
-      <c r="C132" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D132" s="51">
-        <v>1001092436495</v>
-      </c>
-      <c r="E132" s="24"/>
-      <c r="F132" s="111">
-        <v>0.3</v>
-      </c>
-      <c r="G132" s="23">
-        <f>E132*F132</f>
-        <v>0</v>
-      </c>
-      <c r="H132" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I132" s="29">
-        <v>45</v>
       </c>
       <c r="J132" s="29"/>
       <c r="L132" s="102"/>
@@ -12025,87 +12022,88 @@
     <row r="133" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6470</v>
-      </c>
-      <c r="B133" s="117" t="s">
-        <v>126</v>
+        <v>6495</v>
+      </c>
+      <c r="B133" s="98" t="s">
+        <v>97</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D133" s="51">
-        <v>1001092436470</v>
+        <v>1001092436495</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="111">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" ref="G133:G134" si="25">E133</f>
+        <f>E133*F133</f>
         <v>0</v>
       </c>
       <c r="H133" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I133" s="29">
         <v>45</v>
       </c>
       <c r="J133" s="29"/>
-    </row>
-    <row r="134" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L133" s="102"/>
+    </row>
+    <row r="134" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>5452</v>
+        <v>6470</v>
       </c>
       <c r="B134" s="117" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D134" s="51">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="111">
+        <v>1.2</v>
+      </c>
+      <c r="G134" s="23">
+        <f t="shared" ref="G134:G135" si="25">E134</f>
+        <v>0</v>
+      </c>
+      <c r="H134" s="29">
+        <v>4.8</v>
+      </c>
+      <c r="I134" s="29">
+        <v>45</v>
+      </c>
+      <c r="J134" s="29"/>
+    </row>
+    <row r="135" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="109" t="str">
+        <f t="shared" si="24"/>
+        <v>5452</v>
+      </c>
+      <c r="B135" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="C135" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D135" s="51">
+        <v>1001092485452</v>
+      </c>
+      <c r="E135" s="24"/>
+      <c r="F135" s="111">
         <v>1.35</v>
       </c>
-      <c r="G134" s="23">
+      <c r="G135" s="23">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H134" s="29">
+      <c r="H135" s="29">
         <v>4.05</v>
-      </c>
-      <c r="I134" s="29">
-        <v>60</v>
-      </c>
-      <c r="J134" s="29"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" s="109" t="str">
-        <f t="shared" si="24"/>
-        <v>3215</v>
-      </c>
-      <c r="B135" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="C135" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D135" s="51">
-        <v>1001094053215</v>
-      </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="111">
-        <v>0.4</v>
-      </c>
-      <c r="G135" s="23">
-        <f>E135*F135</f>
-        <v>0</v>
-      </c>
-      <c r="H135" s="29">
-        <v>3.2</v>
       </c>
       <c r="I135" s="29">
         <v>60</v>
@@ -12115,27 +12113,27 @@
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6866</v>
+        <v>3215</v>
       </c>
       <c r="B136" s="117" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D136" s="51">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="111">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G136" s="23">
-        <f>E136</f>
+        <f>E136*F136</f>
         <v>0</v>
       </c>
       <c r="H136" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I136" s="29">
         <v>60</v>
@@ -12145,27 +12143,27 @@
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>5495</v>
-      </c>
-      <c r="B137" s="53" t="s">
-        <v>96</v>
+        <v>6866</v>
+      </c>
+      <c r="B137" s="117" t="s">
+        <v>93</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D137" s="110">
-        <v>1001093345495</v>
+        <v>23</v>
+      </c>
+      <c r="D137" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="111">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G137" s="23">
-        <f t="shared" ref="G137:G140" si="26">E137*F137</f>
+        <f>E137</f>
         <v>0</v>
       </c>
       <c r="H137" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I137" s="29">
         <v>60</v>
@@ -12175,46 +12173,46 @@
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>7377</v>
+        <v>5495</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="110">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="111">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G138" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G138:G141" si="26">E138*F138</f>
         <v>0</v>
       </c>
       <c r="H138" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I138" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J138" s="29"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6411</v>
+        <v>7377</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>224</v>
+        <v>127</v>
       </c>
       <c r="C139" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D139" s="110">
-        <v>1001093316411</v>
+        <v>1001095027377</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="111">
@@ -12224,167 +12222,165 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H139" s="29"/>
-      <c r="I139" s="29"/>
+      <c r="H139" s="29">
+        <v>1.8</v>
+      </c>
+      <c r="I139" s="29">
+        <v>45</v>
+      </c>
       <c r="J139" s="29"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6925</v>
+        <v>6411</v>
       </c>
       <c r="B140" s="53" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="C140" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D140" s="110">
-        <v>1001095226925</v>
+        <v>1001093316411</v>
       </c>
       <c r="E140" s="24"/>
       <c r="F140" s="111">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G140" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H140" s="29">
-        <v>4.8</v>
-      </c>
-      <c r="I140" s="29">
-        <v>45</v>
-      </c>
+      <c r="H140" s="29"/>
+      <c r="I140" s="29"/>
       <c r="J140" s="29"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6025</v>
+        <v>6925</v>
       </c>
       <c r="B141" s="53" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D141" s="110">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="111">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G141" s="23">
-        <f>E141</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H141" s="29">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I141" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J141" s="29"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6929</v>
+        <v>6025</v>
       </c>
       <c r="B142" s="53" t="s">
-        <v>229</v>
+        <v>128</v>
       </c>
       <c r="C142" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D142" s="110">
-        <v>1001085476929</v>
+        <v>1001094966025</v>
       </c>
       <c r="E142" s="24"/>
-      <c r="F142" s="111"/>
+      <c r="F142" s="111">
+        <v>3</v>
+      </c>
       <c r="G142" s="23">
         <f>E142</f>
         <v>0</v>
       </c>
-      <c r="H142" s="29"/>
-      <c r="I142" s="29"/>
+      <c r="H142" s="29">
+        <v>6</v>
+      </c>
+      <c r="I142" s="29">
+        <v>60</v>
+      </c>
       <c r="J142" s="29"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>7485</v>
+        <v>6929</v>
       </c>
       <c r="B143" s="53" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D143" s="110">
-        <v>1001107397485</v>
+        <v>1001085476929</v>
       </c>
       <c r="E143" s="24"/>
-      <c r="F143" s="111">
-        <v>0.15</v>
-      </c>
+      <c r="F143" s="111"/>
       <c r="G143" s="23">
-        <f>F143*E143</f>
+        <f>E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="29"/>
       <c r="I143" s="29"/>
-      <c r="J143" s="105" t="s">
-        <v>205</v>
-      </c>
+      <c r="J143" s="29"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>7647</v>
+        <v>7485</v>
       </c>
       <c r="B144" s="53" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C144" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D144" s="110">
-        <v>1001097747647</v>
+        <v>1001107397485</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="111">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G144" s="23">
-        <f>E144*F144</f>
+        <f>F144*E144</f>
         <v>0</v>
       </c>
-      <c r="H144" s="29">
-        <v>1</v>
-      </c>
-      <c r="I144" s="29">
-        <v>30</v>
-      </c>
+      <c r="H144" s="29"/>
+      <c r="I144" s="29"/>
       <c r="J144" s="105" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>7651</v>
+        <v>7647</v>
       </c>
       <c r="B145" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C145" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D145" s="110">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="111">
@@ -12404,72 +12400,74 @@
         <v>205</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="47" t="s">
+    <row r="146" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="109" t="str">
+        <f t="shared" si="24"/>
+        <v>7651</v>
+      </c>
+      <c r="B146" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C146" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="110">
+        <v>1001097767651</v>
+      </c>
+      <c r="E146" s="24"/>
+      <c r="F146" s="111">
+        <v>0.1</v>
+      </c>
+      <c r="G146" s="23">
+        <f>E146*F146</f>
+        <v>0</v>
+      </c>
+      <c r="H146" s="29">
+        <v>1</v>
+      </c>
+      <c r="I146" s="29">
+        <v>30</v>
+      </c>
+      <c r="J146" s="105" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B146" s="42" t="s">
+      <c r="B147" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C146" s="42"/>
-      <c r="D146" s="42"/>
-      <c r="E146" s="42"/>
-      <c r="F146" s="41"/>
-      <c r="G146" s="42"/>
-      <c r="H146" s="42"/>
-      <c r="I146" s="42"/>
-      <c r="J146" s="43"/>
-    </row>
-    <row r="147" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="109" t="str">
-        <f t="shared" ref="A147:A158" si="27">RIGHT(D147,4)</f>
+      <c r="C147" s="42"/>
+      <c r="D147" s="42"/>
+      <c r="E147" s="42"/>
+      <c r="F147" s="41"/>
+      <c r="G147" s="42"/>
+      <c r="H147" s="42"/>
+      <c r="I147" s="42"/>
+      <c r="J147" s="43"/>
+    </row>
+    <row r="148" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="109" t="str">
+        <f t="shared" ref="A148:A159" si="27">RIGHT(D148,4)</f>
         <v>7090</v>
       </c>
-      <c r="B147" s="35" t="s">
+      <c r="B148" s="35" t="s">
         <v>102</v>
-      </c>
-      <c r="C147" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D147" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E147" s="24"/>
-      <c r="F147" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G147" s="23">
-        <f t="shared" ref="G147:G148" si="28">E147*F147</f>
-        <v>0</v>
-      </c>
-      <c r="H147" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I147" s="14">
-        <v>50</v>
-      </c>
-      <c r="J147" s="29"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="109" t="str">
-        <f t="shared" si="27"/>
-        <v>7187</v>
-      </c>
-      <c r="B148" s="35" t="s">
-        <v>103</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D148" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="23">
         <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G148:G149" si="28">E148*F148</f>
         <v>0</v>
       </c>
       <c r="H148" s="14">
@@ -12483,119 +12481,119 @@
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6008</v>
+        <v>7187</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D149" s="51">
-        <v>1001084856008</v>
+        <v>1001085637187</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="23">
         <v>0.3</v>
       </c>
       <c r="G149" s="23">
-        <f>E149</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H149" s="14">
         <v>1.8</v>
       </c>
       <c r="I149" s="14">
-        <v>40</v>
-      </c>
-      <c r="J149" s="105" t="s">
-        <v>205</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J149" s="29"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6620</v>
+        <v>6008</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="C150" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D150" s="51">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G150" s="23">
         <f>E150</f>
         <v>0</v>
       </c>
       <c r="H150" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I150" s="14">
-        <v>30</v>
-      </c>
-      <c r="J150" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J150" s="105" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>7103</v>
+        <v>6620</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D151" s="51">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G151" s="23">
-        <f t="shared" ref="G151:G158" si="29">E151*F151</f>
+        <f>E151</f>
         <v>0</v>
       </c>
       <c r="H151" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I151" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J151" s="29"/>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>7092</v>
+        <v>7103</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C152" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D152" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G152" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G152:G159" si="29">E152*F152</f>
         <v>0</v>
       </c>
       <c r="H152" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I152" s="14">
         <v>50</v>
@@ -12605,57 +12603,57 @@
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6228</v>
+        <v>7092</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D153" s="51">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G153" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H153" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I153" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J153" s="29"/>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6448</v>
+        <v>6228</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C154" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D154" s="51">
-        <v>1001234146448</v>
+        <v>1001225416228</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G154" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I154" s="14">
         <v>45</v>
@@ -12665,27 +12663,27 @@
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6208</v>
+        <v>6448</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D155" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E155" s="24"/>
       <c r="F155" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G155" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H155" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I155" s="14">
         <v>45</v>
@@ -12695,126 +12693,146 @@
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6754</v>
+        <v>6208</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D156" s="51">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G156" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H156" s="14">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I156" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J156" s="29"/>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6279</v>
+        <v>6754</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D157" s="51">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G157" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I157" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J157" s="29"/>
     </row>
-    <row r="158" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>7612</v>
+        <v>6279</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001453907612</v>
+        <v>1001220286279</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G158" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I158" s="14">
+        <v>45</v>
+      </c>
+      <c r="J158" s="29"/>
+    </row>
+    <row r="159" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="109" t="str">
+        <f t="shared" si="27"/>
+        <v>7612</v>
+      </c>
+      <c r="B159" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C159" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E159" s="24"/>
+      <c r="F159" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G159" s="23">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H159" s="14">
         <v>1</v>
       </c>
-      <c r="I158" s="14">
+      <c r="I159" s="14">
         <v>60</v>
       </c>
-      <c r="J158" s="52" t="s">
+      <c r="J159" s="52" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="48"/>
-      <c r="B159" s="45" t="s">
+    <row r="160" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="48"/>
+      <c r="B160" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C159" s="16"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="17">
-        <f>SUM(E10:E158)</f>
+      <c r="C160" s="16"/>
+      <c r="D160" s="36"/>
+      <c r="E160" s="17">
+        <f>SUM(E10:E159)</f>
         <v>0</v>
       </c>
-      <c r="F159" s="17"/>
-      <c r="G159" s="17">
-        <f>SUM(G11:G158)</f>
+      <c r="F160" s="17"/>
+      <c r="G160" s="17">
+        <f>SUM(G11:G159)</f>
         <v>0</v>
       </c>
-      <c r="H159" s="17"/>
-      <c r="I159" s="17"/>
-      <c r="J159" s="17"/>
-    </row>
-    <row r="160" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="37"/>
-      <c r="C160" s="18"/>
-      <c r="D160" s="40"/>
-      <c r="F160" s="19"/>
-      <c r="G160" s="19"/>
-      <c r="H160" s="20"/>
-      <c r="I160" s="20"/>
-      <c r="J160" s="21"/>
-    </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H160" s="17"/>
+      <c r="I160" s="17"/>
+      <c r="J160" s="17"/>
+    </row>
+    <row r="161" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B161" s="37"/>
       <c r="C161" s="18"/>
       <c r="D161" s="40"/>
@@ -27784,8 +27802,18 @@
       <c r="I1657" s="20"/>
       <c r="J1657" s="21"/>
     </row>
+    <row r="1658" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1658" s="37"/>
+      <c r="C1658" s="18"/>
+      <c r="D1658" s="40"/>
+      <c r="F1658" s="19"/>
+      <c r="G1658" s="19"/>
+      <c r="H1658" s="20"/>
+      <c r="I1658" s="20"/>
+      <c r="J1658" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J133" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J134" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833400DA-08FA-4689-B870-E009EF02D520}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FA6265-56F5-451C-A10F-7B282D1E9BCC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="236">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1189,6 +1189,15 @@
   </si>
   <si>
     <t>КРАКОВСКАЯ ГОСТ Останкино п/к н/о мгс</t>
+  </si>
+  <si>
+    <t>КРАКОВСКАЯ ГОСТ п/к н/о мгс 0.3кг</t>
+  </si>
+  <si>
+    <t>КОНСЕРВЫ МЯС.ГОВЯДИНА ТУШ. В/С 338г_ЧЗ</t>
+  </si>
+  <si>
+    <t>КОНСЕРВЫ МЯС.СВИНИНА ТУШ. В/С 325г_ЧЗ</t>
   </si>
 </sst>
 </file>
@@ -9393,7 +9402,7 @@
     </row>
     <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A74" s="109" t="str">
-        <f t="shared" ref="A74:A101" si="14">RIGHT(D74,4)</f>
+        <f t="shared" ref="A74:A102" si="14">RIGHT(D74,4)</f>
         <v>7564</v>
       </c>
       <c r="B74" s="53" t="s">
@@ -10097,7 +10106,7 @@
         <v>0.35</v>
       </c>
       <c r="G93" s="23">
-        <f t="shared" ref="G93:G101" si="16">E93*F93</f>
+        <f t="shared" ref="G93:G102" si="16">E93*F93</f>
         <v>0</v>
       </c>
       <c r="H93" s="14">
@@ -10170,20 +10179,20 @@
     <row r="96" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7513</v>
+        <v>7710</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C96" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D96" s="51">
-        <v>1001307077513</v>
+        <v>1001307587710</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="G96" s="23">
         <f t="shared" si="16"/>
@@ -10197,58 +10206,54 @@
     <row r="97" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7177</v>
+        <v>7513</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D97" s="51">
-        <v>1001302347177</v>
+        <v>1001307077513</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="G97" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H97" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I97" s="14">
-        <v>50</v>
-      </c>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
       <c r="J97" s="49"/>
       <c r="L97" s="102"/>
     </row>
     <row r="98" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7332</v>
+        <v>7177</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="51">
-        <v>1001301777332</v>
+        <v>1001302347177</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G98" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I98" s="14">
         <v>50</v>
@@ -10259,16 +10264,16 @@
     <row r="99" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7333</v>
+        <v>7332</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
@@ -10290,49 +10295,47 @@
     <row r="100" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7608</v>
+        <v>7333</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>216</v>
+        <v>70</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="51">
-        <v>1001304197608</v>
+        <v>1001303987333</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G100" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I100" s="14">
-        <v>45</v>
-      </c>
-      <c r="J100" s="52" t="s">
-        <v>207</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J100" s="49"/>
       <c r="L100" s="102"/>
     </row>
-    <row r="101" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="109" t="str">
         <f t="shared" si="14"/>
-        <v>7610</v>
+        <v>7608</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D101" s="51">
-        <v>1001306717610</v>
+        <v>1001304197608</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
@@ -10349,84 +10352,86 @@
         <v>45</v>
       </c>
       <c r="J101" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="L101" s="102"/>
+    </row>
+    <row r="102" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="109" t="str">
+        <f t="shared" si="14"/>
+        <v>7610</v>
+      </c>
+      <c r="B102" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="C102" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E102" s="24"/>
+      <c r="F102" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G102" s="23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H102" s="14">
+        <v>1</v>
+      </c>
+      <c r="I102" s="14">
+        <v>45</v>
+      </c>
+      <c r="J102" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="L101" s="102"/>
-    </row>
-    <row r="102" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="47" t="s">
+      <c r="L102" s="102"/>
+    </row>
+    <row r="103" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B102" s="42" t="s">
+      <c r="B103" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C102" s="42"/>
-      <c r="D102" s="42"/>
-      <c r="E102" s="42"/>
-      <c r="F102" s="41"/>
-      <c r="G102" s="42"/>
-      <c r="H102" s="42"/>
-      <c r="I102" s="42"/>
-      <c r="J102" s="43"/>
-      <c r="L102" s="102"/>
-    </row>
-    <row r="103" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="109" t="str">
-        <f t="shared" ref="A103:A130" si="17">RIGHT(D103,4)</f>
+      <c r="C103" s="42"/>
+      <c r="D103" s="42"/>
+      <c r="E103" s="42"/>
+      <c r="F103" s="41"/>
+      <c r="G103" s="42"/>
+      <c r="H103" s="42"/>
+      <c r="I103" s="42"/>
+      <c r="J103" s="43"/>
+      <c r="L103" s="102"/>
+    </row>
+    <row r="104" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="109" t="str">
+        <f t="shared" ref="A104:A131" si="17">RIGHT(D104,4)</f>
         <v>3986</v>
       </c>
-      <c r="B103" s="53" t="s">
+      <c r="B104" s="53" t="s">
         <v>80</v>
-      </c>
-      <c r="C103" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D103" s="51">
-        <v>1001061973986</v>
-      </c>
-      <c r="E103" s="24"/>
-      <c r="F103" s="111">
-        <v>0.25</v>
-      </c>
-      <c r="G103" s="23">
-        <f t="shared" ref="G103:G108" si="18">E103*F103</f>
-        <v>0</v>
-      </c>
-      <c r="H103" s="114">
-        <v>2</v>
-      </c>
-      <c r="I103" s="115">
-        <v>120</v>
-      </c>
-      <c r="J103" s="29"/>
-      <c r="L103" s="102"/>
-    </row>
-    <row r="104" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="109" t="str">
-        <f t="shared" si="17"/>
-        <v>5931</v>
-      </c>
-      <c r="B104" s="53" t="s">
-        <v>78</v>
       </c>
       <c r="C104" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="51">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E104" s="24"/>
-      <c r="F104" s="23">
-        <v>0.22</v>
+      <c r="F104" s="111">
+        <v>0.25</v>
       </c>
       <c r="G104" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G104:G109" si="18">E104*F104</f>
         <v>0</v>
       </c>
-      <c r="H104" s="97">
-        <v>1.76</v>
-      </c>
-      <c r="I104" s="14">
+      <c r="H104" s="114">
+        <v>2</v>
+      </c>
+      <c r="I104" s="115">
         <v>120</v>
       </c>
       <c r="J104" s="29"/>
@@ -10435,27 +10440,27 @@
     <row r="105" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>5708</v>
+        <v>5931</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D105" s="51">
-        <v>1001063145708</v>
+        <v>1001060755931</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G105" s="23">
-        <f t="shared" ref="G105:G106" si="19">E105</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H105" s="14">
-        <v>4</v>
+      <c r="H105" s="97">
+        <v>1.76</v>
       </c>
       <c r="I105" s="14">
         <v>120</v>
@@ -10466,27 +10471,27 @@
     <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>3287</v>
+        <v>5708</v>
       </c>
       <c r="B106" s="53" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C106" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D106" s="51">
-        <v>1001060763287</v>
+        <v>1001063145708</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G106:G107" si="19">E106</f>
         <v>0</v>
       </c>
       <c r="H106" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I106" s="14">
         <v>120</v>
@@ -10497,27 +10502,27 @@
     <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>4993</v>
+        <v>3287</v>
       </c>
       <c r="B107" s="53" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D107" s="51">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H107" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I107" s="14">
         <v>120</v>
@@ -10528,16 +10533,16 @@
     <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>5483</v>
+        <v>4993</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="C108" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D108" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
@@ -10559,27 +10564,27 @@
     <row r="109" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>4117</v>
+        <v>5483</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C109" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D109" s="51">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" ref="G109:G110" si="20">E109</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -10590,27 +10595,27 @@
     <row r="110" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>0614</v>
+        <v>4117</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="C110" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D110" s="51">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G110:G111" si="20">E110</f>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -10677,27 +10682,27 @@
     <row r="111" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6967</v>
+        <v>0614</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="C111" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D111" s="51">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" ref="G111:G120" si="21">E111*F111</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I111" s="14">
         <v>120</v>
@@ -10764,23 +10769,23 @@
     <row r="112" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6937</v>
+        <v>6967</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="C112" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D112" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
         <v>0.25</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G112:G121" si="21">E112*F112</f>
         <v>0</v>
       </c>
       <c r="H112" s="14">
@@ -10851,27 +10856,27 @@
     <row r="113" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7143</v>
+        <v>6937</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D113" s="51">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G113" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -10938,16 +10943,16 @@
     <row r="114" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7147</v>
+        <v>7143</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D114" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
@@ -11025,30 +11030,30 @@
     <row r="115" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7456</v>
+        <v>7147</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G115" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I115" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J115" s="29"/>
       <c r="K115" s="27"/>
@@ -11112,27 +11117,27 @@
     <row r="116" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7364</v>
+        <v>7456</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D116" s="51">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G116" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I116" s="14">
         <v>90</v>
@@ -11199,16 +11204,16 @@
     <row r="117" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7383</v>
+        <v>7364</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D117" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
@@ -11285,30 +11290,30 @@
     <row r="118" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7317</v>
+        <v>7383</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D118" s="51">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G118" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I118" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J118" s="29"/>
       <c r="K118" s="27"/>
@@ -11372,27 +11377,27 @@
     <row r="119" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7318</v>
+        <v>7317</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="51">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G119" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I119" s="14">
         <v>120</v>
@@ -11459,27 +11464,27 @@
     <row r="120" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7316</v>
+        <v>7318</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="51">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G120" s="23">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I120" s="14">
         <v>120</v>
@@ -11546,30 +11551,30 @@
     <row r="121" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6832</v>
+        <v>7316</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D121" s="51">
-        <v>1001065616832</v>
+        <v>1001060727316</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" ref="G121:G122" si="22">E121</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I121" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J121" s="29"/>
       <c r="K121" s="27"/>
@@ -11633,23 +11638,23 @@
     <row r="122" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7299</v>
+        <v>6832</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D122" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
         <v>0.215</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G122:G123" si="22">E122</f>
         <v>0</v>
       </c>
       <c r="H122" s="14">
@@ -11720,30 +11725,30 @@
     <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7386</v>
+        <v>7299</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D123" s="51">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" ref="G123:G130" si="23">E123*F123</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I123" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J123" s="29"/>
       <c r="L123" s="102"/>
@@ -11751,144 +11756,144 @@
     <row r="124" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7613</v>
+        <v>7386</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="51">
-        <v>1001061977613</v>
+        <v>1001067017386</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G124:G131" si="23">E124*F124</f>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I124" s="14">
-        <v>60</v>
-      </c>
-      <c r="J124" s="52" t="s">
-        <v>211</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J124" s="29"/>
       <c r="L124" s="102"/>
     </row>
     <row r="125" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7382</v>
+        <v>7613</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D125" s="51">
-        <v>1001203117382</v>
+        <v>1001061977613</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G125" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I125" s="14">
         <v>60</v>
       </c>
-      <c r="J125" s="29"/>
+      <c r="J125" s="52" t="s">
+        <v>211</v>
+      </c>
       <c r="L125" s="102"/>
     </row>
     <row r="126" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7616</v>
+        <v>7382</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="C126" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D126" s="51">
-        <v>1001062507616</v>
+        <v>1001203117382</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G126" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I126" s="14">
         <v>60</v>
       </c>
-      <c r="J126" s="52" t="s">
-        <v>212</v>
-      </c>
+      <c r="J126" s="29"/>
       <c r="L126" s="102"/>
     </row>
     <row r="127" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6221</v>
+        <v>7616</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>87</v>
+        <v>215</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D127" s="51">
-        <v>1001205376221</v>
+        <v>1001062507616</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G127" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I127" s="14">
         <v>60</v>
       </c>
-      <c r="J127" s="29"/>
+      <c r="J127" s="52" t="s">
+        <v>212</v>
+      </c>
       <c r="L127" s="102"/>
     </row>
     <row r="128" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D128" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
@@ -11910,27 +11915,27 @@
     <row r="129" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>5679</v>
+        <v>6222</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D129" s="51">
-        <v>1001190765679</v>
+        <v>1001205386222</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G129" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H129" s="14">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I129" s="14">
         <v>60</v>
@@ -11938,114 +11943,114 @@
       <c r="J129" s="29"/>
       <c r="L129" s="102"/>
     </row>
-    <row r="130" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="109" t="str">
         <f t="shared" si="17"/>
-        <v>7626</v>
+        <v>5679</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D130" s="51">
-        <v>1001066607626</v>
+        <v>1001190765679</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G130" s="23">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I130" s="14">
         <v>60</v>
       </c>
-      <c r="J130" s="52" t="s">
+      <c r="J130" s="29"/>
+      <c r="L130" s="102"/>
+    </row>
+    <row r="131" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="109" t="str">
+        <f t="shared" si="17"/>
+        <v>7626</v>
+      </c>
+      <c r="B131" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="C131" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" s="51">
+        <v>1001066607626</v>
+      </c>
+      <c r="E131" s="24"/>
+      <c r="F131" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G131" s="23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="H131" s="14">
+        <v>1</v>
+      </c>
+      <c r="I131" s="14">
+        <v>60</v>
+      </c>
+      <c r="J131" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="L130" s="102"/>
-    </row>
-    <row r="131" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="47" t="s">
+      <c r="L131" s="102"/>
+    </row>
+    <row r="132" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B131" s="42" t="s">
+      <c r="B132" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C131" s="42"/>
-      <c r="D131" s="42"/>
-      <c r="E131" s="42"/>
-      <c r="F131" s="41"/>
-      <c r="G131" s="42"/>
-      <c r="H131" s="42"/>
-      <c r="I131" s="42"/>
-      <c r="J131" s="43"/>
-      <c r="L131" s="102"/>
-    </row>
-    <row r="132" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="109" t="str">
-        <f t="shared" ref="A132:A146" si="24">RIGHT(D132,4)</f>
+      <c r="C132" s="42"/>
+      <c r="D132" s="42"/>
+      <c r="E132" s="42"/>
+      <c r="F132" s="41"/>
+      <c r="G132" s="42"/>
+      <c r="H132" s="42"/>
+      <c r="I132" s="42"/>
+      <c r="J132" s="43"/>
+      <c r="L132" s="102"/>
+    </row>
+    <row r="133" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="109" t="str">
+        <f t="shared" ref="A133:A147" si="24">RIGHT(D133,4)</f>
         <v>4584</v>
       </c>
-      <c r="B132" s="98" t="s">
+      <c r="B133" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="C132" s="50" t="s">
+      <c r="C133" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D132" s="116">
+      <c r="D133" s="116">
         <v>1001092674584</v>
       </c>
-      <c r="E132" s="24"/>
-      <c r="F132" s="23">
+      <c r="E133" s="24"/>
+      <c r="F133" s="23">
         <v>2.5</v>
       </c>
-      <c r="G132" s="23">
-        <f>E132</f>
+      <c r="G133" s="23">
+        <f>E133</f>
         <v>0</v>
       </c>
-      <c r="H132" s="14">
+      <c r="H133" s="14">
         <v>7.5</v>
       </c>
-      <c r="I132" s="14">
+      <c r="I133" s="14">
         <v>60</v>
-      </c>
-      <c r="J132" s="29"/>
-      <c r="L132" s="102"/>
-    </row>
-    <row r="133" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="109" t="str">
-        <f t="shared" si="24"/>
-        <v>6495</v>
-      </c>
-      <c r="B133" s="98" t="s">
-        <v>97</v>
-      </c>
-      <c r="C133" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D133" s="51">
-        <v>1001092436495</v>
-      </c>
-      <c r="E133" s="24"/>
-      <c r="F133" s="111">
-        <v>0.3</v>
-      </c>
-      <c r="G133" s="23">
-        <f>E133*F133</f>
-        <v>0</v>
-      </c>
-      <c r="H133" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I133" s="29">
-        <v>45</v>
       </c>
       <c r="J133" s="29"/>
       <c r="L133" s="102"/>
@@ -12053,27 +12058,27 @@
     <row r="134" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6470</v>
-      </c>
-      <c r="B134" s="117" t="s">
-        <v>126</v>
+        <v>6495</v>
+      </c>
+      <c r="B134" s="98" t="s">
+        <v>97</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D134" s="51">
-        <v>1001092436470</v>
+        <v>1001092436495</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="111">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" ref="G134:G135" si="25">E134</f>
+        <f>E134*F134</f>
         <v>0</v>
       </c>
       <c r="H134" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I134" s="29">
         <v>45</v>
@@ -12083,57 +12088,57 @@
     <row r="135" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>5452</v>
+        <v>6470</v>
       </c>
       <c r="B135" s="117" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D135" s="51">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="111">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="G135" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G135:G136" si="25">E135</f>
         <v>0</v>
       </c>
       <c r="H135" s="29">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="I135" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J135" s="29"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>3215</v>
+        <v>5452</v>
       </c>
       <c r="B136" s="117" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D136" s="51">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="111">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G136" s="23">
-        <f>E136*F136</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H136" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I136" s="29">
         <v>60</v>
@@ -12143,27 +12148,27 @@
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6866</v>
+        <v>3215</v>
       </c>
       <c r="B137" s="117" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D137" s="51">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="111">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G137" s="23">
-        <f>E137</f>
+        <f>E137*F137</f>
         <v>0</v>
       </c>
       <c r="H137" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I137" s="29">
         <v>60</v>
@@ -12173,27 +12178,27 @@
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>5495</v>
-      </c>
-      <c r="B138" s="53" t="s">
-        <v>96</v>
+        <v>6866</v>
+      </c>
+      <c r="B138" s="117" t="s">
+        <v>93</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D138" s="110">
-        <v>1001093345495</v>
+        <v>23</v>
+      </c>
+      <c r="D138" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="111">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G138" s="23">
-        <f t="shared" ref="G138:G141" si="26">E138*F138</f>
+        <f>E138</f>
         <v>0</v>
       </c>
       <c r="H138" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I138" s="29">
         <v>60</v>
@@ -12203,46 +12208,46 @@
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>7377</v>
+        <v>5495</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C139" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D139" s="110">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="111">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G139" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G139:G142" si="26">E139*F139</f>
         <v>0</v>
       </c>
       <c r="H139" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I139" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J139" s="29"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6411</v>
+        <v>7377</v>
       </c>
       <c r="B140" s="53" t="s">
-        <v>224</v>
+        <v>127</v>
       </c>
       <c r="C140" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D140" s="110">
-        <v>1001093316411</v>
+        <v>1001095027377</v>
       </c>
       <c r="E140" s="24"/>
       <c r="F140" s="111">
@@ -12252,167 +12257,165 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H140" s="29"/>
-      <c r="I140" s="29"/>
+      <c r="H140" s="29">
+        <v>1.8</v>
+      </c>
+      <c r="I140" s="29">
+        <v>45</v>
+      </c>
       <c r="J140" s="29"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6925</v>
+        <v>6411</v>
       </c>
       <c r="B141" s="53" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="C141" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D141" s="110">
-        <v>1001095226925</v>
+        <v>1001093316411</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="111">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G141" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H141" s="29">
-        <v>4.8</v>
-      </c>
-      <c r="I141" s="29">
-        <v>45</v>
-      </c>
+      <c r="H141" s="29"/>
+      <c r="I141" s="29"/>
       <c r="J141" s="29"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6025</v>
+        <v>6925</v>
       </c>
       <c r="B142" s="53" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D142" s="110">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="111">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G142" s="23">
-        <f>E142</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H142" s="29">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I142" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J142" s="29"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>6929</v>
+        <v>6025</v>
       </c>
       <c r="B143" s="53" t="s">
-        <v>229</v>
+        <v>128</v>
       </c>
       <c r="C143" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D143" s="110">
-        <v>1001085476929</v>
+        <v>1001094966025</v>
       </c>
       <c r="E143" s="24"/>
-      <c r="F143" s="111"/>
+      <c r="F143" s="111">
+        <v>3</v>
+      </c>
       <c r="G143" s="23">
         <f>E143</f>
         <v>0</v>
       </c>
-      <c r="H143" s="29"/>
-      <c r="I143" s="29"/>
+      <c r="H143" s="29">
+        <v>6</v>
+      </c>
+      <c r="I143" s="29">
+        <v>60</v>
+      </c>
       <c r="J143" s="29"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>7485</v>
+        <v>6929</v>
       </c>
       <c r="B144" s="53" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D144" s="110">
-        <v>1001107397485</v>
+        <v>1001085476929</v>
       </c>
       <c r="E144" s="24"/>
-      <c r="F144" s="111">
-        <v>0.15</v>
-      </c>
+      <c r="F144" s="111"/>
       <c r="G144" s="23">
-        <f>F144*E144</f>
+        <f>E144</f>
         <v>0</v>
       </c>
       <c r="H144" s="29"/>
       <c r="I144" s="29"/>
-      <c r="J144" s="105" t="s">
-        <v>205</v>
-      </c>
+      <c r="J144" s="29"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>7647</v>
+        <v>7485</v>
       </c>
       <c r="B145" s="53" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C145" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D145" s="110">
-        <v>1001097747647</v>
+        <v>1001107397485</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="111">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G145" s="23">
-        <f>E145*F145</f>
+        <f>F145*E145</f>
         <v>0</v>
       </c>
-      <c r="H145" s="29">
-        <v>1</v>
-      </c>
-      <c r="I145" s="29">
-        <v>30</v>
-      </c>
+      <c r="H145" s="29"/>
+      <c r="I145" s="29"/>
       <c r="J145" s="105" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="109" t="str">
         <f t="shared" si="24"/>
-        <v>7651</v>
+        <v>7647</v>
       </c>
       <c r="B146" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C146" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D146" s="110">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="111">
@@ -12432,72 +12435,74 @@
         <v>205</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="47" t="s">
+    <row r="147" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="109" t="str">
+        <f t="shared" si="24"/>
+        <v>7651</v>
+      </c>
+      <c r="B147" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C147" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" s="110">
+        <v>1001097767651</v>
+      </c>
+      <c r="E147" s="24"/>
+      <c r="F147" s="111">
+        <v>0.1</v>
+      </c>
+      <c r="G147" s="23">
+        <f>E147*F147</f>
+        <v>0</v>
+      </c>
+      <c r="H147" s="29">
+        <v>1</v>
+      </c>
+      <c r="I147" s="29">
+        <v>30</v>
+      </c>
+      <c r="J147" s="105" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B147" s="42" t="s">
+      <c r="B148" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C147" s="42"/>
-      <c r="D147" s="42"/>
-      <c r="E147" s="42"/>
-      <c r="F147" s="41"/>
-      <c r="G147" s="42"/>
-      <c r="H147" s="42"/>
-      <c r="I147" s="42"/>
-      <c r="J147" s="43"/>
-    </row>
-    <row r="148" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="109" t="str">
-        <f t="shared" ref="A148:A159" si="27">RIGHT(D148,4)</f>
+      <c r="C148" s="42"/>
+      <c r="D148" s="42"/>
+      <c r="E148" s="42"/>
+      <c r="F148" s="41"/>
+      <c r="G148" s="42"/>
+      <c r="H148" s="42"/>
+      <c r="I148" s="42"/>
+      <c r="J148" s="43"/>
+    </row>
+    <row r="149" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="109" t="str">
+        <f t="shared" ref="A149:A162" si="27">RIGHT(D149,4)</f>
         <v>7090</v>
       </c>
-      <c r="B148" s="35" t="s">
+      <c r="B149" s="35" t="s">
         <v>102</v>
-      </c>
-      <c r="C148" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D148" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E148" s="24"/>
-      <c r="F148" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G148" s="23">
-        <f t="shared" ref="G148:G149" si="28">E148*F148</f>
-        <v>0</v>
-      </c>
-      <c r="H148" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I148" s="14">
-        <v>50</v>
-      </c>
-      <c r="J148" s="29"/>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="109" t="str">
-        <f t="shared" si="27"/>
-        <v>7187</v>
-      </c>
-      <c r="B149" s="35" t="s">
-        <v>103</v>
       </c>
       <c r="C149" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="23">
         <v>0.3</v>
       </c>
       <c r="G149" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G149:G150" si="28">E149*F149</f>
         <v>0</v>
       </c>
       <c r="H149" s="14">
@@ -12511,119 +12516,119 @@
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6008</v>
+        <v>7187</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D150" s="51">
-        <v>1001084856008</v>
+        <v>1001085637187</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="23">
         <v>0.3</v>
       </c>
       <c r="G150" s="23">
-        <f>E150</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H150" s="14">
         <v>1.8</v>
       </c>
       <c r="I150" s="14">
-        <v>40</v>
-      </c>
-      <c r="J150" s="105" t="s">
-        <v>205</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J150" s="29"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6620</v>
+        <v>6008</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="C151" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D151" s="51">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G151" s="23">
         <f>E151</f>
         <v>0</v>
       </c>
       <c r="H151" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I151" s="14">
-        <v>30</v>
-      </c>
-      <c r="J151" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J151" s="105" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>7103</v>
+        <v>6620</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D152" s="51">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G152" s="23">
-        <f t="shared" ref="G152:G159" si="29">E152*F152</f>
+        <f>E152</f>
         <v>0</v>
       </c>
       <c r="H152" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I152" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J152" s="29"/>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>7092</v>
+        <v>7103</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D153" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G153:G162" si="29">E153*F153</f>
         <v>0</v>
       </c>
       <c r="H153" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I153" s="14">
         <v>50</v>
@@ -12633,57 +12638,57 @@
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6228</v>
+        <v>7092</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C154" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D154" s="51">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G154" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I154" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J154" s="29"/>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6448</v>
+        <v>6228</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D155" s="51">
-        <v>1001234146448</v>
+        <v>1001225416228</v>
       </c>
       <c r="E155" s="24"/>
       <c r="F155" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G155" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H155" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I155" s="14">
         <v>45</v>
@@ -12693,27 +12698,27 @@
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6208</v>
+        <v>6448</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D156" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G156" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H156" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I156" s="14">
         <v>45</v>
@@ -12723,146 +12728,198 @@
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6754</v>
+        <v>6208</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D157" s="51">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G157" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I157" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J157" s="29"/>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>6279</v>
+        <v>6754</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G158" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I158" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J158" s="29"/>
     </row>
-    <row r="159" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="109" t="str">
         <f t="shared" si="27"/>
-        <v>7612</v>
+        <v>6279</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D159" s="51">
-        <v>1001453907612</v>
+        <v>1001220286279</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G159" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I159" s="14">
+        <v>45</v>
+      </c>
+      <c r="J159" s="29"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" s="109" t="str">
+        <f t="shared" si="27"/>
+        <v>7612</v>
+      </c>
+      <c r="B160" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C160" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D160" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E160" s="24"/>
+      <c r="F160" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G160" s="23">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H160" s="14">
         <v>1</v>
       </c>
-      <c r="I159" s="14">
+      <c r="I160" s="14">
         <v>60</v>
       </c>
-      <c r="J159" s="52" t="s">
+      <c r="J160" s="52" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="48"/>
-      <c r="B160" s="45" t="s">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="109" t="str">
+        <f t="shared" si="27"/>
+        <v>7344</v>
+      </c>
+      <c r="B161" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C161" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D161" s="51">
+        <v>1001122287344</v>
+      </c>
+      <c r="E161" s="24"/>
+      <c r="F161" s="23">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="G161" s="23">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H161" s="14"/>
+      <c r="I161" s="14"/>
+      <c r="J161" s="29"/>
+    </row>
+    <row r="162" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="109" t="str">
+        <f t="shared" si="27"/>
+        <v>7345</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C162" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162" s="51">
+        <v>1001123677345</v>
+      </c>
+      <c r="E162" s="24"/>
+      <c r="F162" s="23">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="G162" s="23">
+        <f>E162*F162</f>
+        <v>0</v>
+      </c>
+      <c r="H162" s="14"/>
+      <c r="I162" s="14"/>
+      <c r="J162" s="29"/>
+    </row>
+    <row r="163" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="48"/>
+      <c r="B163" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C160" s="16"/>
-      <c r="D160" s="36"/>
-      <c r="E160" s="17">
-        <f>SUM(E10:E159)</f>
+      <c r="C163" s="16"/>
+      <c r="D163" s="36"/>
+      <c r="E163" s="17">
+        <f>SUM(E10:E160)</f>
         <v>0</v>
       </c>
-      <c r="F160" s="17"/>
-      <c r="G160" s="17">
-        <f>SUM(G11:G159)</f>
+      <c r="F163" s="17"/>
+      <c r="G163" s="17">
+        <f>SUM(G11:G162)</f>
         <v>0</v>
       </c>
-      <c r="H160" s="17"/>
-      <c r="I160" s="17"/>
-      <c r="J160" s="17"/>
-    </row>
-    <row r="161" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="37"/>
-      <c r="C161" s="18"/>
-      <c r="D161" s="40"/>
-      <c r="F161" s="19"/>
-      <c r="G161" s="19"/>
-      <c r="H161" s="20"/>
-      <c r="I161" s="20"/>
-      <c r="J161" s="21"/>
-    </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B162" s="37"/>
-      <c r="C162" s="18"/>
-      <c r="D162" s="40"/>
-      <c r="F162" s="19"/>
-      <c r="G162" s="19"/>
-      <c r="H162" s="20"/>
-      <c r="I162" s="20"/>
-      <c r="J162" s="21"/>
-    </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B163" s="37"/>
-      <c r="C163" s="18"/>
-      <c r="D163" s="40"/>
-      <c r="F163" s="19"/>
-      <c r="G163" s="19"/>
-      <c r="H163" s="20"/>
-      <c r="I163" s="20"/>
-      <c r="J163" s="21"/>
-    </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H163" s="17"/>
+      <c r="I163" s="17"/>
+      <c r="J163" s="17"/>
+    </row>
+    <row r="164" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B164" s="37"/>
       <c r="C164" s="18"/>
       <c r="D164" s="40"/>
@@ -12872,7 +12929,7 @@
       <c r="I164" s="20"/>
       <c r="J164" s="21"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B165" s="37"/>
       <c r="C165" s="18"/>
       <c r="D165" s="40"/>
@@ -12882,7 +12939,7 @@
       <c r="I165" s="20"/>
       <c r="J165" s="21"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B166" s="37"/>
       <c r="C166" s="18"/>
       <c r="D166" s="40"/>
@@ -12892,7 +12949,7 @@
       <c r="I166" s="20"/>
       <c r="J166" s="21"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B167" s="37"/>
       <c r="C167" s="18"/>
       <c r="D167" s="40"/>
@@ -12902,7 +12959,7 @@
       <c r="I167" s="20"/>
       <c r="J167" s="21"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B168" s="37"/>
       <c r="C168" s="18"/>
       <c r="D168" s="40"/>
@@ -12912,7 +12969,7 @@
       <c r="I168" s="20"/>
       <c r="J168" s="21"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B169" s="37"/>
       <c r="C169" s="18"/>
       <c r="D169" s="40"/>
@@ -12922,7 +12979,7 @@
       <c r="I169" s="20"/>
       <c r="J169" s="21"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B170" s="37"/>
       <c r="C170" s="18"/>
       <c r="D170" s="40"/>
@@ -12932,7 +12989,7 @@
       <c r="I170" s="20"/>
       <c r="J170" s="21"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
       <c r="C171" s="18"/>
       <c r="D171" s="40"/>
@@ -12942,7 +12999,7 @@
       <c r="I171" s="20"/>
       <c r="J171" s="21"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B172" s="37"/>
       <c r="C172" s="18"/>
       <c r="D172" s="40"/>
@@ -12952,7 +13009,7 @@
       <c r="I172" s="20"/>
       <c r="J172" s="21"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
       <c r="C173" s="18"/>
       <c r="D173" s="40"/>
@@ -12962,7 +13019,7 @@
       <c r="I173" s="20"/>
       <c r="J173" s="21"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
       <c r="C174" s="18"/>
       <c r="D174" s="40"/>
@@ -12972,7 +13029,7 @@
       <c r="I174" s="20"/>
       <c r="J174" s="21"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B175" s="37"/>
       <c r="C175" s="18"/>
       <c r="D175" s="40"/>
@@ -12982,7 +13039,7 @@
       <c r="I175" s="20"/>
       <c r="J175" s="21"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B176" s="37"/>
       <c r="C176" s="18"/>
       <c r="D176" s="40"/>
